--- a/artfynd/A 39541-2025 artfynd.xlsx
+++ b/artfynd/A 39541-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -778,6 +778,5818 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129254223</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57566</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>102621</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Sparvuggla</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Glaucidium passerinum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Mångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>486737</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7037835</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129254218</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57725</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Mångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>486524</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7037965</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129254206</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57725</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Mångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>486751</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7037804</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129254875</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57725</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Mångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>486429</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7037954</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129242015</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57725</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>486782</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7037909</v>
+      </c>
+      <c r="S7" t="n">
+        <v>11</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129242509</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79037</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Mångan, Mångan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>486672</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7037952</v>
+      </c>
+      <c r="S8" t="n">
+        <v>11</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129241859</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79037</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Tomasbodarna, Tomasbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>486860</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7037938</v>
+      </c>
+      <c r="S9" t="n">
+        <v>9</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129243523</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57725</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>486472</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7037927</v>
+      </c>
+      <c r="S10" t="n">
+        <v>11</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en hyfsat grov gran.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129254871</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57725</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Mångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>486833</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7037850</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129254215</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57725</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Mångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>486524</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7037917</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129254205</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57725</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Mångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>486752</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7037802</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129254220</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57725</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Mångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>486583</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7038073</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129254208</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57725</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Mångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>486747</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7037816</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129254221</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57725</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Mångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>486595</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7038075</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129254211</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57725</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Mångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>486582</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7037881</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129243687</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98667</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Mångan, Mångan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>486517</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7037922</v>
+      </c>
+      <c r="S18" t="n">
+        <v>12</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Minst 120 plantor och 1 fröställning inom ca 1 m2 yta  intill en naturvårdsnitslad björk.</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129254199</v>
+      </c>
+      <c r="B19" t="n">
+        <v>83013</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Mångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>486581</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7038074</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129242968</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79037</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Mångan, Mångan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>486617</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7037991</v>
+      </c>
+      <c r="S20" t="n">
+        <v>9</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129254216</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57725</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Mångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>486478</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7037962</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129254228</v>
+      </c>
+      <c r="B22" t="n">
+        <v>91549</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Mångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>486556</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7037879</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129254210</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57725</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Mångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>486650</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7037866</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129254222</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57885</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Mångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>486607</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7038047</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129254212</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57725</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Mångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>486572</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7037884</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129254874</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57725</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Mångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>486550</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7037929</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129254219</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57725</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Mångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>486543</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7037939</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129244388</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79037</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Mångan, Mångan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>486782</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7037877</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129254201</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57725</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Mångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>486797</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7037788</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129254876</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57725</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Mångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>486409</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7037957</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129241899</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79037</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Mångan, Mångan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>486803</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7037939</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>129254873</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57725</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Mångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>486683</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7037917</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>129254877</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57725</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Mångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>486495</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7037956</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>129254202</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57725</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Mångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>486780</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7037796</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>129254204</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57725</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Mångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>486767</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7037800</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>129254203</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57725</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Mångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>486775</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7037792</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>129254207</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57725</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Mångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>486743</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7037808</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>129254217</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57725</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Mångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>486372</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7038001</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>129244231</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79037</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Mångan, Mångan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>486671</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7037887</v>
+      </c>
+      <c r="S39" t="n">
+        <v>12</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>129254226</v>
+      </c>
+      <c r="B40" t="n">
+        <v>78050</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Mångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>486585</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7038070</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>129243863</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79037</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Mångan, Mångan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>486663</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7037905</v>
+      </c>
+      <c r="S41" t="n">
+        <v>12</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Långväxta bålar, på flera granar.</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>129243061</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57725</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>486568</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7037962</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen.</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>129254225</v>
+      </c>
+      <c r="B43" t="n">
+        <v>80046</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Mångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>486624</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7038036</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>129254230</v>
+      </c>
+      <c r="B44" t="n">
+        <v>82900</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Mångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>486609</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7038052</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>129254879</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57725</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Mångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>486552</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7037942</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>129254872</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57725</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Mångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>486715</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7037924</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>129254227</v>
+      </c>
+      <c r="B47" t="n">
+        <v>91527</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Mångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>486462</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7037962</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>129254214</v>
+      </c>
+      <c r="B48" t="n">
+        <v>57725</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Mångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>486551</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7037889</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>129254231</v>
+      </c>
+      <c r="B49" t="n">
+        <v>88928</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>510</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Mångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>486615</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7037875</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>129254196</v>
+      </c>
+      <c r="B50" t="n">
+        <v>83013</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Mångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>486582</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7038072</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>129254224</v>
+      </c>
+      <c r="B51" t="n">
+        <v>80046</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Mångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>486599</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7038068</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>129243695</v>
+      </c>
+      <c r="B52" t="n">
+        <v>79037</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Mångan, Mångan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>486541</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7037938</v>
+      </c>
+      <c r="S52" t="n">
+        <v>11</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>129254213</v>
+      </c>
+      <c r="B53" t="n">
+        <v>57725</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Mångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>486551</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7037886</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>129254229</v>
+      </c>
+      <c r="B54" t="n">
+        <v>82900</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Mångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>486611</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7038042</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>129243772</v>
+      </c>
+      <c r="B55" t="n">
+        <v>79037</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Mångan, Mångan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>486608</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7037908</v>
+      </c>
+      <c r="S55" t="n">
+        <v>9</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>129254878</v>
+      </c>
+      <c r="B56" t="n">
+        <v>57725</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Mångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>486553</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7037937</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39541-2025 artfynd.xlsx
+++ b/artfynd/A 39541-2025 artfynd.xlsx
@@ -781,27 +781,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129254223</v>
+        <v>129254218</v>
       </c>
       <c r="B3" t="n">
-        <v>57566</v>
+        <v>57725</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -809,29 +809,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>486737</v>
+        <v>486524</v>
       </c>
       <c r="R3" t="n">
-        <v>7037835</v>
+        <v>7037965</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,6 +852,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,7 +883,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129254218</v>
+        <v>129254875</v>
       </c>
       <c r="B4" t="n">
         <v>57725</v>
@@ -925,10 +918,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486524</v>
+        <v>486429</v>
       </c>
       <c r="R4" t="n">
-        <v>7037965</v>
+        <v>7037954</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,7 +958,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -980,12 +973,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1094,27 +1087,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129254875</v>
+        <v>129254223</v>
       </c>
       <c r="B6" t="n">
-        <v>57725</v>
+        <v>57566</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1122,17 +1115,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>486429</v>
+        <v>486737</v>
       </c>
       <c r="R6" t="n">
-        <v>7037954</v>
+        <v>7037835</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1167,11 +1172,6 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1184,22 +1184,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129242015</v>
+        <v>129241859</v>
       </c>
       <c r="B7" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1207,47 +1207,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
+          <t>Tomasbodarna, Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>486782</v>
+        <v>486860</v>
       </c>
       <c r="R7" t="n">
-        <v>7037909</v>
+        <v>7037938</v>
       </c>
       <c r="S7" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1276,7 +1266,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1286,12 +1276,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1305,27 +1290,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1346,7 +1311,7 @@
         <v>129242509</v>
       </c>
       <c r="B8" t="n">
-        <v>79037</v>
+        <v>79039</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,10 +1420,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129241859</v>
+        <v>129242015</v>
       </c>
       <c r="B9" t="n">
-        <v>79037</v>
+        <v>57725</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1466,37 +1431,47 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Tomasbodarna, Tomasbodarna, Jmt</t>
+          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>486860</v>
+        <v>486782</v>
       </c>
       <c r="R9" t="n">
-        <v>7037938</v>
+        <v>7037909</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1525,7 +1500,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1535,7 +1510,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1549,7 +1529,27 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1816,7 +1816,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129254215</v>
+        <v>129254205</v>
       </c>
       <c r="B12" t="n">
         <v>57725</v>
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>486524</v>
+        <v>486752</v>
       </c>
       <c r="R12" t="n">
-        <v>7037917</v>
+        <v>7037802</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1918,7 +1918,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129254205</v>
+        <v>129254220</v>
       </c>
       <c r="B13" t="n">
         <v>57725</v>
@@ -1953,10 +1953,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>486752</v>
+        <v>486583</v>
       </c>
       <c r="R13" t="n">
-        <v>7037802</v>
+        <v>7038073</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2020,7 +2020,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129254220</v>
+        <v>129254215</v>
       </c>
       <c r="B14" t="n">
         <v>57725</v>
@@ -2055,10 +2055,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>486583</v>
+        <v>486524</v>
       </c>
       <c r="R14" t="n">
-        <v>7038073</v>
+        <v>7037917</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2224,7 +2224,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129254221</v>
+        <v>129254211</v>
       </c>
       <c r="B16" t="n">
         <v>57725</v>
@@ -2259,10 +2259,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>486595</v>
+        <v>486582</v>
       </c>
       <c r="R16" t="n">
-        <v>7038075</v>
+        <v>7037881</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2326,7 +2326,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129254211</v>
+        <v>129254221</v>
       </c>
       <c r="B17" t="n">
         <v>57725</v>
@@ -2361,10 +2361,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>486582</v>
+        <v>486595</v>
       </c>
       <c r="R17" t="n">
-        <v>7037881</v>
+        <v>7038075</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2431,7 +2431,7 @@
         <v>129243687</v>
       </c>
       <c r="B18" t="n">
-        <v>98667</v>
+        <v>98669</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>129254199</v>
       </c>
       <c r="B19" t="n">
-        <v>83013</v>
+        <v>83015</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         <v>129242968</v>
       </c>
       <c r="B20" t="n">
-        <v>79037</v>
+        <v>79039</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2887,10 +2887,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129254228</v>
+        <v>129254222</v>
       </c>
       <c r="B22" t="n">
-        <v>91549</v>
+        <v>57885</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2898,34 +2898,50 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>486556</v>
+        <v>486607</v>
       </c>
       <c r="R22" t="n">
-        <v>7037879</v>
+        <v>7038047</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3086,10 +3102,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129254222</v>
+        <v>129254228</v>
       </c>
       <c r="B24" t="n">
-        <v>57885</v>
+        <v>91551</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3097,50 +3113,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>486607</v>
+        <v>486556</v>
       </c>
       <c r="R24" t="n">
-        <v>7038047</v>
+        <v>7037879</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3508,7 +3508,7 @@
         <v>129244388</v>
       </c>
       <c r="B28" t="n">
-        <v>79037</v>
+        <v>79039</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         <v>129241899</v>
       </c>
       <c r="B31" t="n">
-        <v>79037</v>
+        <v>79039</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129254202</v>
+        <v>129254204</v>
       </c>
       <c r="B34" t="n">
         <v>57725</v>
@@ -4197,10 +4197,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>486780</v>
+        <v>486767</v>
       </c>
       <c r="R34" t="n">
-        <v>7037796</v>
+        <v>7037800</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4237,7 +4237,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4264,7 +4264,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129254204</v>
+        <v>129254202</v>
       </c>
       <c r="B35" t="n">
         <v>57725</v>
@@ -4299,10 +4299,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>486767</v>
+        <v>486780</v>
       </c>
       <c r="R35" t="n">
-        <v>7037800</v>
+        <v>7037796</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4339,7 +4339,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4366,7 +4366,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129254203</v>
+        <v>129254207</v>
       </c>
       <c r="B36" t="n">
         <v>57725</v>
@@ -4401,10 +4401,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>486775</v>
+        <v>486743</v>
       </c>
       <c r="R36" t="n">
-        <v>7037792</v>
+        <v>7037808</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4468,7 +4468,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129254207</v>
+        <v>129254203</v>
       </c>
       <c r="B37" t="n">
         <v>57725</v>
@@ -4503,10 +4503,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>486743</v>
+        <v>486775</v>
       </c>
       <c r="R37" t="n">
-        <v>7037808</v>
+        <v>7037792</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4672,10 +4672,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129244231</v>
+        <v>129254226</v>
       </c>
       <c r="B39" t="n">
-        <v>79037</v>
+        <v>78052</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4683,37 +4683,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>486671</v>
+        <v>486585</v>
       </c>
       <c r="R39" t="n">
-        <v>7037887</v>
+        <v>7038070</v>
       </c>
       <c r="S39" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4740,24 +4740,9 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4772,22 +4757,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129254226</v>
+        <v>129244231</v>
       </c>
       <c r="B40" t="n">
-        <v>78050</v>
+        <v>79039</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4795,37 +4780,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>486585</v>
+        <v>486671</v>
       </c>
       <c r="R40" t="n">
-        <v>7038070</v>
+        <v>7037887</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4852,9 +4837,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4869,60 +4869,60 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129243863</v>
+        <v>129254225</v>
       </c>
       <c r="B41" t="n">
-        <v>79037</v>
+        <v>80048</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>486663</v>
+        <v>486624</v>
       </c>
       <c r="R41" t="n">
-        <v>7037905</v>
+        <v>7038036</v>
       </c>
       <c r="S41" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4949,26 +4949,11 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Långväxta bålar, på flera granar.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -4977,48 +4962,23 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129243061</v>
+        <v>129254879</v>
       </c>
       <c r="B42" t="n">
         <v>57725</v>
@@ -5047,26 +5007,16 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>486568</v>
+        <v>486552</v>
       </c>
       <c r="R42" t="n">
-        <v>7037962</v>
+        <v>7037942</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5096,24 +5046,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5124,73 +5064,48 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129254225</v>
+        <v>129254872</v>
       </c>
       <c r="B43" t="n">
-        <v>80046</v>
+        <v>57725</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5200,10 +5115,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>486624</v>
+        <v>486715</v>
       </c>
       <c r="R43" t="n">
-        <v>7038036</v>
+        <v>7037924</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5238,6 +5153,11 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5250,12 +5170,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5265,7 +5185,7 @@
         <v>129254230</v>
       </c>
       <c r="B44" t="n">
-        <v>82900</v>
+        <v>82902</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5359,10 +5279,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129254879</v>
+        <v>129243863</v>
       </c>
       <c r="B45" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5370,37 +5290,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>486552</v>
+        <v>486663</v>
       </c>
       <c r="R45" t="n">
-        <v>7037942</v>
+        <v>7037905</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5427,14 +5347,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Långväxta bålar, på flera granar.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5445,23 +5375,48 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129254872</v>
+        <v>129243061</v>
       </c>
       <c r="B46" t="n">
         <v>57725</v>
@@ -5490,16 +5445,26 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>486715</v>
+        <v>486568</v>
       </c>
       <c r="R46" t="n">
-        <v>7037924</v>
+        <v>7037962</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5529,14 +5494,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5547,16 +5522,41 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5566,7 +5566,7 @@
         <v>129254227</v>
       </c>
       <c r="B47" t="n">
-        <v>91527</v>
+        <v>91529</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5660,10 +5660,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129254214</v>
+        <v>129254196</v>
       </c>
       <c r="B48" t="n">
-        <v>57725</v>
+        <v>83015</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5671,21 +5671,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5695,10 +5695,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>486551</v>
+        <v>486582</v>
       </c>
       <c r="R48" t="n">
-        <v>7037889</v>
+        <v>7038072</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5731,11 +5731,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5762,10 +5757,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129254231</v>
+        <v>129254214</v>
       </c>
       <c r="B49" t="n">
-        <v>88928</v>
+        <v>57725</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5773,21 +5768,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5797,10 +5792,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>486615</v>
+        <v>486551</v>
       </c>
       <c r="R49" t="n">
-        <v>7037875</v>
+        <v>7037889</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5833,6 +5828,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5859,32 +5859,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129254196</v>
+        <v>129254224</v>
       </c>
       <c r="B50" t="n">
-        <v>83013</v>
+        <v>80048</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6440</v>
+        <v>6456</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5894,10 +5894,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>486582</v>
+        <v>486599</v>
       </c>
       <c r="R50" t="n">
-        <v>7038072</v>
+        <v>7038068</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5956,32 +5956,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129254224</v>
+        <v>129254231</v>
       </c>
       <c r="B51" t="n">
-        <v>80046</v>
+        <v>88930</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6456</v>
+        <v>510</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5991,10 +5991,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>486599</v>
+        <v>486615</v>
       </c>
       <c r="R51" t="n">
-        <v>7038068</v>
+        <v>7037875</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6056,7 +6056,7 @@
         <v>129243695</v>
       </c>
       <c r="B52" t="n">
-        <v>79037</v>
+        <v>79039</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6265,7 +6265,7 @@
         <v>129254229</v>
       </c>
       <c r="B54" t="n">
-        <v>82900</v>
+        <v>82902</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>129243772</v>
       </c>
       <c r="B55" t="n">
-        <v>79037</v>
+        <v>79039</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 39541-2025 artfynd.xlsx
+++ b/artfynd/A 39541-2025 artfynd.xlsx
@@ -1567,7 +1567,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129243523</v>
+        <v>129254871</v>
       </c>
       <c r="B10" t="n">
         <v>57725</v>
@@ -1596,29 +1596,19 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>486472</v>
+        <v>486833</v>
       </c>
       <c r="R10" t="n">
-        <v>7037927</v>
+        <v>7037850</v>
       </c>
       <c r="S10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1645,24 +1635,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>15:21</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:21</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en hyfsat grov gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1673,48 +1653,23 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129254871</v>
+        <v>129254205</v>
       </c>
       <c r="B11" t="n">
         <v>57725</v>
@@ -1749,10 +1704,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>486833</v>
+        <v>486752</v>
       </c>
       <c r="R11" t="n">
-        <v>7037850</v>
+        <v>7037802</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1789,7 +1744,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1804,19 +1759,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129254205</v>
+        <v>129254220</v>
       </c>
       <c r="B12" t="n">
         <v>57725</v>
@@ -1851,10 +1806,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>486752</v>
+        <v>486583</v>
       </c>
       <c r="R12" t="n">
-        <v>7037802</v>
+        <v>7038073</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1918,7 +1873,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129254220</v>
+        <v>129254215</v>
       </c>
       <c r="B13" t="n">
         <v>57725</v>
@@ -1953,10 +1908,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>486583</v>
+        <v>486524</v>
       </c>
       <c r="R13" t="n">
-        <v>7038073</v>
+        <v>7037917</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2020,7 +1975,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129254215</v>
+        <v>129243523</v>
       </c>
       <c r="B14" t="n">
         <v>57725</v>
@@ -2049,19 +2004,29 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>486524</v>
+        <v>486472</v>
       </c>
       <c r="R14" t="n">
-        <v>7037917</v>
+        <v>7037927</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2088,14 +2053,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack, äldre, på stambasen av en hyfsat grov gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2106,16 +2081,41 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2224,48 +2224,68 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129254211</v>
+        <v>129243687</v>
       </c>
       <c r="B16" t="n">
-        <v>57725</v>
+        <v>98669</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>486582</v>
+        <v>486517</v>
       </c>
       <c r="R16" t="n">
-        <v>7037881</v>
+        <v>7037922</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2292,14 +2312,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Minst 120 plantor och 1 fröställning inom ca 1 m2 yta  intill en naturvårdsnitslad björk.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2308,25 +2338,31 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129254221</v>
+        <v>129254211</v>
       </c>
       <c r="B17" t="n">
         <v>57725</v>
@@ -2361,10 +2397,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>486595</v>
+        <v>486582</v>
       </c>
       <c r="R17" t="n">
-        <v>7038075</v>
+        <v>7037881</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2428,68 +2464,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129243687</v>
+        <v>129254221</v>
       </c>
       <c r="B18" t="n">
-        <v>98669</v>
+        <v>57725</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>486517</v>
+        <v>486595</v>
       </c>
       <c r="R18" t="n">
-        <v>7037922</v>
+        <v>7038075</v>
       </c>
       <c r="S18" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2516,24 +2532,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>15:26</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>15:26</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Minst 120 plantor och 1 fröställning inom ca 1 m2 yta  intill en naturvårdsnitslad björk.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2542,24 +2548,18 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2663,10 +2663,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129242968</v>
+        <v>129254216</v>
       </c>
       <c r="B20" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2674,37 +2674,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>486617</v>
+        <v>486478</v>
       </c>
       <c r="R20" t="n">
-        <v>7037991</v>
+        <v>7037962</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2731,19 +2731,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>14:51</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>14:51</t>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2754,41 +2749,26 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129254216</v>
+        <v>129242968</v>
       </c>
       <c r="B21" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2796,37 +2776,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>486478</v>
+        <v>486617</v>
       </c>
       <c r="R21" t="n">
-        <v>7037962</v>
+        <v>7037991</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2853,14 +2833,19 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2871,16 +2856,31 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3622,10 +3622,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129254201</v>
+        <v>129241899</v>
       </c>
       <c r="B29" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3633,34 +3633,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>486797</v>
+        <v>486803</v>
       </c>
       <c r="R29" t="n">
-        <v>7037788</v>
+        <v>7037939</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3690,14 +3690,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3708,23 +3718,43 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129254876</v>
+        <v>129254201</v>
       </c>
       <c r="B30" t="n">
         <v>57725</v>
@@ -3759,10 +3789,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>486409</v>
+        <v>486797</v>
       </c>
       <c r="R30" t="n">
-        <v>7037957</v>
+        <v>7037788</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3799,7 +3829,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3814,22 +3844,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129241899</v>
+        <v>129254876</v>
       </c>
       <c r="B31" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3837,34 +3867,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>486803</v>
+        <v>486409</v>
       </c>
       <c r="R31" t="n">
-        <v>7037939</v>
+        <v>7037957</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3894,24 +3924,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3922,36 +3942,16 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -5279,10 +5279,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129243863</v>
+        <v>129243061</v>
       </c>
       <c r="B45" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5290,37 +5290,47 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>486663</v>
+        <v>486568</v>
       </c>
       <c r="R45" t="n">
-        <v>7037905</v>
+        <v>7037962</v>
       </c>
       <c r="S45" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5349,7 +5359,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5359,12 +5369,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Långväxta bålar, på flera granar.</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5378,7 +5388,7 @@
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr">
@@ -5393,12 +5403,12 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5416,10 +5426,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129243061</v>
+        <v>129243863</v>
       </c>
       <c r="B46" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5427,47 +5437,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>486568</v>
+        <v>486663</v>
       </c>
       <c r="R46" t="n">
-        <v>7037962</v>
+        <v>7037905</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5506,12 +5506,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Långväxta bålar, på flera granar.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5525,7 +5525,7 @@
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ46" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5660,10 +5660,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129254196</v>
+        <v>129254231</v>
       </c>
       <c r="B48" t="n">
-        <v>83015</v>
+        <v>88930</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5671,21 +5671,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6440</v>
+        <v>510</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5695,10 +5695,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>486582</v>
+        <v>486615</v>
       </c>
       <c r="R48" t="n">
-        <v>7038072</v>
+        <v>7037875</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5757,10 +5757,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129254214</v>
+        <v>129254196</v>
       </c>
       <c r="B49" t="n">
-        <v>57725</v>
+        <v>83015</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5768,21 +5768,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5792,10 +5792,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>486551</v>
+        <v>486582</v>
       </c>
       <c r="R49" t="n">
-        <v>7037889</v>
+        <v>7038072</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5828,11 +5828,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5859,32 +5854,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129254224</v>
+        <v>129254214</v>
       </c>
       <c r="B50" t="n">
-        <v>80048</v>
+        <v>57725</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5894,10 +5889,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>486599</v>
+        <v>486551</v>
       </c>
       <c r="R50" t="n">
-        <v>7038068</v>
+        <v>7037889</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5930,6 +5925,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5956,32 +5956,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129254231</v>
+        <v>129254224</v>
       </c>
       <c r="B51" t="n">
-        <v>88930</v>
+        <v>80048</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>510</v>
+        <v>6456</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5991,10 +5991,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>486615</v>
+        <v>486599</v>
       </c>
       <c r="R51" t="n">
-        <v>7037875</v>
+        <v>7038068</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6359,10 +6359,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129243772</v>
+        <v>129254878</v>
       </c>
       <c r="B55" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6370,37 +6370,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>486608</v>
+        <v>486553</v>
       </c>
       <c r="R55" t="n">
-        <v>7037908</v>
+        <v>7037937</v>
       </c>
       <c r="S55" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6427,19 +6427,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>15:38</t>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6450,51 +6445,26 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129254878</v>
+        <v>129243772</v>
       </c>
       <c r="B56" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6502,37 +6472,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>486553</v>
+        <v>486608</v>
       </c>
       <c r="R56" t="n">
-        <v>7037937</v>
+        <v>7037908</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6559,14 +6529,19 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6577,16 +6552,41 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>

--- a/artfynd/A 39541-2025 artfynd.xlsx
+++ b/artfynd/A 39541-2025 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129254218</v>
+        <v>129241859</v>
       </c>
       <c r="B3" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,37 +792,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Tomasbodarna, Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>486524</v>
+        <v>486860</v>
       </c>
       <c r="R3" t="n">
-        <v>7037965</v>
+        <v>7037938</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -849,14 +849,19 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,26 +872,31 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129254875</v>
+        <v>129242509</v>
       </c>
       <c r="B4" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -894,37 +904,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486429</v>
+        <v>486672</v>
       </c>
       <c r="R4" t="n">
-        <v>7037954</v>
+        <v>7037952</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -951,14 +961,19 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -969,23 +984,28 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129254206</v>
+        <v>129242015</v>
       </c>
       <c r="B5" t="n">
         <v>57725</v>
@@ -1014,19 +1034,29 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>486751</v>
+        <v>486782</v>
       </c>
       <c r="R5" t="n">
-        <v>7037804</v>
+        <v>7037909</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1053,14 +1083,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,16 +1111,41 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1196,10 +1261,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129241859</v>
+        <v>129254218</v>
       </c>
       <c r="B7" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1207,37 +1272,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tomasbodarna, Tomasbodarna, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>486860</v>
+        <v>486524</v>
       </c>
       <c r="R7" t="n">
-        <v>7037938</v>
+        <v>7037965</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1264,19 +1329,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>14:27</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:27</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1287,31 +1347,26 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129242509</v>
+        <v>129254875</v>
       </c>
       <c r="B8" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1319,37 +1374,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>486672</v>
+        <v>486429</v>
       </c>
       <c r="R8" t="n">
-        <v>7037952</v>
+        <v>7037954</v>
       </c>
       <c r="S8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1376,19 +1431,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>14:42</t>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1399,28 +1449,23 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129242015</v>
+        <v>129254206</v>
       </c>
       <c r="B9" t="n">
         <v>57725</v>
@@ -1449,29 +1494,19 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>486782</v>
+        <v>486751</v>
       </c>
       <c r="R9" t="n">
-        <v>7037909</v>
+        <v>7037804</v>
       </c>
       <c r="S9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1498,24 +1533,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,41 +1551,16 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -2227,7 +2227,7 @@
         <v>129243687</v>
       </c>
       <c r="B16" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>129254199</v>
       </c>
       <c r="B19" t="n">
-        <v>83015</v>
+        <v>83005</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2663,10 +2663,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129254216</v>
+        <v>129242968</v>
       </c>
       <c r="B20" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2674,37 +2674,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>486478</v>
+        <v>486617</v>
       </c>
       <c r="R20" t="n">
-        <v>7037962</v>
+        <v>7037991</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2731,14 +2731,19 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2749,26 +2754,41 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129242968</v>
+        <v>129254216</v>
       </c>
       <c r="B21" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2776,37 +2796,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>486617</v>
+        <v>486478</v>
       </c>
       <c r="R21" t="n">
-        <v>7037991</v>
+        <v>7037962</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2833,19 +2853,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>14:51</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>14:51</t>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2856,41 +2871,26 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129254222</v>
+        <v>129254228</v>
       </c>
       <c r="B22" t="n">
-        <v>57885</v>
+        <v>91558</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2898,50 +2898,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>486607</v>
+        <v>486556</v>
       </c>
       <c r="R22" t="n">
-        <v>7038047</v>
+        <v>7037879</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3000,10 +2984,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129254210</v>
+        <v>129254222</v>
       </c>
       <c r="B23" t="n">
-        <v>57725</v>
+        <v>57885</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3011,34 +2995,50 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>486650</v>
+        <v>486607</v>
       </c>
       <c r="R23" t="n">
-        <v>7037866</v>
+        <v>7038047</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3071,11 +3071,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3102,10 +3097,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129254228</v>
+        <v>129254210</v>
       </c>
       <c r="B24" t="n">
-        <v>91551</v>
+        <v>57725</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3113,21 +3108,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3137,10 +3132,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>486556</v>
+        <v>486650</v>
       </c>
       <c r="R24" t="n">
-        <v>7037879</v>
+        <v>7037866</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3173,6 +3168,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -4672,10 +4672,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129254226</v>
+        <v>129244231</v>
       </c>
       <c r="B39" t="n">
-        <v>78052</v>
+        <v>79039</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4683,37 +4683,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>486585</v>
+        <v>486671</v>
       </c>
       <c r="R39" t="n">
-        <v>7038070</v>
+        <v>7037887</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4740,9 +4740,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4757,22 +4772,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129244231</v>
+        <v>129254226</v>
       </c>
       <c r="B40" t="n">
-        <v>79039</v>
+        <v>78052</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4780,37 +4795,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>486671</v>
+        <v>486585</v>
       </c>
       <c r="R40" t="n">
-        <v>7037887</v>
+        <v>7038070</v>
       </c>
       <c r="S40" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4837,24 +4852,9 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4869,60 +4869,60 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129254225</v>
+        <v>129243863</v>
       </c>
       <c r="B41" t="n">
-        <v>80048</v>
+        <v>79039</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>486624</v>
+        <v>486663</v>
       </c>
       <c r="R41" t="n">
-        <v>7038036</v>
+        <v>7037905</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4949,11 +4949,26 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Långväxta bålar, på flera granar.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -4962,23 +4977,48 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129254879</v>
+        <v>129243061</v>
       </c>
       <c r="B42" t="n">
         <v>57725</v>
@@ -5007,16 +5047,26 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>486552</v>
+        <v>486568</v>
       </c>
       <c r="R42" t="n">
-        <v>7037942</v>
+        <v>7037962</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5046,14 +5096,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5064,26 +5124,51 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129254872</v>
+        <v>129254230</v>
       </c>
       <c r="B43" t="n">
-        <v>57725</v>
+        <v>82871</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5091,21 +5176,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5115,10 +5200,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>486715</v>
+        <v>486609</v>
       </c>
       <c r="R43" t="n">
-        <v>7037924</v>
+        <v>7038052</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5153,11 +5238,6 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5170,44 +5250,44 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129254230</v>
+        <v>129254225</v>
       </c>
       <c r="B44" t="n">
-        <v>82902</v>
+        <v>80048</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1312</v>
+        <v>6456</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5217,10 +5297,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>486609</v>
+        <v>486624</v>
       </c>
       <c r="R44" t="n">
-        <v>7038052</v>
+        <v>7038036</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5279,7 +5359,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129243061</v>
+        <v>129254879</v>
       </c>
       <c r="B45" t="n">
         <v>57725</v>
@@ -5308,26 +5388,16 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>486568</v>
+        <v>486552</v>
       </c>
       <c r="R45" t="n">
-        <v>7037962</v>
+        <v>7037942</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5357,24 +5427,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5385,51 +5445,26 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129243863</v>
+        <v>129254872</v>
       </c>
       <c r="B46" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5437,37 +5472,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>486663</v>
+        <v>486715</v>
       </c>
       <c r="R46" t="n">
-        <v>7037905</v>
+        <v>7037924</v>
       </c>
       <c r="S46" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5494,24 +5529,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Långväxta bålar, på flera granar.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5522,41 +5547,16 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5566,7 +5566,7 @@
         <v>129254227</v>
       </c>
       <c r="B47" t="n">
-        <v>91529</v>
+        <v>91536</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5663,7 +5663,7 @@
         <v>129254231</v>
       </c>
       <c r="B48" t="n">
-        <v>88930</v>
+        <v>88937</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
         <v>129254196</v>
       </c>
       <c r="B49" t="n">
-        <v>83015</v>
+        <v>83005</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5854,32 +5854,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129254214</v>
+        <v>129254224</v>
       </c>
       <c r="B50" t="n">
-        <v>57725</v>
+        <v>80048</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5889,10 +5889,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>486551</v>
+        <v>486599</v>
       </c>
       <c r="R50" t="n">
-        <v>7037889</v>
+        <v>7038068</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5925,11 +5925,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5956,32 +5951,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129254224</v>
+        <v>129254214</v>
       </c>
       <c r="B51" t="n">
-        <v>80048</v>
+        <v>57725</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5991,10 +5986,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>486599</v>
+        <v>486551</v>
       </c>
       <c r="R51" t="n">
-        <v>7038068</v>
+        <v>7037889</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6027,6 +6022,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6160,10 +6160,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129254213</v>
+        <v>129254229</v>
       </c>
       <c r="B53" t="n">
-        <v>57725</v>
+        <v>82871</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6171,21 +6171,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6195,10 +6195,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>486551</v>
+        <v>486611</v>
       </c>
       <c r="R53" t="n">
-        <v>7037886</v>
+        <v>7038042</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6231,11 +6231,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6262,10 +6257,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129254229</v>
+        <v>129254213</v>
       </c>
       <c r="B54" t="n">
-        <v>82902</v>
+        <v>57725</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6273,21 +6268,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6297,10 +6292,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>486611</v>
+        <v>486551</v>
       </c>
       <c r="R54" t="n">
-        <v>7038042</v>
+        <v>7037886</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6333,6 +6328,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6359,10 +6359,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129254878</v>
+        <v>129243772</v>
       </c>
       <c r="B55" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6370,37 +6370,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>486553</v>
+        <v>486608</v>
       </c>
       <c r="R55" t="n">
-        <v>7037937</v>
+        <v>7037908</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6427,14 +6427,19 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6445,26 +6450,51 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129243772</v>
+        <v>129254878</v>
       </c>
       <c r="B56" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6472,37 +6502,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>486608</v>
+        <v>486553</v>
       </c>
       <c r="R56" t="n">
-        <v>7037908</v>
+        <v>7037937</v>
       </c>
       <c r="S56" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6529,19 +6559,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>15:38</t>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6552,41 +6577,16 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>

--- a/artfynd/A 39541-2025 artfynd.xlsx
+++ b/artfynd/A 39541-2025 artfynd.xlsx
@@ -781,48 +781,60 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129241859</v>
+        <v>129254223</v>
       </c>
       <c r="B3" t="n">
-        <v>79039</v>
+        <v>57568</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>102621</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tomasbodarna, Tomasbodarna, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>486860</v>
+        <v>486737</v>
       </c>
       <c r="R3" t="n">
-        <v>7037938</v>
+        <v>7037835</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -849,21 +861,11 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:27</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:27</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -872,31 +874,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129242509</v>
+        <v>129254875</v>
       </c>
       <c r="B4" t="n">
-        <v>79039</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,37 +901,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486672</v>
+        <v>486429</v>
       </c>
       <c r="R4" t="n">
-        <v>7037952</v>
+        <v>7037954</v>
       </c>
       <c r="S4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -961,19 +958,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:42</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,31 +976,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129242015</v>
+        <v>129254218</v>
       </c>
       <c r="B5" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1034,29 +1021,19 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>486782</v>
+        <v>486524</v>
       </c>
       <c r="R5" t="n">
-        <v>7037909</v>
+        <v>7037965</v>
       </c>
       <c r="S5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,24 +1060,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,68 +1078,43 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129254223</v>
+        <v>129254206</v>
       </c>
       <c r="B6" t="n">
-        <v>57566</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1180,29 +1122,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>486737</v>
+        <v>486751</v>
       </c>
       <c r="R6" t="n">
-        <v>7037835</v>
+        <v>7037804</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1235,6 +1165,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1261,10 +1196,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129254218</v>
+        <v>129241859</v>
       </c>
       <c r="B7" t="n">
-        <v>57725</v>
+        <v>79041</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1272,37 +1207,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Tomasbodarna, Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>486524</v>
+        <v>486860</v>
       </c>
       <c r="R7" t="n">
-        <v>7037965</v>
+        <v>7037938</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1329,14 +1264,19 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,26 +1287,31 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129254875</v>
+        <v>129242509</v>
       </c>
       <c r="B8" t="n">
-        <v>57725</v>
+        <v>79041</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1374,37 +1319,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>486429</v>
+        <v>486672</v>
       </c>
       <c r="R8" t="n">
-        <v>7037954</v>
+        <v>7037952</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1431,14 +1376,19 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1449,26 +1399,31 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129254206</v>
+        <v>129242015</v>
       </c>
       <c r="B9" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,19 +1449,29 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>486751</v>
+        <v>486782</v>
       </c>
       <c r="R9" t="n">
-        <v>7037804</v>
+        <v>7037909</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1533,14 +1498,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1551,26 +1526,51 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129254871</v>
+        <v>129254205</v>
       </c>
       <c r="B10" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1602,10 +1602,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>486833</v>
+        <v>486752</v>
       </c>
       <c r="R10" t="n">
-        <v>7037850</v>
+        <v>7037802</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1642,7 +1642,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1657,22 +1657,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129254205</v>
+        <v>129254220</v>
       </c>
       <c r="B11" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1704,10 +1704,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>486752</v>
+        <v>486583</v>
       </c>
       <c r="R11" t="n">
-        <v>7037802</v>
+        <v>7038073</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1771,10 +1771,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129254220</v>
+        <v>129254215</v>
       </c>
       <c r="B12" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,10 +1806,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>486583</v>
+        <v>486524</v>
       </c>
       <c r="R12" t="n">
-        <v>7038073</v>
+        <v>7037917</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1873,10 +1873,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129254215</v>
+        <v>129254871</v>
       </c>
       <c r="B13" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>486524</v>
+        <v>486833</v>
       </c>
       <c r="R13" t="n">
-        <v>7037917</v>
+        <v>7037850</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1963,12 +1963,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1978,7 +1978,7 @@
         <v>129243523</v>
       </c>
       <c r="B14" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>129254208</v>
       </c>
       <c r="B15" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2224,68 +2224,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129243687</v>
+        <v>129254211</v>
       </c>
       <c r="B16" t="n">
-        <v>98676</v>
+        <v>57727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>486517</v>
+        <v>486582</v>
       </c>
       <c r="R16" t="n">
-        <v>7037922</v>
+        <v>7037881</v>
       </c>
       <c r="S16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2312,24 +2292,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>15:26</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>15:26</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Minst 120 plantor och 1 fröställning inom ca 1 m2 yta  intill en naturvårdsnitslad björk.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2338,34 +2308,28 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129254211</v>
+        <v>129254221</v>
       </c>
       <c r="B17" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2397,10 +2361,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>486582</v>
+        <v>486595</v>
       </c>
       <c r="R17" t="n">
-        <v>7037881</v>
+        <v>7038075</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2464,48 +2428,68 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129254221</v>
+        <v>129243687</v>
       </c>
       <c r="B18" t="n">
-        <v>57725</v>
+        <v>98678</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>486595</v>
+        <v>486517</v>
       </c>
       <c r="R18" t="n">
-        <v>7038075</v>
+        <v>7037922</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2532,14 +2516,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Minst 120 plantor och 1 fröställning inom ca 1 m2 yta  intill en naturvårdsnitslad björk.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2548,18 +2542,24 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2569,7 +2569,7 @@
         <v>129254199</v>
       </c>
       <c r="B19" t="n">
-        <v>83005</v>
+        <v>83007</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2663,10 +2663,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129242968</v>
+        <v>129254216</v>
       </c>
       <c r="B20" t="n">
-        <v>79039</v>
+        <v>57727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2674,37 +2674,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>486617</v>
+        <v>486478</v>
       </c>
       <c r="R20" t="n">
-        <v>7037991</v>
+        <v>7037962</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2731,19 +2731,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>14:51</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>14:51</t>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2754,41 +2749,26 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129254216</v>
+        <v>129242968</v>
       </c>
       <c r="B21" t="n">
-        <v>57725</v>
+        <v>79041</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2796,37 +2776,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>486478</v>
+        <v>486617</v>
       </c>
       <c r="R21" t="n">
-        <v>7037962</v>
+        <v>7037991</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2853,14 +2833,19 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2871,16 +2856,31 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2890,7 +2890,7 @@
         <v>129254228</v>
       </c>
       <c r="B22" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2984,10 +2984,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129254222</v>
+        <v>129254210</v>
       </c>
       <c r="B23" t="n">
-        <v>57885</v>
+        <v>57727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2995,50 +2995,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>486607</v>
+        <v>486650</v>
       </c>
       <c r="R23" t="n">
-        <v>7038047</v>
+        <v>7037866</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3071,6 +3055,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3097,10 +3086,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129254210</v>
+        <v>129254222</v>
       </c>
       <c r="B24" t="n">
-        <v>57725</v>
+        <v>57887</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3108,34 +3097,50 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>486650</v>
+        <v>486607</v>
       </c>
       <c r="R24" t="n">
-        <v>7037866</v>
+        <v>7038047</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3168,11 +3173,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3202,7 +3202,7 @@
         <v>129254212</v>
       </c>
       <c r="B25" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3301,10 +3301,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129254874</v>
+        <v>129244388</v>
       </c>
       <c r="B26" t="n">
-        <v>57725</v>
+        <v>79041</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3312,34 +3312,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>486550</v>
+        <v>486782</v>
       </c>
       <c r="R26" t="n">
-        <v>7037929</v>
+        <v>7037877</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3369,14 +3369,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3387,26 +3397,31 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129254219</v>
+        <v>129254874</v>
       </c>
       <c r="B27" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3438,10 +3453,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>486543</v>
+        <v>486550</v>
       </c>
       <c r="R27" t="n">
-        <v>7037939</v>
+        <v>7037929</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3478,7 +3493,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3493,22 +3508,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129244388</v>
+        <v>129254219</v>
       </c>
       <c r="B28" t="n">
-        <v>79039</v>
+        <v>57727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3516,34 +3531,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>486782</v>
+        <v>486543</v>
       </c>
       <c r="R28" t="n">
-        <v>7037877</v>
+        <v>7037939</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3573,24 +3588,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>15:53</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>15:53</t>
-        </is>
-      </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3601,31 +3606,26 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129241899</v>
+        <v>129254876</v>
       </c>
       <c r="B29" t="n">
-        <v>79039</v>
+        <v>57727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3633,34 +3633,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>486803</v>
+        <v>486409</v>
       </c>
       <c r="R29" t="n">
-        <v>7037939</v>
+        <v>7037957</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3690,24 +3690,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3718,36 +3708,16 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3757,7 +3727,7 @@
         <v>129254201</v>
       </c>
       <c r="B30" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3856,10 +3826,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129254876</v>
+        <v>129241899</v>
       </c>
       <c r="B31" t="n">
-        <v>57725</v>
+        <v>79041</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3867,34 +3837,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>486409</v>
+        <v>486803</v>
       </c>
       <c r="R31" t="n">
-        <v>7037957</v>
+        <v>7037939</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3924,14 +3894,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3942,16 +3922,36 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -3961,7 +3961,7 @@
         <v>129254873</v>
       </c>
       <c r="B32" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         <v>129254877</v>
       </c>
       <c r="B33" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4162,10 +4162,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129254204</v>
+        <v>129254202</v>
       </c>
       <c r="B34" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4197,10 +4197,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>486767</v>
+        <v>486780</v>
       </c>
       <c r="R34" t="n">
-        <v>7037800</v>
+        <v>7037796</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4237,7 +4237,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4264,10 +4264,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129254202</v>
+        <v>129254203</v>
       </c>
       <c r="B35" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4299,10 +4299,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>486780</v>
+        <v>486775</v>
       </c>
       <c r="R35" t="n">
-        <v>7037796</v>
+        <v>7037792</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4366,10 +4366,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129254207</v>
+        <v>129254204</v>
       </c>
       <c r="B36" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4401,10 +4401,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>486743</v>
+        <v>486767</v>
       </c>
       <c r="R36" t="n">
-        <v>7037808</v>
+        <v>7037800</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4468,10 +4468,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129254203</v>
+        <v>129254207</v>
       </c>
       <c r="B37" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4503,10 +4503,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>486775</v>
+        <v>486743</v>
       </c>
       <c r="R37" t="n">
-        <v>7037792</v>
+        <v>7037808</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4573,7 +4573,7 @@
         <v>129254217</v>
       </c>
       <c r="B38" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         <v>129244231</v>
       </c>
       <c r="B39" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4787,7 +4787,7 @@
         <v>129254226</v>
       </c>
       <c r="B40" t="n">
-        <v>78052</v>
+        <v>78054</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4881,48 +4881,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129243863</v>
+        <v>129254225</v>
       </c>
       <c r="B41" t="n">
-        <v>79039</v>
+        <v>80050</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>486663</v>
+        <v>486624</v>
       </c>
       <c r="R41" t="n">
-        <v>7037905</v>
+        <v>7038036</v>
       </c>
       <c r="S41" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4949,26 +4949,11 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Långväxta bålar, på flera granar.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -4977,51 +4962,26 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129243061</v>
+        <v>129254879</v>
       </c>
       <c r="B42" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5047,26 +5007,16 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>486568</v>
+        <v>486552</v>
       </c>
       <c r="R42" t="n">
-        <v>7037962</v>
+        <v>7037942</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5096,24 +5046,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5124,51 +5064,26 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129254230</v>
+        <v>129254872</v>
       </c>
       <c r="B43" t="n">
-        <v>82871</v>
+        <v>57727</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5176,21 +5091,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5200,10 +5115,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>486609</v>
+        <v>486715</v>
       </c>
       <c r="R43" t="n">
-        <v>7038052</v>
+        <v>7037924</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5238,6 +5153,11 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5250,44 +5170,44 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129254225</v>
+        <v>129254230</v>
       </c>
       <c r="B44" t="n">
-        <v>80048</v>
+        <v>82873</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6456</v>
+        <v>1312</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5297,10 +5217,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>486624</v>
+        <v>486609</v>
       </c>
       <c r="R44" t="n">
-        <v>7038036</v>
+        <v>7038052</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5359,10 +5279,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129254879</v>
+        <v>129243863</v>
       </c>
       <c r="B45" t="n">
-        <v>57725</v>
+        <v>79041</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5370,37 +5290,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>486552</v>
+        <v>486663</v>
       </c>
       <c r="R45" t="n">
-        <v>7037942</v>
+        <v>7037905</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5427,14 +5347,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Långväxta bålar, på flera granar.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5445,26 +5375,51 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129254872</v>
+        <v>129243061</v>
       </c>
       <c r="B46" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5490,16 +5445,26 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>486715</v>
+        <v>486568</v>
       </c>
       <c r="R46" t="n">
-        <v>7037924</v>
+        <v>7037962</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5529,14 +5494,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5547,16 +5522,41 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5566,7 +5566,7 @@
         <v>129254227</v>
       </c>
       <c r="B47" t="n">
-        <v>91536</v>
+        <v>91538</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5663,7 +5663,7 @@
         <v>129254231</v>
       </c>
       <c r="B48" t="n">
-        <v>88937</v>
+        <v>88939</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
         <v>129254196</v>
       </c>
       <c r="B49" t="n">
-        <v>83005</v>
+        <v>83007</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>129254224</v>
       </c>
       <c r="B50" t="n">
-        <v>80048</v>
+        <v>80050</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5954,7 +5954,7 @@
         <v>129254214</v>
       </c>
       <c r="B51" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6056,7 +6056,7 @@
         <v>129243695</v>
       </c>
       <c r="B52" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         <v>129254229</v>
       </c>
       <c r="B53" t="n">
-        <v>82871</v>
+        <v>82873</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6260,7 +6260,7 @@
         <v>129254213</v>
       </c>
       <c r="B54" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>129243772</v>
       </c>
       <c r="B55" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6494,7 +6494,7 @@
         <v>129254878</v>
       </c>
       <c r="B56" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 39541-2025 artfynd.xlsx
+++ b/artfynd/A 39541-2025 artfynd.xlsx
@@ -890,7 +890,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129254875</v>
+        <v>129254218</v>
       </c>
       <c r="B4" t="n">
         <v>57727</v>
@@ -925,10 +925,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486429</v>
+        <v>486524</v>
       </c>
       <c r="R4" t="n">
-        <v>7037954</v>
+        <v>7037965</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,7 +965,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -980,19 +980,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129254218</v>
+        <v>129254875</v>
       </c>
       <c r="B5" t="n">
         <v>57727</v>
@@ -1027,10 +1027,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>486524</v>
+        <v>486429</v>
       </c>
       <c r="R5" t="n">
-        <v>7037965</v>
+        <v>7037954</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1082,12 +1082,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1567,7 +1567,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129254205</v>
+        <v>129254871</v>
       </c>
       <c r="B10" t="n">
         <v>57727</v>
@@ -1602,10 +1602,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>486752</v>
+        <v>486833</v>
       </c>
       <c r="R10" t="n">
-        <v>7037802</v>
+        <v>7037850</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1642,7 +1642,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1657,19 +1657,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129254220</v>
+        <v>129254205</v>
       </c>
       <c r="B11" t="n">
         <v>57727</v>
@@ -1704,10 +1704,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>486583</v>
+        <v>486752</v>
       </c>
       <c r="R11" t="n">
-        <v>7038073</v>
+        <v>7037802</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1771,7 +1771,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129254215</v>
+        <v>129254220</v>
       </c>
       <c r="B12" t="n">
         <v>57727</v>
@@ -1806,10 +1806,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>486524</v>
+        <v>486583</v>
       </c>
       <c r="R12" t="n">
-        <v>7037917</v>
+        <v>7038073</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1873,7 +1873,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129254871</v>
+        <v>129254215</v>
       </c>
       <c r="B13" t="n">
         <v>57727</v>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>486833</v>
+        <v>486524</v>
       </c>
       <c r="R13" t="n">
-        <v>7037850</v>
+        <v>7037917</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1963,12 +1963,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2887,10 +2887,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129254228</v>
+        <v>129254210</v>
       </c>
       <c r="B22" t="n">
-        <v>91560</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2898,21 +2898,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2922,10 +2922,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>486556</v>
+        <v>486650</v>
       </c>
       <c r="R22" t="n">
-        <v>7037879</v>
+        <v>7037866</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2958,6 +2958,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2984,10 +2989,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129254210</v>
+        <v>129254222</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2995,34 +3000,50 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>486650</v>
+        <v>486607</v>
       </c>
       <c r="R23" t="n">
-        <v>7037866</v>
+        <v>7038047</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3055,11 +3076,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3086,10 +3102,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129254222</v>
+        <v>129254228</v>
       </c>
       <c r="B24" t="n">
-        <v>57887</v>
+        <v>91560</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3097,50 +3113,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>486607</v>
+        <v>486556</v>
       </c>
       <c r="R24" t="n">
-        <v>7038047</v>
+        <v>7037879</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3622,10 +3622,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129254876</v>
+        <v>129241899</v>
       </c>
       <c r="B29" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3633,34 +3633,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>486409</v>
+        <v>486803</v>
       </c>
       <c r="R29" t="n">
-        <v>7037957</v>
+        <v>7037939</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3690,14 +3690,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3708,16 +3718,36 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3826,10 +3856,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129241899</v>
+        <v>129254876</v>
       </c>
       <c r="B31" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3837,34 +3867,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>486803</v>
+        <v>486409</v>
       </c>
       <c r="R31" t="n">
-        <v>7037939</v>
+        <v>7037957</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3894,24 +3924,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3922,36 +3942,16 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4162,7 +4162,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129254202</v>
+        <v>129254204</v>
       </c>
       <c r="B34" t="n">
         <v>57727</v>
@@ -4197,10 +4197,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>486780</v>
+        <v>486767</v>
       </c>
       <c r="R34" t="n">
-        <v>7037796</v>
+        <v>7037800</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4237,7 +4237,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4264,7 +4264,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129254203</v>
+        <v>129254202</v>
       </c>
       <c r="B35" t="n">
         <v>57727</v>
@@ -4299,10 +4299,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>486775</v>
+        <v>486780</v>
       </c>
       <c r="R35" t="n">
-        <v>7037792</v>
+        <v>7037796</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4366,7 +4366,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129254204</v>
+        <v>129254207</v>
       </c>
       <c r="B36" t="n">
         <v>57727</v>
@@ -4401,10 +4401,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>486767</v>
+        <v>486743</v>
       </c>
       <c r="R36" t="n">
-        <v>7037800</v>
+        <v>7037808</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4468,7 +4468,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129254207</v>
+        <v>129254203</v>
       </c>
       <c r="B37" t="n">
         <v>57727</v>
@@ -4503,10 +4503,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>486743</v>
+        <v>486775</v>
       </c>
       <c r="R37" t="n">
-        <v>7037808</v>
+        <v>7037792</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4672,10 +4672,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129244231</v>
+        <v>129254226</v>
       </c>
       <c r="B39" t="n">
-        <v>79041</v>
+        <v>78054</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4683,37 +4683,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>486671</v>
+        <v>486585</v>
       </c>
       <c r="R39" t="n">
-        <v>7037887</v>
+        <v>7038070</v>
       </c>
       <c r="S39" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4740,24 +4740,9 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4772,22 +4757,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129254226</v>
+        <v>129244231</v>
       </c>
       <c r="B40" t="n">
-        <v>78054</v>
+        <v>79041</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4795,37 +4780,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>486585</v>
+        <v>486671</v>
       </c>
       <c r="R40" t="n">
-        <v>7038070</v>
+        <v>7037887</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4852,9 +4837,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4869,44 +4869,44 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129254225</v>
+        <v>129254230</v>
       </c>
       <c r="B41" t="n">
-        <v>80050</v>
+        <v>82873</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6456</v>
+        <v>1312</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>486624</v>
+        <v>486609</v>
       </c>
       <c r="R41" t="n">
-        <v>7038036</v>
+        <v>7038052</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4978,32 +4978,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129254879</v>
+        <v>129254225</v>
       </c>
       <c r="B42" t="n">
-        <v>57727</v>
+        <v>80050</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5013,10 +5013,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>486552</v>
+        <v>486624</v>
       </c>
       <c r="R42" t="n">
-        <v>7037942</v>
+        <v>7038036</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5051,11 +5051,6 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5068,22 +5063,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129254872</v>
+        <v>129243863</v>
       </c>
       <c r="B43" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5091,37 +5086,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>486715</v>
+        <v>486663</v>
       </c>
       <c r="R43" t="n">
-        <v>7037924</v>
+        <v>7037905</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5148,14 +5143,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Långväxta bålar, på flera granar.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5166,26 +5171,51 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129254230</v>
+        <v>129243061</v>
       </c>
       <c r="B44" t="n">
-        <v>82873</v>
+        <v>57727</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5193,34 +5223,44 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>486609</v>
+        <v>486568</v>
       </c>
       <c r="R44" t="n">
-        <v>7038052</v>
+        <v>7037962</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5250,11 +5290,26 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5263,26 +5318,51 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129243863</v>
+        <v>129254879</v>
       </c>
       <c r="B45" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5290,37 +5370,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>486663</v>
+        <v>486552</v>
       </c>
       <c r="R45" t="n">
-        <v>7037905</v>
+        <v>7037942</v>
       </c>
       <c r="S45" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5347,24 +5427,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Långväxta bålar, på flera granar.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5375,48 +5445,23 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129243061</v>
+        <v>129254872</v>
       </c>
       <c r="B46" t="n">
         <v>57727</v>
@@ -5445,26 +5490,16 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>486568</v>
+        <v>486715</v>
       </c>
       <c r="R46" t="n">
-        <v>7037962</v>
+        <v>7037924</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5494,24 +5529,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5522,41 +5547,16 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5660,10 +5660,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129254231</v>
+        <v>129254196</v>
       </c>
       <c r="B48" t="n">
-        <v>88939</v>
+        <v>83007</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5671,21 +5671,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>510</v>
+        <v>6440</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5695,10 +5695,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>486615</v>
+        <v>486582</v>
       </c>
       <c r="R48" t="n">
-        <v>7037875</v>
+        <v>7038072</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5757,32 +5757,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129254196</v>
+        <v>129254224</v>
       </c>
       <c r="B49" t="n">
-        <v>83007</v>
+        <v>80050</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6440</v>
+        <v>6456</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5792,10 +5792,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>486582</v>
+        <v>486599</v>
       </c>
       <c r="R49" t="n">
-        <v>7038072</v>
+        <v>7038068</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5854,32 +5854,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129254224</v>
+        <v>129254214</v>
       </c>
       <c r="B50" t="n">
-        <v>80050</v>
+        <v>57727</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5889,10 +5889,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>486599</v>
+        <v>486551</v>
       </c>
       <c r="R50" t="n">
-        <v>7038068</v>
+        <v>7037889</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5925,6 +5925,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5951,10 +5956,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129254214</v>
+        <v>129254231</v>
       </c>
       <c r="B51" t="n">
-        <v>57727</v>
+        <v>88939</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5962,21 +5967,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5986,10 +5991,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>486551</v>
+        <v>486615</v>
       </c>
       <c r="R51" t="n">
-        <v>7037889</v>
+        <v>7037875</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6022,11 +6027,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6359,10 +6359,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129243772</v>
+        <v>129254878</v>
       </c>
       <c r="B55" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6370,37 +6370,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>486608</v>
+        <v>486553</v>
       </c>
       <c r="R55" t="n">
-        <v>7037908</v>
+        <v>7037937</v>
       </c>
       <c r="S55" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6427,19 +6427,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>15:38</t>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6450,51 +6445,26 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129254878</v>
+        <v>129243772</v>
       </c>
       <c r="B56" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6502,37 +6472,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>486553</v>
+        <v>486608</v>
       </c>
       <c r="R56" t="n">
-        <v>7037937</v>
+        <v>7037908</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6559,14 +6529,19 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6577,16 +6552,41 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>

--- a/artfynd/A 39541-2025 artfynd.xlsx
+++ b/artfynd/A 39541-2025 artfynd.xlsx
@@ -2663,10 +2663,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129254216</v>
+        <v>129242968</v>
       </c>
       <c r="B20" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2674,37 +2674,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>486478</v>
+        <v>486617</v>
       </c>
       <c r="R20" t="n">
-        <v>7037962</v>
+        <v>7037991</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2731,14 +2731,19 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2749,26 +2754,41 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129242968</v>
+        <v>129254216</v>
       </c>
       <c r="B21" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2776,37 +2796,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>486617</v>
+        <v>486478</v>
       </c>
       <c r="R21" t="n">
-        <v>7037991</v>
+        <v>7037962</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2833,19 +2853,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>14:51</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>14:51</t>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2856,31 +2871,16 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3622,10 +3622,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129241899</v>
+        <v>129254201</v>
       </c>
       <c r="B29" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3633,34 +3633,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>486803</v>
+        <v>486797</v>
       </c>
       <c r="R29" t="n">
-        <v>7037939</v>
+        <v>7037788</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3690,24 +3690,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3718,43 +3708,23 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129254201</v>
+        <v>129254876</v>
       </c>
       <c r="B30" t="n">
         <v>57727</v>
@@ -3789,10 +3759,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>486797</v>
+        <v>486409</v>
       </c>
       <c r="R30" t="n">
-        <v>7037788</v>
+        <v>7037957</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3829,7 +3799,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3844,22 +3814,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129254876</v>
+        <v>129241899</v>
       </c>
       <c r="B31" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3867,34 +3837,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>486409</v>
+        <v>486803</v>
       </c>
       <c r="R31" t="n">
-        <v>7037957</v>
+        <v>7037939</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3924,14 +3894,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3942,16 +3922,36 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4672,10 +4672,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129254226</v>
+        <v>129244231</v>
       </c>
       <c r="B39" t="n">
-        <v>78054</v>
+        <v>79041</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4683,37 +4683,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>486585</v>
+        <v>486671</v>
       </c>
       <c r="R39" t="n">
-        <v>7038070</v>
+        <v>7037887</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4740,9 +4740,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4757,22 +4772,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129244231</v>
+        <v>129254226</v>
       </c>
       <c r="B40" t="n">
-        <v>79041</v>
+        <v>78054</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4780,37 +4795,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>486671</v>
+        <v>486585</v>
       </c>
       <c r="R40" t="n">
-        <v>7037887</v>
+        <v>7038070</v>
       </c>
       <c r="S40" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4837,24 +4852,9 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4869,12 +4869,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5854,10 +5854,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129254214</v>
+        <v>129254231</v>
       </c>
       <c r="B50" t="n">
-        <v>57727</v>
+        <v>88939</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5865,21 +5865,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5889,10 +5889,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>486551</v>
+        <v>486615</v>
       </c>
       <c r="R50" t="n">
-        <v>7037889</v>
+        <v>7037875</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5925,11 +5925,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5956,10 +5951,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129254231</v>
+        <v>129254214</v>
       </c>
       <c r="B51" t="n">
-        <v>88939</v>
+        <v>57727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5967,21 +5962,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5991,10 +5986,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>486615</v>
+        <v>486551</v>
       </c>
       <c r="R51" t="n">
-        <v>7037875</v>
+        <v>7037889</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6027,6 +6022,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6359,10 +6359,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129254878</v>
+        <v>129243772</v>
       </c>
       <c r="B55" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6370,37 +6370,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>486553</v>
+        <v>486608</v>
       </c>
       <c r="R55" t="n">
-        <v>7037937</v>
+        <v>7037908</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6427,14 +6427,19 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6445,26 +6450,51 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129243772</v>
+        <v>129254878</v>
       </c>
       <c r="B56" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6472,37 +6502,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>486608</v>
+        <v>486553</v>
       </c>
       <c r="R56" t="n">
-        <v>7037908</v>
+        <v>7037937</v>
       </c>
       <c r="S56" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6529,19 +6559,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>15:38</t>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6552,41 +6577,16 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>

--- a/artfynd/A 39541-2025 artfynd.xlsx
+++ b/artfynd/A 39541-2025 artfynd.xlsx
@@ -781,27 +781,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129254223</v>
+        <v>129254218</v>
       </c>
       <c r="B3" t="n">
-        <v>57568</v>
+        <v>57727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -809,29 +809,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>486737</v>
+        <v>486524</v>
       </c>
       <c r="R3" t="n">
-        <v>7037835</v>
+        <v>7037965</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,6 +852,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,7 +883,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129254218</v>
+        <v>129254875</v>
       </c>
       <c r="B4" t="n">
         <v>57727</v>
@@ -925,10 +918,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486524</v>
+        <v>486429</v>
       </c>
       <c r="R4" t="n">
-        <v>7037965</v>
+        <v>7037954</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,7 +958,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -980,19 +973,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129254875</v>
+        <v>129254206</v>
       </c>
       <c r="B5" t="n">
         <v>57727</v>
@@ -1027,10 +1020,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>486429</v>
+        <v>486751</v>
       </c>
       <c r="R5" t="n">
-        <v>7037954</v>
+        <v>7037804</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,7 +1060,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1082,39 +1075,39 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129254206</v>
+        <v>129254223</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>57568</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1122,17 +1115,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>486751</v>
+        <v>486737</v>
       </c>
       <c r="R6" t="n">
-        <v>7037804</v>
+        <v>7037835</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,11 +1170,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -2224,48 +2224,68 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129254211</v>
+        <v>129243687</v>
       </c>
       <c r="B16" t="n">
-        <v>57727</v>
+        <v>98704</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>486582</v>
+        <v>486517</v>
       </c>
       <c r="R16" t="n">
-        <v>7037881</v>
+        <v>7037922</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2292,14 +2312,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Minst 120 plantor och 1 fröställning inom ca 1 m2 yta  intill en naturvårdsnitslad björk.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2308,25 +2338,31 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129254221</v>
+        <v>129254211</v>
       </c>
       <c r="B17" t="n">
         <v>57727</v>
@@ -2361,10 +2397,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>486595</v>
+        <v>486582</v>
       </c>
       <c r="R17" t="n">
-        <v>7038075</v>
+        <v>7037881</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2428,68 +2464,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129243687</v>
+        <v>129254221</v>
       </c>
       <c r="B18" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>486517</v>
+        <v>486595</v>
       </c>
       <c r="R18" t="n">
-        <v>7037922</v>
+        <v>7038075</v>
       </c>
       <c r="S18" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2516,24 +2532,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>15:26</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>15:26</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Minst 120 plantor och 1 fröställning inom ca 1 m2 yta  intill en naturvårdsnitslad björk.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2542,24 +2548,18 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2887,10 +2887,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129254210</v>
+        <v>129254228</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>91558</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2898,21 +2898,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2922,10 +2922,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>486650</v>
+        <v>486556</v>
       </c>
       <c r="R22" t="n">
-        <v>7037866</v>
+        <v>7037879</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2958,11 +2958,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2989,10 +2984,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129254222</v>
+        <v>129254210</v>
       </c>
       <c r="B23" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3000,50 +2995,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>486607</v>
+        <v>486650</v>
       </c>
       <c r="R23" t="n">
-        <v>7038047</v>
+        <v>7037866</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3076,6 +3055,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3102,10 +3086,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129254228</v>
+        <v>129254222</v>
       </c>
       <c r="B24" t="n">
-        <v>91560</v>
+        <v>57887</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3113,34 +3097,50 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>486556</v>
+        <v>486607</v>
       </c>
       <c r="R24" t="n">
-        <v>7037879</v>
+        <v>7038047</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3301,10 +3301,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129244388</v>
+        <v>129254874</v>
       </c>
       <c r="B26" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3312,34 +3312,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>486782</v>
+        <v>486550</v>
       </c>
       <c r="R26" t="n">
-        <v>7037877</v>
+        <v>7037929</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3369,24 +3369,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>15:53</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>15:53</t>
-        </is>
-      </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3397,28 +3387,23 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129254874</v>
+        <v>129254219</v>
       </c>
       <c r="B27" t="n">
         <v>57727</v>
@@ -3453,10 +3438,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>486550</v>
+        <v>486543</v>
       </c>
       <c r="R27" t="n">
-        <v>7037929</v>
+        <v>7037939</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3493,7 +3478,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3508,22 +3493,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129254219</v>
+        <v>129244388</v>
       </c>
       <c r="B28" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3531,34 +3516,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>486543</v>
+        <v>486782</v>
       </c>
       <c r="R28" t="n">
-        <v>7037939</v>
+        <v>7037877</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3588,14 +3573,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3606,16 +3601,21 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -4672,10 +4672,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129244231</v>
+        <v>129254226</v>
       </c>
       <c r="B39" t="n">
-        <v>79041</v>
+        <v>78054</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4683,37 +4683,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>486671</v>
+        <v>486585</v>
       </c>
       <c r="R39" t="n">
-        <v>7037887</v>
+        <v>7038070</v>
       </c>
       <c r="S39" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4740,24 +4740,9 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4772,22 +4757,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129254226</v>
+        <v>129244231</v>
       </c>
       <c r="B40" t="n">
-        <v>78054</v>
+        <v>79041</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4795,37 +4780,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>486585</v>
+        <v>486671</v>
       </c>
       <c r="R40" t="n">
-        <v>7038070</v>
+        <v>7037887</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4852,9 +4837,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4869,22 +4869,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129254230</v>
+        <v>129243863</v>
       </c>
       <c r="B41" t="n">
-        <v>82873</v>
+        <v>79041</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4892,37 +4892,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>486609</v>
+        <v>486663</v>
       </c>
       <c r="R41" t="n">
-        <v>7038052</v>
+        <v>7037905</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4949,11 +4949,26 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Långväxta bålar, på flera granar.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -4962,16 +4977,41 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5075,10 +5115,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129243863</v>
+        <v>129254879</v>
       </c>
       <c r="B43" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5086,37 +5126,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>486663</v>
+        <v>486552</v>
       </c>
       <c r="R43" t="n">
-        <v>7037905</v>
+        <v>7037942</v>
       </c>
       <c r="S43" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5143,24 +5183,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Långväxta bålar, på flera granar.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5171,48 +5201,23 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129243061</v>
+        <v>129254872</v>
       </c>
       <c r="B44" t="n">
         <v>57727</v>
@@ -5241,26 +5246,16 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>486568</v>
+        <v>486715</v>
       </c>
       <c r="R44" t="n">
-        <v>7037962</v>
+        <v>7037924</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5290,24 +5285,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5318,51 +5303,26 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129254879</v>
+        <v>129254230</v>
       </c>
       <c r="B45" t="n">
-        <v>57727</v>
+        <v>82873</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5370,21 +5330,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5394,10 +5354,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>486552</v>
+        <v>486609</v>
       </c>
       <c r="R45" t="n">
-        <v>7037942</v>
+        <v>7038052</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5432,11 +5392,6 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5449,19 +5404,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129254872</v>
+        <v>129243061</v>
       </c>
       <c r="B46" t="n">
         <v>57727</v>
@@ -5490,16 +5445,26 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>486715</v>
+        <v>486568</v>
       </c>
       <c r="R46" t="n">
-        <v>7037924</v>
+        <v>7037962</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5529,14 +5494,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5547,16 +5522,41 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5566,7 +5566,7 @@
         <v>129254227</v>
       </c>
       <c r="B47" t="n">
-        <v>91538</v>
+        <v>91536</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5660,10 +5660,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129254196</v>
+        <v>129254231</v>
       </c>
       <c r="B48" t="n">
-        <v>83007</v>
+        <v>88940</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5671,21 +5671,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6440</v>
+        <v>510</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5695,10 +5695,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>486582</v>
+        <v>486615</v>
       </c>
       <c r="R48" t="n">
-        <v>7038072</v>
+        <v>7037875</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5757,32 +5757,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129254224</v>
+        <v>129254214</v>
       </c>
       <c r="B49" t="n">
-        <v>80050</v>
+        <v>57727</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5792,10 +5792,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>486599</v>
+        <v>486551</v>
       </c>
       <c r="R49" t="n">
-        <v>7038068</v>
+        <v>7037889</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5828,6 +5828,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5854,10 +5859,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129254231</v>
+        <v>129254196</v>
       </c>
       <c r="B50" t="n">
-        <v>88939</v>
+        <v>83007</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5865,21 +5870,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>510</v>
+        <v>6440</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5889,10 +5894,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>486615</v>
+        <v>486582</v>
       </c>
       <c r="R50" t="n">
-        <v>7037875</v>
+        <v>7038072</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5951,32 +5956,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129254214</v>
+        <v>129254224</v>
       </c>
       <c r="B51" t="n">
-        <v>57727</v>
+        <v>80050</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5986,10 +5991,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>486551</v>
+        <v>486599</v>
       </c>
       <c r="R51" t="n">
-        <v>7037889</v>
+        <v>7038068</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6022,11 +6027,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6160,10 +6160,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129254229</v>
+        <v>129254213</v>
       </c>
       <c r="B53" t="n">
-        <v>82873</v>
+        <v>57727</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6171,21 +6171,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6195,10 +6195,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>486611</v>
+        <v>486551</v>
       </c>
       <c r="R53" t="n">
-        <v>7038042</v>
+        <v>7037886</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6231,6 +6231,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6257,10 +6262,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129254213</v>
+        <v>129254229</v>
       </c>
       <c r="B54" t="n">
-        <v>57727</v>
+        <v>82873</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6268,21 +6273,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6292,10 +6297,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>486551</v>
+        <v>486611</v>
       </c>
       <c r="R54" t="n">
-        <v>7037886</v>
+        <v>7038042</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6328,11 +6333,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6359,10 +6359,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129243772</v>
+        <v>129254878</v>
       </c>
       <c r="B55" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6370,37 +6370,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>486608</v>
+        <v>486553</v>
       </c>
       <c r="R55" t="n">
-        <v>7037908</v>
+        <v>7037937</v>
       </c>
       <c r="S55" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6427,19 +6427,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>15:38</t>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6450,51 +6445,26 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129254878</v>
+        <v>129243772</v>
       </c>
       <c r="B56" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6502,37 +6472,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>486553</v>
+        <v>486608</v>
       </c>
       <c r="R56" t="n">
-        <v>7037937</v>
+        <v>7037908</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6559,14 +6529,19 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6577,16 +6552,41 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>

--- a/artfynd/A 39541-2025 artfynd.xlsx
+++ b/artfynd/A 39541-2025 artfynd.xlsx
@@ -883,27 +883,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129254875</v>
+        <v>129254223</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>57568</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -911,17 +911,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486429</v>
+        <v>486737</v>
       </c>
       <c r="R4" t="n">
-        <v>7037954</v>
+        <v>7037835</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -956,11 +968,6 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -973,22 +980,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129254206</v>
+        <v>129241859</v>
       </c>
       <c r="B5" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -996,37 +1003,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Tomasbodarna, Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>486751</v>
+        <v>486860</v>
       </c>
       <c r="R5" t="n">
-        <v>7037804</v>
+        <v>7037938</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1053,14 +1060,19 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,76 +1083,69 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129254223</v>
+        <v>129242509</v>
       </c>
       <c r="B6" t="n">
-        <v>57568</v>
+        <v>79041</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102621</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>486737</v>
+        <v>486672</v>
       </c>
       <c r="R6" t="n">
-        <v>7037835</v>
+        <v>7037952</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1167,11 +1172,21 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1180,26 +1195,31 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129241859</v>
+        <v>129242015</v>
       </c>
       <c r="B7" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1207,37 +1227,47 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tomasbodarna, Tomasbodarna, Jmt</t>
+          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>486860</v>
+        <v>486782</v>
       </c>
       <c r="R7" t="n">
-        <v>7037938</v>
+        <v>7037909</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1266,7 +1296,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1276,7 +1306,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1290,7 +1325,27 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1308,10 +1363,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129242509</v>
+        <v>129254875</v>
       </c>
       <c r="B8" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1319,37 +1374,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>486672</v>
+        <v>486429</v>
       </c>
       <c r="R8" t="n">
-        <v>7037952</v>
+        <v>7037954</v>
       </c>
       <c r="S8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1376,19 +1431,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>14:42</t>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1399,28 +1449,23 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129242015</v>
+        <v>129254206</v>
       </c>
       <c r="B9" t="n">
         <v>57727</v>
@@ -1449,29 +1494,19 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>486782</v>
+        <v>486751</v>
       </c>
       <c r="R9" t="n">
-        <v>7037909</v>
+        <v>7037804</v>
       </c>
       <c r="S9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1498,24 +1533,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,48 +1551,23 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129254871</v>
+        <v>129254215</v>
       </c>
       <c r="B10" t="n">
         <v>57727</v>
@@ -1602,10 +1602,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>486833</v>
+        <v>486524</v>
       </c>
       <c r="R10" t="n">
-        <v>7037850</v>
+        <v>7037917</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1642,7 +1642,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1657,19 +1657,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129254205</v>
+        <v>129243523</v>
       </c>
       <c r="B11" t="n">
         <v>57727</v>
@@ -1698,19 +1698,29 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>486752</v>
+        <v>486472</v>
       </c>
       <c r="R11" t="n">
-        <v>7037802</v>
+        <v>7037927</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1737,14 +1747,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack, äldre, på stambasen av en hyfsat grov gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1755,23 +1775,48 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129254220</v>
+        <v>129254871</v>
       </c>
       <c r="B12" t="n">
         <v>57727</v>
@@ -1806,10 +1851,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>486583</v>
+        <v>486833</v>
       </c>
       <c r="R12" t="n">
-        <v>7038073</v>
+        <v>7037850</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1846,7 +1891,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1861,19 +1906,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129254215</v>
+        <v>129254205</v>
       </c>
       <c r="B13" t="n">
         <v>57727</v>
@@ -1908,10 +1953,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>486524</v>
+        <v>486752</v>
       </c>
       <c r="R13" t="n">
-        <v>7037917</v>
+        <v>7037802</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1975,7 +2020,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129243523</v>
+        <v>129254220</v>
       </c>
       <c r="B14" t="n">
         <v>57727</v>
@@ -2004,29 +2049,19 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>486472</v>
+        <v>486583</v>
       </c>
       <c r="R14" t="n">
-        <v>7037927</v>
+        <v>7038073</v>
       </c>
       <c r="S14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2053,24 +2088,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>15:21</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>15:21</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en hyfsat grov gran.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2081,41 +2106,16 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2224,68 +2224,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129243687</v>
+        <v>129254211</v>
       </c>
       <c r="B16" t="n">
-        <v>98704</v>
+        <v>57727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>486517</v>
+        <v>486582</v>
       </c>
       <c r="R16" t="n">
-        <v>7037922</v>
+        <v>7037881</v>
       </c>
       <c r="S16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2312,24 +2292,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>15:26</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>15:26</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Minst 120 plantor och 1 fröställning inom ca 1 m2 yta  intill en naturvårdsnitslad björk.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2338,31 +2308,25 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129254211</v>
+        <v>129254221</v>
       </c>
       <c r="B17" t="n">
         <v>57727</v>
@@ -2397,10 +2361,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>486582</v>
+        <v>486595</v>
       </c>
       <c r="R17" t="n">
-        <v>7037881</v>
+        <v>7038075</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2464,48 +2428,68 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129254221</v>
+        <v>129243687</v>
       </c>
       <c r="B18" t="n">
-        <v>57727</v>
+        <v>98705</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>486595</v>
+        <v>486517</v>
       </c>
       <c r="R18" t="n">
-        <v>7038075</v>
+        <v>7037922</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2532,14 +2516,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Minst 120 plantor och 1 fröställning inom ca 1 m2 yta  intill en naturvårdsnitslad björk.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2548,18 +2542,24 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2663,10 +2663,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129242968</v>
+        <v>129254216</v>
       </c>
       <c r="B20" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2674,37 +2674,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>486617</v>
+        <v>486478</v>
       </c>
       <c r="R20" t="n">
-        <v>7037991</v>
+        <v>7037962</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2731,19 +2731,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>14:51</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>14:51</t>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2754,41 +2749,26 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129254216</v>
+        <v>129242968</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2796,37 +2776,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>486478</v>
+        <v>486617</v>
       </c>
       <c r="R21" t="n">
-        <v>7037962</v>
+        <v>7037991</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2853,14 +2833,19 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2871,16 +2856,31 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2890,7 +2890,7 @@
         <v>129254228</v>
       </c>
       <c r="B22" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2907,14 +2907,10 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3301,10 +3297,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129254874</v>
+        <v>129244388</v>
       </c>
       <c r="B26" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3312,34 +3308,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>486550</v>
+        <v>486782</v>
       </c>
       <c r="R26" t="n">
-        <v>7037929</v>
+        <v>7037877</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3369,14 +3365,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3387,23 +3393,28 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129254219</v>
+        <v>129254874</v>
       </c>
       <c r="B27" t="n">
         <v>57727</v>
@@ -3438,10 +3449,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>486543</v>
+        <v>486550</v>
       </c>
       <c r="R27" t="n">
-        <v>7037939</v>
+        <v>7037929</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3478,7 +3489,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3493,22 +3504,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129244388</v>
+        <v>129254219</v>
       </c>
       <c r="B28" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3516,34 +3527,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>486782</v>
+        <v>486543</v>
       </c>
       <c r="R28" t="n">
-        <v>7037877</v>
+        <v>7037939</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3573,24 +3584,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>15:53</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>15:53</t>
-        </is>
-      </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3601,31 +3602,26 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129254201</v>
+        <v>129241899</v>
       </c>
       <c r="B29" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3633,34 +3629,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>486797</v>
+        <v>486803</v>
       </c>
       <c r="R29" t="n">
-        <v>7037788</v>
+        <v>7037939</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3690,14 +3686,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3708,23 +3714,43 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129254876</v>
+        <v>129254201</v>
       </c>
       <c r="B30" t="n">
         <v>57727</v>
@@ -3759,10 +3785,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>486409</v>
+        <v>486797</v>
       </c>
       <c r="R30" t="n">
-        <v>7037957</v>
+        <v>7037788</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3799,7 +3825,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3814,22 +3840,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129241899</v>
+        <v>129254876</v>
       </c>
       <c r="B31" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3837,34 +3863,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>486803</v>
+        <v>486409</v>
       </c>
       <c r="R31" t="n">
-        <v>7037939</v>
+        <v>7037957</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3894,24 +3920,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3922,36 +3938,16 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4672,10 +4668,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129254226</v>
+        <v>129244231</v>
       </c>
       <c r="B39" t="n">
-        <v>78054</v>
+        <v>79041</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4683,37 +4679,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>486585</v>
+        <v>486671</v>
       </c>
       <c r="R39" t="n">
-        <v>7038070</v>
+        <v>7037887</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4740,9 +4736,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4757,22 +4768,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129244231</v>
+        <v>129254226</v>
       </c>
       <c r="B40" t="n">
-        <v>79041</v>
+        <v>78054</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4780,37 +4791,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>486671</v>
+        <v>486585</v>
       </c>
       <c r="R40" t="n">
-        <v>7037887</v>
+        <v>7038070</v>
       </c>
       <c r="S40" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4837,24 +4848,9 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4869,60 +4865,60 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129243863</v>
+        <v>129254225</v>
       </c>
       <c r="B41" t="n">
-        <v>79041</v>
+        <v>80050</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>486663</v>
+        <v>486624</v>
       </c>
       <c r="R41" t="n">
-        <v>7037905</v>
+        <v>7038036</v>
       </c>
       <c r="S41" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4949,26 +4945,11 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Långväxta bålar, på flera granar.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -4977,73 +4958,48 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129254225</v>
+        <v>129254879</v>
       </c>
       <c r="B42" t="n">
-        <v>80050</v>
+        <v>57727</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5053,10 +5009,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>486624</v>
+        <v>486552</v>
       </c>
       <c r="R42" t="n">
-        <v>7038036</v>
+        <v>7037942</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5091,6 +5047,11 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5103,19 +5064,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129254879</v>
+        <v>129254872</v>
       </c>
       <c r="B43" t="n">
         <v>57727</v>
@@ -5150,10 +5111,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>486552</v>
+        <v>486715</v>
       </c>
       <c r="R43" t="n">
-        <v>7037942</v>
+        <v>7037924</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5217,10 +5178,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129254872</v>
+        <v>129254230</v>
       </c>
       <c r="B44" t="n">
-        <v>57727</v>
+        <v>82873</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5228,21 +5189,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5252,10 +5213,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>486715</v>
+        <v>486609</v>
       </c>
       <c r="R44" t="n">
-        <v>7037924</v>
+        <v>7038052</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5290,11 +5251,6 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5307,22 +5263,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129254230</v>
+        <v>129243863</v>
       </c>
       <c r="B45" t="n">
-        <v>82873</v>
+        <v>79041</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5330,37 +5286,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>486609</v>
+        <v>486663</v>
       </c>
       <c r="R45" t="n">
-        <v>7038052</v>
+        <v>7037905</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5387,11 +5343,26 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Långväxta bålar, på flera granar.</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5400,16 +5371,41 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5660,10 +5656,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129254231</v>
+        <v>129254196</v>
       </c>
       <c r="B48" t="n">
-        <v>88940</v>
+        <v>83007</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5671,21 +5667,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>510</v>
+        <v>6440</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5695,10 +5691,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>486615</v>
+        <v>486582</v>
       </c>
       <c r="R48" t="n">
-        <v>7037875</v>
+        <v>7038072</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5757,32 +5753,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129254214</v>
+        <v>129254224</v>
       </c>
       <c r="B49" t="n">
-        <v>57727</v>
+        <v>80050</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5792,10 +5788,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>486551</v>
+        <v>486599</v>
       </c>
       <c r="R49" t="n">
-        <v>7037889</v>
+        <v>7038068</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5828,11 +5824,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5859,10 +5850,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129254196</v>
+        <v>129254214</v>
       </c>
       <c r="B50" t="n">
-        <v>83007</v>
+        <v>57727</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5870,21 +5861,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5894,10 +5885,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>486582</v>
+        <v>486551</v>
       </c>
       <c r="R50" t="n">
-        <v>7038072</v>
+        <v>7037889</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5930,6 +5921,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5956,32 +5952,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129254224</v>
+        <v>129254231</v>
       </c>
       <c r="B51" t="n">
-        <v>80050</v>
+        <v>88940</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6456</v>
+        <v>510</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5991,10 +5987,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>486599</v>
+        <v>486615</v>
       </c>
       <c r="R51" t="n">
-        <v>7038068</v>
+        <v>7037875</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>

--- a/artfynd/A 39541-2025 artfynd.xlsx
+++ b/artfynd/A 39541-2025 artfynd.xlsx
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129254218</v>
+        <v>129242015</v>
       </c>
       <c r="B3" t="n">
         <v>57727</v>
@@ -810,19 +810,29 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>486524</v>
+        <v>486782</v>
       </c>
       <c r="R3" t="n">
-        <v>7037965</v>
+        <v>7037909</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -849,14 +859,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,76 +887,89 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129254223</v>
+        <v>129241859</v>
       </c>
       <c r="B4" t="n">
-        <v>57568</v>
+        <v>79041</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102621</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Tomasbodarna, Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486737</v>
+        <v>486860</v>
       </c>
       <c r="R4" t="n">
-        <v>7037835</v>
+        <v>7037938</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -963,11 +996,21 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -976,23 +1019,28 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129241859</v>
+        <v>129242509</v>
       </c>
       <c r="B5" t="n">
         <v>79041</v>
@@ -1023,17 +1071,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tomasbodarna, Tomasbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>486860</v>
+        <v>486672</v>
       </c>
       <c r="R5" t="n">
-        <v>7037938</v>
+        <v>7037952</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1062,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1072,7 +1120,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1104,48 +1152,60 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129242509</v>
+        <v>129254223</v>
       </c>
       <c r="B6" t="n">
-        <v>79041</v>
+        <v>57568</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>102621</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>486672</v>
+        <v>486737</v>
       </c>
       <c r="R6" t="n">
-        <v>7037952</v>
+        <v>7037835</v>
       </c>
       <c r="S6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1172,21 +1232,11 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1195,28 +1245,23 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129242015</v>
+        <v>129254218</v>
       </c>
       <c r="B7" t="n">
         <v>57727</v>
@@ -1245,29 +1290,19 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>486782</v>
+        <v>486524</v>
       </c>
       <c r="R7" t="n">
-        <v>7037909</v>
+        <v>7037965</v>
       </c>
       <c r="S7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1294,24 +1329,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1322,41 +1347,16 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1555,19 +1555,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129254215</v>
+        <v>129243523</v>
       </c>
       <c r="B10" t="n">
         <v>57727</v>
@@ -1596,19 +1596,29 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>486524</v>
+        <v>486472</v>
       </c>
       <c r="R10" t="n">
-        <v>7037917</v>
+        <v>7037927</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1635,14 +1645,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack, äldre, på stambasen av en hyfsat grov gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,23 +1673,48 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129243523</v>
+        <v>129254871</v>
       </c>
       <c r="B11" t="n">
         <v>57727</v>
@@ -1698,29 +1743,19 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>486472</v>
+        <v>486833</v>
       </c>
       <c r="R11" t="n">
-        <v>7037927</v>
+        <v>7037850</v>
       </c>
       <c r="S11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1747,24 +1782,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>15:21</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>15:21</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en hyfsat grov gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1775,48 +1800,23 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129254871</v>
+        <v>129254205</v>
       </c>
       <c r="B12" t="n">
         <v>57727</v>
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>486833</v>
+        <v>486752</v>
       </c>
       <c r="R12" t="n">
-        <v>7037850</v>
+        <v>7037802</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1906,19 +1906,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129254205</v>
+        <v>129254220</v>
       </c>
       <c r="B13" t="n">
         <v>57727</v>
@@ -1953,10 +1953,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>486752</v>
+        <v>486583</v>
       </c>
       <c r="R13" t="n">
-        <v>7037802</v>
+        <v>7038073</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2008,19 +2008,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129254220</v>
+        <v>129254215</v>
       </c>
       <c r="B14" t="n">
         <v>57727</v>
@@ -2055,10 +2055,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>486583</v>
+        <v>486524</v>
       </c>
       <c r="R14" t="n">
-        <v>7038073</v>
+        <v>7037917</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2110,12 +2110,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2212,60 +2212,80 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129254211</v>
+        <v>129243687</v>
       </c>
       <c r="B16" t="n">
-        <v>57727</v>
+        <v>98706</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>486582</v>
+        <v>486517</v>
       </c>
       <c r="R16" t="n">
-        <v>7037881</v>
+        <v>7037922</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2292,14 +2312,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Minst 120 plantor och 1 fröställning inom ca 1 m2 yta  intill en naturvårdsnitslad björk.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2308,25 +2338,31 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129254221</v>
+        <v>129254211</v>
       </c>
       <c r="B17" t="n">
         <v>57727</v>
@@ -2361,10 +2397,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>486595</v>
+        <v>486582</v>
       </c>
       <c r="R17" t="n">
-        <v>7038075</v>
+        <v>7037881</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2416,80 +2452,60 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129243687</v>
+        <v>129254221</v>
       </c>
       <c r="B18" t="n">
-        <v>98705</v>
+        <v>57727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>486517</v>
+        <v>486595</v>
       </c>
       <c r="R18" t="n">
-        <v>7037922</v>
+        <v>7038075</v>
       </c>
       <c r="S18" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2516,24 +2532,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>15:26</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>15:26</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Minst 120 plantor och 1 fröställning inom ca 1 m2 yta  intill en naturvårdsnitslad björk.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2542,24 +2548,18 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2651,22 +2651,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129254216</v>
+        <v>129242968</v>
       </c>
       <c r="B20" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2674,37 +2674,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>486478</v>
+        <v>486617</v>
       </c>
       <c r="R20" t="n">
-        <v>7037962</v>
+        <v>7037991</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2731,14 +2731,19 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2749,26 +2754,41 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129242968</v>
+        <v>129254216</v>
       </c>
       <c r="B21" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2776,37 +2796,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>486617</v>
+        <v>486478</v>
       </c>
       <c r="R21" t="n">
-        <v>7037991</v>
+        <v>7037962</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2833,19 +2853,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>14:51</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>14:51</t>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2856,31 +2871,16 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2968,12 +2968,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3070,12 +3070,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3183,12 +3183,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3285,12 +3285,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3606,12 +3606,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3840,12 +3840,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -4056,7 +4056,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129254877</v>
+        <v>129254202</v>
       </c>
       <c r="B33" t="n">
         <v>57727</v>
@@ -4091,10 +4091,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>486495</v>
+        <v>486780</v>
       </c>
       <c r="R33" t="n">
-        <v>7037956</v>
+        <v>7037796</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4131,7 +4131,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4146,19 +4146,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129254204</v>
+        <v>129254203</v>
       </c>
       <c r="B34" t="n">
         <v>57727</v>
@@ -4193,10 +4193,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>486767</v>
+        <v>486775</v>
       </c>
       <c r="R34" t="n">
-        <v>7037800</v>
+        <v>7037792</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4233,7 +4233,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4248,19 +4248,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129254202</v>
+        <v>129254877</v>
       </c>
       <c r="B35" t="n">
         <v>57727</v>
@@ -4295,10 +4295,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>486780</v>
+        <v>486495</v>
       </c>
       <c r="R35" t="n">
-        <v>7037796</v>
+        <v>7037956</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4335,7 +4335,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4350,19 +4350,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129254207</v>
+        <v>129254204</v>
       </c>
       <c r="B36" t="n">
         <v>57727</v>
@@ -4397,10 +4397,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>486743</v>
+        <v>486767</v>
       </c>
       <c r="R36" t="n">
-        <v>7037808</v>
+        <v>7037800</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4437,7 +4437,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4452,19 +4452,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129254203</v>
+        <v>129254207</v>
       </c>
       <c r="B37" t="n">
         <v>57727</v>
@@ -4499,10 +4499,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>486775</v>
+        <v>486743</v>
       </c>
       <c r="R37" t="n">
-        <v>7037792</v>
+        <v>7037808</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4554,12 +4554,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4656,22 +4656,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129244231</v>
+        <v>129254226</v>
       </c>
       <c r="B39" t="n">
-        <v>79041</v>
+        <v>78054</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4679,37 +4679,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>486671</v>
+        <v>486585</v>
       </c>
       <c r="R39" t="n">
-        <v>7037887</v>
+        <v>7038070</v>
       </c>
       <c r="S39" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4736,24 +4736,9 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4768,22 +4753,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129254226</v>
+        <v>129244231</v>
       </c>
       <c r="B40" t="n">
-        <v>78054</v>
+        <v>79041</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4791,37 +4776,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>486585</v>
+        <v>486671</v>
       </c>
       <c r="R40" t="n">
-        <v>7038070</v>
+        <v>7037887</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4848,9 +4833,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4865,57 +4865,67 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129254225</v>
+        <v>129243061</v>
       </c>
       <c r="B41" t="n">
-        <v>80050</v>
+        <v>57727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>486624</v>
+        <v>486568</v>
       </c>
       <c r="R41" t="n">
-        <v>7038036</v>
+        <v>7037962</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4945,11 +4955,26 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -4958,48 +4983,73 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129254879</v>
+        <v>129254225</v>
       </c>
       <c r="B42" t="n">
-        <v>57727</v>
+        <v>80050</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5009,10 +5059,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>486552</v>
+        <v>486624</v>
       </c>
       <c r="R42" t="n">
-        <v>7037942</v>
+        <v>7038036</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5047,11 +5097,6 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5064,22 +5109,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129254872</v>
+        <v>129254230</v>
       </c>
       <c r="B43" t="n">
-        <v>57727</v>
+        <v>82873</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5087,21 +5132,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5111,10 +5156,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>486715</v>
+        <v>486609</v>
       </c>
       <c r="R43" t="n">
-        <v>7037924</v>
+        <v>7038052</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5149,11 +5194,6 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5166,22 +5206,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129254230</v>
+        <v>129254879</v>
       </c>
       <c r="B44" t="n">
-        <v>82873</v>
+        <v>57727</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5189,21 +5229,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5213,10 +5253,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>486609</v>
+        <v>486552</v>
       </c>
       <c r="R44" t="n">
-        <v>7038052</v>
+        <v>7037942</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5251,6 +5291,11 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5263,22 +5308,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129243863</v>
+        <v>129254872</v>
       </c>
       <c r="B45" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5286,37 +5331,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>486663</v>
+        <v>486715</v>
       </c>
       <c r="R45" t="n">
-        <v>7037905</v>
+        <v>7037924</v>
       </c>
       <c r="S45" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5343,24 +5388,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Långväxta bålar, på flera granar.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5371,51 +5406,26 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129243061</v>
+        <v>129243863</v>
       </c>
       <c r="B46" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5423,47 +5433,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>486568</v>
+        <v>486663</v>
       </c>
       <c r="R46" t="n">
-        <v>7037962</v>
+        <v>7037905</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5492,7 +5492,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5502,12 +5502,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Långväxta bålar, på flera granar.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5521,7 +5521,7 @@
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ46" t="inlineStr">
@@ -5536,12 +5536,12 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5644,12 +5644,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5741,12 +5741,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5838,12 +5838,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -5940,12 +5940,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -6037,12 +6037,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6246,12 +6246,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -6343,12 +6343,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>

--- a/artfynd/A 39541-2025 artfynd.xlsx
+++ b/artfynd/A 39541-2025 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129242015</v>
+        <v>129241859</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>79043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,47 +792,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
+          <t>Tomasbodarna, Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>486782</v>
+        <v>486860</v>
       </c>
       <c r="R3" t="n">
-        <v>7037909</v>
+        <v>7037938</v>
       </c>
       <c r="S3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,7 +851,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -871,12 +861,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,27 +875,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -928,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129241859</v>
+        <v>129242509</v>
       </c>
       <c r="B4" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -959,17 +924,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tomasbodarna, Tomasbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486860</v>
+        <v>486672</v>
       </c>
       <c r="R4" t="n">
-        <v>7037938</v>
+        <v>7037952</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -998,7 +963,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,7 +973,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129242509</v>
+        <v>129242015</v>
       </c>
       <c r="B5" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1051,34 +1016,44 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>486672</v>
+        <v>486782</v>
       </c>
       <c r="R5" t="n">
-        <v>7037952</v>
+        <v>7037909</v>
       </c>
       <c r="S5" t="n">
         <v>11</v>
@@ -1110,7 +1085,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,7 +1095,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,7 +1114,27 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1152,27 +1152,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129254223</v>
+        <v>129254218</v>
       </c>
       <c r="B6" t="n">
-        <v>57568</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1180,29 +1180,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>486737</v>
+        <v>486524</v>
       </c>
       <c r="R6" t="n">
-        <v>7037835</v>
+        <v>7037965</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1235,6 +1223,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1261,7 +1254,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129254218</v>
+        <v>129254206</v>
       </c>
       <c r="B7" t="n">
         <v>57727</v>
@@ -1296,10 +1289,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>486524</v>
+        <v>486751</v>
       </c>
       <c r="R7" t="n">
-        <v>7037965</v>
+        <v>7037804</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1336,7 +1329,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1465,27 +1458,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129254206</v>
+        <v>129254223</v>
       </c>
       <c r="B9" t="n">
-        <v>57727</v>
+        <v>57568</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1493,17 +1486,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>486751</v>
+        <v>486737</v>
       </c>
       <c r="R9" t="n">
-        <v>7037804</v>
+        <v>7037835</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1536,11 +1541,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1714,7 +1714,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129254871</v>
+        <v>129254205</v>
       </c>
       <c r="B11" t="n">
         <v>57727</v>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>486833</v>
+        <v>486752</v>
       </c>
       <c r="R11" t="n">
-        <v>7037850</v>
+        <v>7037802</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1789,7 +1789,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1804,19 +1804,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129254205</v>
+        <v>129254220</v>
       </c>
       <c r="B12" t="n">
         <v>57727</v>
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>486752</v>
+        <v>486583</v>
       </c>
       <c r="R12" t="n">
-        <v>7037802</v>
+        <v>7038073</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1918,7 +1918,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129254220</v>
+        <v>129254215</v>
       </c>
       <c r="B13" t="n">
         <v>57727</v>
@@ -1953,10 +1953,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>486583</v>
+        <v>486524</v>
       </c>
       <c r="R13" t="n">
-        <v>7038073</v>
+        <v>7037917</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2020,7 +2020,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129254215</v>
+        <v>129254871</v>
       </c>
       <c r="B14" t="n">
         <v>57727</v>
@@ -2055,10 +2055,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>486524</v>
+        <v>486833</v>
       </c>
       <c r="R14" t="n">
-        <v>7037917</v>
+        <v>7037850</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2095,7 +2095,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2110,12 +2110,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2227,7 +2227,7 @@
         <v>129243687</v>
       </c>
       <c r="B16" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>129254199</v>
       </c>
       <c r="B19" t="n">
-        <v>83007</v>
+        <v>83011</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         <v>129242968</v>
       </c>
       <c r="B20" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>129254228</v>
       </c>
       <c r="B22" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3297,10 +3297,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129244388</v>
+        <v>129254874</v>
       </c>
       <c r="B26" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3308,34 +3308,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>486782</v>
+        <v>486550</v>
       </c>
       <c r="R26" t="n">
-        <v>7037877</v>
+        <v>7037929</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3365,24 +3365,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>15:53</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>15:53</t>
-        </is>
-      </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3393,31 +3383,26 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129254874</v>
+        <v>129244388</v>
       </c>
       <c r="B27" t="n">
-        <v>57727</v>
+        <v>79043</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3425,34 +3410,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>486550</v>
+        <v>486782</v>
       </c>
       <c r="R27" t="n">
-        <v>7037929</v>
+        <v>7037877</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3482,14 +3467,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3500,16 +3495,21 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3621,7 +3621,7 @@
         <v>129241899</v>
       </c>
       <c r="B29" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129254873</v>
+        <v>129254204</v>
       </c>
       <c r="B32" t="n">
         <v>57727</v>
@@ -3989,10 +3989,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>486683</v>
+        <v>486767</v>
       </c>
       <c r="R32" t="n">
-        <v>7037917</v>
+        <v>7037800</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4044,19 +4044,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129254202</v>
+        <v>129254207</v>
       </c>
       <c r="B33" t="n">
         <v>57727</v>
@@ -4091,10 +4091,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>486780</v>
+        <v>486743</v>
       </c>
       <c r="R33" t="n">
-        <v>7037796</v>
+        <v>7037808</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4158,7 +4158,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129254203</v>
+        <v>129254873</v>
       </c>
       <c r="B34" t="n">
         <v>57727</v>
@@ -4193,10 +4193,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>486775</v>
+        <v>486683</v>
       </c>
       <c r="R34" t="n">
-        <v>7037792</v>
+        <v>7037917</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4233,7 +4233,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4248,12 +4248,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4362,7 +4362,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129254204</v>
+        <v>129254202</v>
       </c>
       <c r="B36" t="n">
         <v>57727</v>
@@ -4397,10 +4397,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>486767</v>
+        <v>486780</v>
       </c>
       <c r="R36" t="n">
-        <v>7037800</v>
+        <v>7037796</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4437,7 +4437,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4464,7 +4464,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129254207</v>
+        <v>129254203</v>
       </c>
       <c r="B37" t="n">
         <v>57727</v>
@@ -4499,10 +4499,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>486743</v>
+        <v>486775</v>
       </c>
       <c r="R37" t="n">
-        <v>7037808</v>
+        <v>7037792</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4671,7 +4671,7 @@
         <v>129254226</v>
       </c>
       <c r="B39" t="n">
-        <v>78054</v>
+        <v>78056</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
         <v>129244231</v>
       </c>
       <c r="B40" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4877,10 +4877,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129243061</v>
+        <v>129243863</v>
       </c>
       <c r="B41" t="n">
-        <v>57727</v>
+        <v>79043</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4888,47 +4888,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>486568</v>
+        <v>486663</v>
       </c>
       <c r="R41" t="n">
-        <v>7037962</v>
+        <v>7037905</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4957,7 +4947,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4967,12 +4957,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Långväxta bålar, på flera granar.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4986,7 +4976,7 @@
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ41" t="inlineStr">
@@ -5001,12 +4991,12 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5024,45 +5014,55 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129254225</v>
+        <v>129243061</v>
       </c>
       <c r="B42" t="n">
-        <v>80050</v>
+        <v>57727</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>486624</v>
+        <v>486568</v>
       </c>
       <c r="R42" t="n">
-        <v>7038036</v>
+        <v>7037962</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5092,11 +5092,26 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5105,26 +5120,51 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129254230</v>
+        <v>129254879</v>
       </c>
       <c r="B43" t="n">
-        <v>82873</v>
+        <v>57727</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5132,21 +5172,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5156,10 +5196,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>486609</v>
+        <v>486552</v>
       </c>
       <c r="R43" t="n">
-        <v>7038052</v>
+        <v>7037942</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5194,6 +5234,11 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5206,19 +5251,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129254879</v>
+        <v>129254872</v>
       </c>
       <c r="B44" t="n">
         <v>57727</v>
@@ -5253,10 +5298,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>486552</v>
+        <v>486715</v>
       </c>
       <c r="R44" t="n">
-        <v>7037942</v>
+        <v>7037924</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5320,10 +5365,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129254872</v>
+        <v>129254230</v>
       </c>
       <c r="B45" t="n">
-        <v>57727</v>
+        <v>82877</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5331,21 +5376,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5355,10 +5400,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>486715</v>
+        <v>486609</v>
       </c>
       <c r="R45" t="n">
-        <v>7037924</v>
+        <v>7038052</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5393,11 +5438,6 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5410,60 +5450,60 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129243863</v>
+        <v>129254225</v>
       </c>
       <c r="B46" t="n">
-        <v>79041</v>
+        <v>80052</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>486663</v>
+        <v>486624</v>
       </c>
       <c r="R46" t="n">
-        <v>7037905</v>
+        <v>7038036</v>
       </c>
       <c r="S46" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5490,26 +5530,11 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Långväxta bålar, på flera granar.</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5518,41 +5543,16 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5562,7 +5562,7 @@
         <v>129254227</v>
       </c>
       <c r="B47" t="n">
-        <v>91536</v>
+        <v>91539</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5656,10 +5656,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129254196</v>
+        <v>129254231</v>
       </c>
       <c r="B48" t="n">
-        <v>83007</v>
+        <v>88943</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5667,21 +5667,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6440</v>
+        <v>510</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5691,10 +5691,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>486582</v>
+        <v>486615</v>
       </c>
       <c r="R48" t="n">
-        <v>7038072</v>
+        <v>7037875</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5753,32 +5753,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129254224</v>
+        <v>129254196</v>
       </c>
       <c r="B49" t="n">
-        <v>80050</v>
+        <v>83011</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6456</v>
+        <v>6440</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5788,10 +5788,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>486599</v>
+        <v>486582</v>
       </c>
       <c r="R49" t="n">
-        <v>7038068</v>
+        <v>7038072</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5850,32 +5850,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129254214</v>
+        <v>129254224</v>
       </c>
       <c r="B50" t="n">
-        <v>57727</v>
+        <v>80052</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5885,10 +5885,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>486551</v>
+        <v>486599</v>
       </c>
       <c r="R50" t="n">
-        <v>7037889</v>
+        <v>7038068</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5921,11 +5921,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5952,10 +5947,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129254231</v>
+        <v>129254214</v>
       </c>
       <c r="B51" t="n">
-        <v>88940</v>
+        <v>57727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5963,21 +5958,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5987,10 +5982,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>486615</v>
+        <v>486551</v>
       </c>
       <c r="R51" t="n">
-        <v>7037875</v>
+        <v>7037889</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6023,6 +6018,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6052,7 +6052,7 @@
         <v>129243695</v>
       </c>
       <c r="B52" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6156,10 +6156,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129254213</v>
+        <v>129254229</v>
       </c>
       <c r="B53" t="n">
-        <v>57727</v>
+        <v>82877</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6167,21 +6167,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6191,10 +6191,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>486551</v>
+        <v>486611</v>
       </c>
       <c r="R53" t="n">
-        <v>7037886</v>
+        <v>7038042</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6227,11 +6227,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6258,10 +6253,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129254229</v>
+        <v>129254213</v>
       </c>
       <c r="B54" t="n">
-        <v>82873</v>
+        <v>57727</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6269,21 +6264,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6293,10 +6288,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>486611</v>
+        <v>486551</v>
       </c>
       <c r="R54" t="n">
-        <v>7038042</v>
+        <v>7037886</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6329,6 +6324,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6460,7 +6460,7 @@
         <v>129243772</v>
       </c>
       <c r="B56" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 39541-2025 artfynd.xlsx
+++ b/artfynd/A 39541-2025 artfynd.xlsx
@@ -2663,10 +2663,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129242968</v>
+        <v>129254216</v>
       </c>
       <c r="B20" t="n">
-        <v>79043</v>
+        <v>57727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2674,37 +2674,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>486617</v>
+        <v>486478</v>
       </c>
       <c r="R20" t="n">
-        <v>7037991</v>
+        <v>7037962</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2731,19 +2731,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>14:51</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>14:51</t>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2754,41 +2749,26 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129254216</v>
+        <v>129242968</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>79043</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2796,37 +2776,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>486478</v>
+        <v>486617</v>
       </c>
       <c r="R21" t="n">
-        <v>7037962</v>
+        <v>7037991</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2853,14 +2833,19 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2871,16 +2856,31 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -4668,10 +4668,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129254226</v>
+        <v>129244231</v>
       </c>
       <c r="B39" t="n">
-        <v>78056</v>
+        <v>79043</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4679,37 +4679,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>486585</v>
+        <v>486671</v>
       </c>
       <c r="R39" t="n">
-        <v>7038070</v>
+        <v>7037887</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4736,9 +4736,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4753,22 +4768,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129244231</v>
+        <v>129254226</v>
       </c>
       <c r="B40" t="n">
-        <v>79043</v>
+        <v>78056</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4776,37 +4791,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>486671</v>
+        <v>486585</v>
       </c>
       <c r="R40" t="n">
-        <v>7037887</v>
+        <v>7038070</v>
       </c>
       <c r="S40" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4833,24 +4848,9 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4865,12 +4865,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>

--- a/artfynd/A 39541-2025 artfynd.xlsx
+++ b/artfynd/A 39541-2025 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129241859</v>
+        <v>129254875</v>
       </c>
       <c r="B3" t="n">
-        <v>79043</v>
+        <v>57727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,37 +792,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tomasbodarna, Tomasbodarna, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>486860</v>
+        <v>486429</v>
       </c>
       <c r="R3" t="n">
-        <v>7037938</v>
+        <v>7037954</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -849,19 +849,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:27</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:27</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,31 +867,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129242509</v>
+        <v>129254206</v>
       </c>
       <c r="B4" t="n">
-        <v>79043</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,37 +894,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486672</v>
+        <v>486751</v>
       </c>
       <c r="R4" t="n">
-        <v>7037952</v>
+        <v>7037804</v>
       </c>
       <c r="S4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -961,19 +951,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:42</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,31 +969,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129242015</v>
+        <v>129241859</v>
       </c>
       <c r="B5" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,47 +996,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
+          <t>Tomasbodarna, Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>486782</v>
+        <v>486860</v>
       </c>
       <c r="R5" t="n">
-        <v>7037909</v>
+        <v>7037938</v>
       </c>
       <c r="S5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1085,7 +1055,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,12 +1065,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1114,27 +1079,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1152,10 +1097,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129254218</v>
+        <v>129242509</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,37 +1108,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>486524</v>
+        <v>486672</v>
       </c>
       <c r="R6" t="n">
-        <v>7037965</v>
+        <v>7037952</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1220,14 +1165,19 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,23 +1188,28 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129254206</v>
+        <v>129242015</v>
       </c>
       <c r="B7" t="n">
         <v>57727</v>
@@ -1283,19 +1238,29 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>486751</v>
+        <v>486782</v>
       </c>
       <c r="R7" t="n">
-        <v>7037804</v>
+        <v>7037909</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1322,14 +1287,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1340,43 +1315,68 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129254875</v>
+        <v>129254223</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>57568</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1384,17 +1384,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>486429</v>
+        <v>486737</v>
       </c>
       <c r="R8" t="n">
-        <v>7037954</v>
+        <v>7037835</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1429,11 +1441,6 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1446,39 +1453,39 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129254223</v>
+        <v>129254218</v>
       </c>
       <c r="B9" t="n">
-        <v>57568</v>
+        <v>57727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1486,29 +1493,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>486737</v>
+        <v>486524</v>
       </c>
       <c r="R9" t="n">
-        <v>7037835</v>
+        <v>7037965</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1541,6 +1536,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1918,7 +1918,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129254215</v>
+        <v>129254871</v>
       </c>
       <c r="B13" t="n">
         <v>57727</v>
@@ -1953,10 +1953,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>486524</v>
+        <v>486833</v>
       </c>
       <c r="R13" t="n">
-        <v>7037917</v>
+        <v>7037850</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1993,7 +1993,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2008,19 +2008,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129254871</v>
+        <v>129254215</v>
       </c>
       <c r="B14" t="n">
         <v>57727</v>
@@ -2055,10 +2055,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>486833</v>
+        <v>486524</v>
       </c>
       <c r="R14" t="n">
-        <v>7037850</v>
+        <v>7037917</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2095,7 +2095,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2110,12 +2110,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2224,68 +2224,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129243687</v>
+        <v>129254221</v>
       </c>
       <c r="B16" t="n">
-        <v>98710</v>
+        <v>57727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>486517</v>
+        <v>486595</v>
       </c>
       <c r="R16" t="n">
-        <v>7037922</v>
+        <v>7038075</v>
       </c>
       <c r="S16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2312,24 +2292,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>15:26</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>15:26</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Minst 120 plantor och 1 fröställning inom ca 1 m2 yta  intill en naturvårdsnitslad björk.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2338,72 +2308,86 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129254211</v>
+        <v>129243687</v>
       </c>
       <c r="B17" t="n">
-        <v>57727</v>
+        <v>98712</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>486582</v>
+        <v>486517</v>
       </c>
       <c r="R17" t="n">
-        <v>7037881</v>
+        <v>7037922</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2430,14 +2414,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Minst 120 plantor och 1 fröställning inom ca 1 m2 yta  intill en naturvårdsnitslad björk.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2446,25 +2440,31 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129254221</v>
+        <v>129254211</v>
       </c>
       <c r="B18" t="n">
         <v>57727</v>
@@ -2499,10 +2499,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>486595</v>
+        <v>486582</v>
       </c>
       <c r="R18" t="n">
-        <v>7038075</v>
+        <v>7037881</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2569,7 +2569,7 @@
         <v>129254199</v>
       </c>
       <c r="B19" t="n">
-        <v>83011</v>
+        <v>83012</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2663,10 +2663,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129254216</v>
+        <v>129242968</v>
       </c>
       <c r="B20" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2674,37 +2674,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>486478</v>
+        <v>486617</v>
       </c>
       <c r="R20" t="n">
-        <v>7037962</v>
+        <v>7037991</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2731,14 +2731,19 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2749,26 +2754,41 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129242968</v>
+        <v>129254216</v>
       </c>
       <c r="B21" t="n">
-        <v>79043</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2776,37 +2796,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>486617</v>
+        <v>486478</v>
       </c>
       <c r="R21" t="n">
-        <v>7037991</v>
+        <v>7037962</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2833,19 +2853,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>14:51</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>14:51</t>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2856,41 +2871,26 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129254228</v>
+        <v>129254210</v>
       </c>
       <c r="B22" t="n">
-        <v>91563</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2898,19 +2898,23 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2918,10 +2922,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>486556</v>
+        <v>486650</v>
       </c>
       <c r="R22" t="n">
-        <v>7037879</v>
+        <v>7037866</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2954,6 +2958,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2980,10 +2989,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129254210</v>
+        <v>129254228</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>91565</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2991,23 +3000,19 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3015,10 +3020,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>486650</v>
+        <v>486556</v>
       </c>
       <c r="R23" t="n">
-        <v>7037866</v>
+        <v>7037879</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3051,11 +3056,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3297,10 +3297,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129254874</v>
+        <v>129244388</v>
       </c>
       <c r="B26" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3308,34 +3308,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>486550</v>
+        <v>486782</v>
       </c>
       <c r="R26" t="n">
-        <v>7037929</v>
+        <v>7037877</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3365,14 +3365,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3383,26 +3393,31 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129244388</v>
+        <v>129254219</v>
       </c>
       <c r="B27" t="n">
-        <v>79043</v>
+        <v>57727</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3410,34 +3425,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>486782</v>
+        <v>486543</v>
       </c>
       <c r="R27" t="n">
-        <v>7037877</v>
+        <v>7037939</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3467,24 +3482,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>15:53</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>15:53</t>
-        </is>
-      </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3495,28 +3500,23 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129254219</v>
+        <v>129254874</v>
       </c>
       <c r="B28" t="n">
         <v>57727</v>
@@ -3551,10 +3551,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>486543</v>
+        <v>486550</v>
       </c>
       <c r="R28" t="n">
-        <v>7037939</v>
+        <v>7037929</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3591,7 +3591,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3606,12 +3606,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3621,7 +3621,7 @@
         <v>129241899</v>
       </c>
       <c r="B29" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129254204</v>
+        <v>129254873</v>
       </c>
       <c r="B32" t="n">
         <v>57727</v>
@@ -3989,10 +3989,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>486767</v>
+        <v>486683</v>
       </c>
       <c r="R32" t="n">
-        <v>7037800</v>
+        <v>7037917</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4044,19 +4044,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129254207</v>
+        <v>129254877</v>
       </c>
       <c r="B33" t="n">
         <v>57727</v>
@@ -4091,10 +4091,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>486743</v>
+        <v>486495</v>
       </c>
       <c r="R33" t="n">
-        <v>7037808</v>
+        <v>7037956</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4131,7 +4131,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4146,19 +4146,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129254873</v>
+        <v>129254207</v>
       </c>
       <c r="B34" t="n">
         <v>57727</v>
@@ -4193,10 +4193,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>486683</v>
+        <v>486743</v>
       </c>
       <c r="R34" t="n">
-        <v>7037917</v>
+        <v>7037808</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4233,7 +4233,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4248,19 +4248,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129254877</v>
+        <v>129254204</v>
       </c>
       <c r="B35" t="n">
         <v>57727</v>
@@ -4295,10 +4295,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>486495</v>
+        <v>486767</v>
       </c>
       <c r="R35" t="n">
-        <v>7037956</v>
+        <v>7037800</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4335,7 +4335,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4350,12 +4350,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4671,7 +4671,7 @@
         <v>129244231</v>
       </c>
       <c r="B39" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>129254226</v>
       </c>
       <c r="B40" t="n">
-        <v>78056</v>
+        <v>78057</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4877,10 +4877,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129243863</v>
+        <v>129243061</v>
       </c>
       <c r="B41" t="n">
-        <v>79043</v>
+        <v>57727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4888,37 +4888,47 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>486663</v>
+        <v>486568</v>
       </c>
       <c r="R41" t="n">
-        <v>7037905</v>
+        <v>7037962</v>
       </c>
       <c r="S41" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4947,7 +4957,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4957,12 +4967,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Långväxta bålar, på flera granar.</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4976,7 +4986,7 @@
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ41" t="inlineStr">
@@ -4991,12 +5001,12 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5014,10 +5024,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129243061</v>
+        <v>129254230</v>
       </c>
       <c r="B42" t="n">
-        <v>57727</v>
+        <v>82878</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5025,44 +5035,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>486568</v>
+        <v>486609</v>
       </c>
       <c r="R42" t="n">
-        <v>7037962</v>
+        <v>7038052</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5092,26 +5092,11 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen.</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5120,41 +5105,16 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5365,10 +5325,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129254230</v>
+        <v>129243863</v>
       </c>
       <c r="B45" t="n">
-        <v>82877</v>
+        <v>79044</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5376,37 +5336,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>486609</v>
+        <v>486663</v>
       </c>
       <c r="R45" t="n">
-        <v>7038052</v>
+        <v>7037905</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5433,11 +5393,26 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Långväxta bålar, på flera granar.</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5446,16 +5421,41 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5465,7 +5465,7 @@
         <v>129254225</v>
       </c>
       <c r="B46" t="n">
-        <v>80052</v>
+        <v>80053</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5562,7 +5562,7 @@
         <v>129254227</v>
       </c>
       <c r="B47" t="n">
-        <v>91539</v>
+        <v>91541</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         <v>129254231</v>
       </c>
       <c r="B48" t="n">
-        <v>88943</v>
+        <v>88945</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5756,7 +5756,7 @@
         <v>129254196</v>
       </c>
       <c r="B49" t="n">
-        <v>83011</v>
+        <v>83012</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         <v>129254224</v>
       </c>
       <c r="B50" t="n">
-        <v>80052</v>
+        <v>80053</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6052,7 +6052,7 @@
         <v>129243695</v>
       </c>
       <c r="B52" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6159,7 +6159,7 @@
         <v>129254229</v>
       </c>
       <c r="B53" t="n">
-        <v>82877</v>
+        <v>82878</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6355,10 +6355,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129254878</v>
+        <v>129243772</v>
       </c>
       <c r="B55" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6366,37 +6366,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>486553</v>
+        <v>486608</v>
       </c>
       <c r="R55" t="n">
-        <v>7037937</v>
+        <v>7037908</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6423,14 +6423,19 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6441,26 +6446,51 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129243772</v>
+        <v>129254878</v>
       </c>
       <c r="B56" t="n">
-        <v>79043</v>
+        <v>57727</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6468,37 +6498,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>486608</v>
+        <v>486553</v>
       </c>
       <c r="R56" t="n">
-        <v>7037908</v>
+        <v>7037937</v>
       </c>
       <c r="S56" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6525,19 +6555,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>15:38</t>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6548,41 +6573,16 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>

--- a/artfynd/A 39541-2025 artfynd.xlsx
+++ b/artfynd/A 39541-2025 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129254875</v>
+        <v>129241859</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,37 +792,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Tomasbodarna, Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>486429</v>
+        <v>486860</v>
       </c>
       <c r="R3" t="n">
-        <v>7037954</v>
+        <v>7037938</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -849,14 +849,19 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,26 +872,31 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129254206</v>
+        <v>129242509</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -894,37 +904,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486751</v>
+        <v>486672</v>
       </c>
       <c r="R4" t="n">
-        <v>7037804</v>
+        <v>7037952</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -951,14 +961,19 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -969,26 +984,31 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129241859</v>
+        <v>129242015</v>
       </c>
       <c r="B5" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -996,37 +1016,47 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tomasbodarna, Tomasbodarna, Jmt</t>
+          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>486860</v>
+        <v>486782</v>
       </c>
       <c r="R5" t="n">
-        <v>7037938</v>
+        <v>7037909</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1055,7 +1085,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1065,7 +1095,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1079,7 +1114,27 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1097,10 +1152,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129242509</v>
+        <v>129254218</v>
       </c>
       <c r="B6" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1108,37 +1163,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>486672</v>
+        <v>486524</v>
       </c>
       <c r="R6" t="n">
-        <v>7037952</v>
+        <v>7037965</v>
       </c>
       <c r="S6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1165,19 +1220,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:42</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1188,28 +1238,23 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129242015</v>
+        <v>129254875</v>
       </c>
       <c r="B7" t="n">
         <v>57727</v>
@@ -1238,29 +1283,19 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>486782</v>
+        <v>486429</v>
       </c>
       <c r="R7" t="n">
-        <v>7037909</v>
+        <v>7037954</v>
       </c>
       <c r="S7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1287,24 +1322,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1315,68 +1340,43 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129254223</v>
+        <v>129254206</v>
       </c>
       <c r="B8" t="n">
-        <v>57568</v>
+        <v>57727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1384,29 +1384,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>486737</v>
+        <v>486751</v>
       </c>
       <c r="R8" t="n">
-        <v>7037835</v>
+        <v>7037804</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1439,6 +1427,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1465,27 +1458,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129254218</v>
+        <v>129254223</v>
       </c>
       <c r="B9" t="n">
-        <v>57727</v>
+        <v>57568</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1493,17 +1486,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>486524</v>
+        <v>486737</v>
       </c>
       <c r="R9" t="n">
-        <v>7037965</v>
+        <v>7037835</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1536,11 +1541,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1714,7 +1714,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129254205</v>
+        <v>129254871</v>
       </c>
       <c r="B11" t="n">
         <v>57727</v>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>486752</v>
+        <v>486833</v>
       </c>
       <c r="R11" t="n">
-        <v>7037802</v>
+        <v>7037850</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1789,7 +1789,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1804,19 +1804,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129254220</v>
+        <v>129254205</v>
       </c>
       <c r="B12" t="n">
         <v>57727</v>
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>486583</v>
+        <v>486752</v>
       </c>
       <c r="R12" t="n">
-        <v>7038073</v>
+        <v>7037802</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1918,7 +1918,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129254871</v>
+        <v>129254220</v>
       </c>
       <c r="B13" t="n">
         <v>57727</v>
@@ -1953,10 +1953,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>486833</v>
+        <v>486583</v>
       </c>
       <c r="R13" t="n">
-        <v>7037850</v>
+        <v>7038073</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1993,7 +1993,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2008,12 +2008,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2224,7 +2224,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129254221</v>
+        <v>129254211</v>
       </c>
       <c r="B16" t="n">
         <v>57727</v>
@@ -2259,10 +2259,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>486595</v>
+        <v>486582</v>
       </c>
       <c r="R16" t="n">
-        <v>7038075</v>
+        <v>7037881</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2326,68 +2326,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129243687</v>
+        <v>129254221</v>
       </c>
       <c r="B17" t="n">
-        <v>98712</v>
+        <v>57727</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>486517</v>
+        <v>486595</v>
       </c>
       <c r="R17" t="n">
-        <v>7037922</v>
+        <v>7038075</v>
       </c>
       <c r="S17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2414,24 +2394,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>15:26</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>15:26</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Minst 120 plantor och 1 fröställning inom ca 1 m2 yta  intill en naturvårdsnitslad björk.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2440,72 +2410,86 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129254211</v>
+        <v>129243687</v>
       </c>
       <c r="B18" t="n">
-        <v>57727</v>
+        <v>98716</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>486582</v>
+        <v>486517</v>
       </c>
       <c r="R18" t="n">
-        <v>7037881</v>
+        <v>7037922</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2532,14 +2516,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Minst 120 plantor och 1 fröställning inom ca 1 m2 yta  intill en naturvårdsnitslad björk.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2548,18 +2542,24 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2887,10 +2887,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129254210</v>
+        <v>129254228</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>91569</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2898,23 +2898,19 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2922,10 +2918,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>486650</v>
+        <v>486556</v>
       </c>
       <c r="R22" t="n">
-        <v>7037866</v>
+        <v>7037879</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2958,11 +2954,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2989,10 +2980,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129254228</v>
+        <v>129254210</v>
       </c>
       <c r="B23" t="n">
-        <v>91565</v>
+        <v>57727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3000,19 +2991,23 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3020,10 +3015,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>486556</v>
+        <v>486650</v>
       </c>
       <c r="R23" t="n">
-        <v>7037879</v>
+        <v>7037866</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3056,6 +3051,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3414,7 +3414,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129254219</v>
+        <v>129254874</v>
       </c>
       <c r="B27" t="n">
         <v>57727</v>
@@ -3449,10 +3449,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>486543</v>
+        <v>486550</v>
       </c>
       <c r="R27" t="n">
-        <v>7037939</v>
+        <v>7037929</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3489,7 +3489,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3504,19 +3504,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129254874</v>
+        <v>129254219</v>
       </c>
       <c r="B28" t="n">
         <v>57727</v>
@@ -3551,10 +3551,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>486550</v>
+        <v>486543</v>
       </c>
       <c r="R28" t="n">
-        <v>7037929</v>
+        <v>7037939</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3591,7 +3591,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3606,12 +3606,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3954,7 +3954,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129254873</v>
+        <v>129254877</v>
       </c>
       <c r="B32" t="n">
         <v>57727</v>
@@ -3989,10 +3989,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>486683</v>
+        <v>486495</v>
       </c>
       <c r="R32" t="n">
-        <v>7037917</v>
+        <v>7037956</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4056,7 +4056,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129254877</v>
+        <v>129254204</v>
       </c>
       <c r="B33" t="n">
         <v>57727</v>
@@ -4091,10 +4091,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>486495</v>
+        <v>486767</v>
       </c>
       <c r="R33" t="n">
-        <v>7037956</v>
+        <v>7037800</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4131,7 +4131,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4146,19 +4146,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129254207</v>
+        <v>129254202</v>
       </c>
       <c r="B34" t="n">
         <v>57727</v>
@@ -4193,10 +4193,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>486743</v>
+        <v>486780</v>
       </c>
       <c r="R34" t="n">
-        <v>7037808</v>
+        <v>7037796</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4260,7 +4260,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129254204</v>
+        <v>129254207</v>
       </c>
       <c r="B35" t="n">
         <v>57727</v>
@@ -4295,10 +4295,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>486767</v>
+        <v>486743</v>
       </c>
       <c r="R35" t="n">
-        <v>7037800</v>
+        <v>7037808</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4335,7 +4335,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4362,7 +4362,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129254202</v>
+        <v>129254203</v>
       </c>
       <c r="B36" t="n">
         <v>57727</v>
@@ -4397,10 +4397,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>486780</v>
+        <v>486775</v>
       </c>
       <c r="R36" t="n">
-        <v>7037796</v>
+        <v>7037792</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4464,7 +4464,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129254203</v>
+        <v>129254873</v>
       </c>
       <c r="B37" t="n">
         <v>57727</v>
@@ -4499,10 +4499,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>486775</v>
+        <v>486683</v>
       </c>
       <c r="R37" t="n">
-        <v>7037792</v>
+        <v>7037917</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4539,7 +4539,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4554,12 +4554,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4668,10 +4668,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129244231</v>
+        <v>129254226</v>
       </c>
       <c r="B39" t="n">
-        <v>79044</v>
+        <v>78057</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4679,37 +4679,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>486671</v>
+        <v>486585</v>
       </c>
       <c r="R39" t="n">
-        <v>7037887</v>
+        <v>7038070</v>
       </c>
       <c r="S39" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4736,24 +4736,9 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4768,22 +4753,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129254226</v>
+        <v>129244231</v>
       </c>
       <c r="B40" t="n">
-        <v>78057</v>
+        <v>79044</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4791,37 +4776,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>486585</v>
+        <v>486671</v>
       </c>
       <c r="R40" t="n">
-        <v>7038070</v>
+        <v>7037887</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4848,9 +4833,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4865,22 +4865,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129243061</v>
+        <v>129243863</v>
       </c>
       <c r="B41" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4888,47 +4888,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>486568</v>
+        <v>486663</v>
       </c>
       <c r="R41" t="n">
-        <v>7037962</v>
+        <v>7037905</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4957,7 +4947,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4967,12 +4957,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Långväxta bålar, på flera granar.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4986,7 +4976,7 @@
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ41" t="inlineStr">
@@ -5001,12 +4991,12 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5024,10 +5014,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129254230</v>
+        <v>129243061</v>
       </c>
       <c r="B42" t="n">
-        <v>82878</v>
+        <v>57727</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5035,34 +5025,44 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>486609</v>
+        <v>486568</v>
       </c>
       <c r="R42" t="n">
-        <v>7038052</v>
+        <v>7037962</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5092,11 +5092,26 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5105,26 +5120,51 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129254879</v>
+        <v>129254230</v>
       </c>
       <c r="B43" t="n">
-        <v>57727</v>
+        <v>82878</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5132,21 +5172,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5156,10 +5196,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>486552</v>
+        <v>486609</v>
       </c>
       <c r="R43" t="n">
-        <v>7037942</v>
+        <v>7038052</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5194,11 +5234,6 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5211,44 +5246,44 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129254872</v>
+        <v>129254225</v>
       </c>
       <c r="B44" t="n">
-        <v>57727</v>
+        <v>80053</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5258,10 +5293,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>486715</v>
+        <v>486624</v>
       </c>
       <c r="R44" t="n">
-        <v>7037924</v>
+        <v>7038036</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5296,11 +5331,6 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5313,22 +5343,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129243863</v>
+        <v>129254879</v>
       </c>
       <c r="B45" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5336,37 +5366,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>486663</v>
+        <v>486552</v>
       </c>
       <c r="R45" t="n">
-        <v>7037905</v>
+        <v>7037942</v>
       </c>
       <c r="S45" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5393,24 +5423,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Långväxta bålar, på flera granar.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5421,73 +5441,48 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129254225</v>
+        <v>129254872</v>
       </c>
       <c r="B46" t="n">
-        <v>80053</v>
+        <v>57727</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5497,10 +5492,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>486624</v>
+        <v>486715</v>
       </c>
       <c r="R46" t="n">
-        <v>7038036</v>
+        <v>7037924</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5535,6 +5530,11 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5547,12 +5547,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5562,7 +5562,7 @@
         <v>129254227</v>
       </c>
       <c r="B47" t="n">
-        <v>91541</v>
+        <v>91545</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         <v>129254231</v>
       </c>
       <c r="B48" t="n">
-        <v>88945</v>
+        <v>88949</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6355,10 +6355,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129243772</v>
+        <v>129254878</v>
       </c>
       <c r="B55" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6366,37 +6366,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>486608</v>
+        <v>486553</v>
       </c>
       <c r="R55" t="n">
-        <v>7037908</v>
+        <v>7037937</v>
       </c>
       <c r="S55" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6423,19 +6423,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>15:38</t>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6446,51 +6441,26 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129254878</v>
+        <v>129243772</v>
       </c>
       <c r="B56" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6498,37 +6468,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>486553</v>
+        <v>486608</v>
       </c>
       <c r="R56" t="n">
-        <v>7037937</v>
+        <v>7037908</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6555,14 +6525,19 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6573,16 +6548,41 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>

--- a/artfynd/A 39541-2025 artfynd.xlsx
+++ b/artfynd/A 39541-2025 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129241859</v>
+        <v>129254218</v>
       </c>
       <c r="B3" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,37 +792,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tomasbodarna, Tomasbodarna, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>486860</v>
+        <v>486524</v>
       </c>
       <c r="R3" t="n">
-        <v>7037938</v>
+        <v>7037965</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -849,19 +849,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:27</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:27</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,31 +867,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129242509</v>
+        <v>129254875</v>
       </c>
       <c r="B4" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,37 +894,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486672</v>
+        <v>486429</v>
       </c>
       <c r="R4" t="n">
-        <v>7037952</v>
+        <v>7037954</v>
       </c>
       <c r="S4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -961,19 +951,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:42</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,28 +969,23 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129242015</v>
+        <v>129254206</v>
       </c>
       <c r="B5" t="n">
         <v>57727</v>
@@ -1034,29 +1014,19 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>486782</v>
+        <v>486751</v>
       </c>
       <c r="R5" t="n">
-        <v>7037909</v>
+        <v>7037804</v>
       </c>
       <c r="S5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,24 +1053,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,68 +1071,43 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129254218</v>
+        <v>129254223</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>57568</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1180,17 +1115,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>486524</v>
+        <v>486737</v>
       </c>
       <c r="R6" t="n">
-        <v>7037965</v>
+        <v>7037835</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1223,11 +1170,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,10 +1196,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129254875</v>
+        <v>129241859</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,37 +1207,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Tomasbodarna, Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>486429</v>
+        <v>486860</v>
       </c>
       <c r="R7" t="n">
-        <v>7037954</v>
+        <v>7037938</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1322,14 +1264,19 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1340,26 +1287,31 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129254206</v>
+        <v>129242509</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,37 +1319,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>486751</v>
+        <v>486672</v>
       </c>
       <c r="R8" t="n">
-        <v>7037804</v>
+        <v>7037952</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1424,14 +1376,19 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1442,43 +1399,48 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129254223</v>
+        <v>129242015</v>
       </c>
       <c r="B9" t="n">
-        <v>57568</v>
+        <v>57727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1486,32 +1448,30 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>486737</v>
+        <v>486782</v>
       </c>
       <c r="R9" t="n">
-        <v>7037835</v>
+        <v>7037909</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1538,11 +1498,26 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1551,23 +1526,48 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129243523</v>
+        <v>129254871</v>
       </c>
       <c r="B10" t="n">
         <v>57727</v>
@@ -1596,29 +1596,19 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>486472</v>
+        <v>486833</v>
       </c>
       <c r="R10" t="n">
-        <v>7037927</v>
+        <v>7037850</v>
       </c>
       <c r="S10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1645,24 +1635,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>15:21</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:21</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en hyfsat grov gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1673,48 +1653,23 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129254871</v>
+        <v>129254205</v>
       </c>
       <c r="B11" t="n">
         <v>57727</v>
@@ -1749,10 +1704,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>486833</v>
+        <v>486752</v>
       </c>
       <c r="R11" t="n">
-        <v>7037850</v>
+        <v>7037802</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1789,7 +1744,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1804,19 +1759,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129254205</v>
+        <v>129254220</v>
       </c>
       <c r="B12" t="n">
         <v>57727</v>
@@ -1851,10 +1806,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>486752</v>
+        <v>486583</v>
       </c>
       <c r="R12" t="n">
-        <v>7037802</v>
+        <v>7038073</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1918,7 +1873,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129254220</v>
+        <v>129254215</v>
       </c>
       <c r="B13" t="n">
         <v>57727</v>
@@ -1953,10 +1908,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>486583</v>
+        <v>486524</v>
       </c>
       <c r="R13" t="n">
-        <v>7038073</v>
+        <v>7037917</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2020,7 +1975,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129254215</v>
+        <v>129243523</v>
       </c>
       <c r="B14" t="n">
         <v>57727</v>
@@ -2049,19 +2004,29 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>486524</v>
+        <v>486472</v>
       </c>
       <c r="R14" t="n">
-        <v>7037917</v>
+        <v>7037927</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2088,14 +2053,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack, äldre, på stambasen av en hyfsat grov gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2106,16 +2081,41 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2431,7 +2431,7 @@
         <v>129243687</v>
       </c>
       <c r="B18" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2663,10 +2663,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129242968</v>
+        <v>129254216</v>
       </c>
       <c r="B20" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2674,37 +2674,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>486617</v>
+        <v>486478</v>
       </c>
       <c r="R20" t="n">
-        <v>7037991</v>
+        <v>7037962</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2731,19 +2731,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>14:51</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>14:51</t>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2754,41 +2749,26 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129254216</v>
+        <v>129242968</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2796,37 +2776,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>486478</v>
+        <v>486617</v>
       </c>
       <c r="R21" t="n">
-        <v>7037962</v>
+        <v>7037991</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2853,14 +2833,19 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2871,16 +2856,31 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2890,7 +2890,7 @@
         <v>129254228</v>
       </c>
       <c r="B22" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3297,10 +3297,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129244388</v>
+        <v>129254874</v>
       </c>
       <c r="B26" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3308,34 +3308,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>486782</v>
+        <v>486550</v>
       </c>
       <c r="R26" t="n">
-        <v>7037877</v>
+        <v>7037929</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3365,24 +3365,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>15:53</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>15:53</t>
-        </is>
-      </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3393,28 +3383,23 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129254874</v>
+        <v>129254219</v>
       </c>
       <c r="B27" t="n">
         <v>57727</v>
@@ -3449,10 +3434,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>486550</v>
+        <v>486543</v>
       </c>
       <c r="R27" t="n">
-        <v>7037929</v>
+        <v>7037939</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3489,7 +3474,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3504,22 +3489,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129254219</v>
+        <v>129244388</v>
       </c>
       <c r="B28" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3527,34 +3512,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>486543</v>
+        <v>486782</v>
       </c>
       <c r="R28" t="n">
-        <v>7037939</v>
+        <v>7037877</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3584,14 +3569,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3602,16 +3597,21 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3954,7 +3954,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129254877</v>
+        <v>129254873</v>
       </c>
       <c r="B32" t="n">
         <v>57727</v>
@@ -3989,10 +3989,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>486495</v>
+        <v>486683</v>
       </c>
       <c r="R32" t="n">
-        <v>7037956</v>
+        <v>7037917</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4056,7 +4056,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129254204</v>
+        <v>129254877</v>
       </c>
       <c r="B33" t="n">
         <v>57727</v>
@@ -4091,10 +4091,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>486767</v>
+        <v>486495</v>
       </c>
       <c r="R33" t="n">
-        <v>7037800</v>
+        <v>7037956</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4131,7 +4131,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4146,19 +4146,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129254202</v>
+        <v>129254204</v>
       </c>
       <c r="B34" t="n">
         <v>57727</v>
@@ -4193,10 +4193,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>486780</v>
+        <v>486767</v>
       </c>
       <c r="R34" t="n">
-        <v>7037796</v>
+        <v>7037800</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4233,7 +4233,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4260,7 +4260,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129254207</v>
+        <v>129254202</v>
       </c>
       <c r="B35" t="n">
         <v>57727</v>
@@ -4295,10 +4295,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>486743</v>
+        <v>486780</v>
       </c>
       <c r="R35" t="n">
-        <v>7037808</v>
+        <v>7037796</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4362,7 +4362,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129254203</v>
+        <v>129254207</v>
       </c>
       <c r="B36" t="n">
         <v>57727</v>
@@ -4397,10 +4397,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>486775</v>
+        <v>486743</v>
       </c>
       <c r="R36" t="n">
-        <v>7037792</v>
+        <v>7037808</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4464,7 +4464,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129254873</v>
+        <v>129254203</v>
       </c>
       <c r="B37" t="n">
         <v>57727</v>
@@ -4499,10 +4499,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>486683</v>
+        <v>486775</v>
       </c>
       <c r="R37" t="n">
-        <v>7037917</v>
+        <v>7037792</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4539,7 +4539,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4554,12 +4554,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4668,10 +4668,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129254226</v>
+        <v>129244231</v>
       </c>
       <c r="B39" t="n">
-        <v>78057</v>
+        <v>79044</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4679,37 +4679,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>486585</v>
+        <v>486671</v>
       </c>
       <c r="R39" t="n">
-        <v>7038070</v>
+        <v>7037887</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4736,9 +4736,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4753,22 +4768,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129244231</v>
+        <v>129254226</v>
       </c>
       <c r="B40" t="n">
-        <v>79044</v>
+        <v>78057</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4776,37 +4791,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>486671</v>
+        <v>486585</v>
       </c>
       <c r="R40" t="n">
-        <v>7037887</v>
+        <v>7038070</v>
       </c>
       <c r="S40" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4833,24 +4848,9 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4865,22 +4865,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129243863</v>
+        <v>129254230</v>
       </c>
       <c r="B41" t="n">
-        <v>79044</v>
+        <v>82878</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4888,37 +4888,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>486663</v>
+        <v>486609</v>
       </c>
       <c r="R41" t="n">
-        <v>7037905</v>
+        <v>7038052</v>
       </c>
       <c r="S41" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4945,26 +4945,11 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Långväxta bålar, på flera granar.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -4973,96 +4958,61 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129243061</v>
+        <v>129254225</v>
       </c>
       <c r="B42" t="n">
-        <v>57727</v>
+        <v>80053</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>486568</v>
+        <v>486624</v>
       </c>
       <c r="R42" t="n">
-        <v>7037962</v>
+        <v>7038036</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5092,26 +5042,11 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen.</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5120,51 +5055,26 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129254230</v>
+        <v>129254879</v>
       </c>
       <c r="B43" t="n">
-        <v>82878</v>
+        <v>57727</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5172,21 +5082,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5196,10 +5106,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>486609</v>
+        <v>486552</v>
       </c>
       <c r="R43" t="n">
-        <v>7038052</v>
+        <v>7037942</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5234,6 +5144,11 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5246,44 +5161,44 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129254225</v>
+        <v>129254872</v>
       </c>
       <c r="B44" t="n">
-        <v>80053</v>
+        <v>57727</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5293,10 +5208,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>486624</v>
+        <v>486715</v>
       </c>
       <c r="R44" t="n">
-        <v>7038036</v>
+        <v>7037924</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5331,6 +5246,11 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5343,22 +5263,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129254879</v>
+        <v>129243863</v>
       </c>
       <c r="B45" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5366,37 +5286,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>486552</v>
+        <v>486663</v>
       </c>
       <c r="R45" t="n">
-        <v>7037942</v>
+        <v>7037905</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5423,14 +5343,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Långväxta bålar, på flera granar.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5441,23 +5371,48 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129254872</v>
+        <v>129243061</v>
       </c>
       <c r="B46" t="n">
         <v>57727</v>
@@ -5486,16 +5441,26 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>486715</v>
+        <v>486568</v>
       </c>
       <c r="R46" t="n">
-        <v>7037924</v>
+        <v>7037962</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5525,14 +5490,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5543,16 +5518,41 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5562,7 +5562,7 @@
         <v>129254227</v>
       </c>
       <c r="B47" t="n">
-        <v>91545</v>
+        <v>91546</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5656,10 +5656,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129254231</v>
+        <v>129254196</v>
       </c>
       <c r="B48" t="n">
-        <v>88949</v>
+        <v>83012</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5667,21 +5667,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>510</v>
+        <v>6440</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5691,10 +5691,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>486615</v>
+        <v>486582</v>
       </c>
       <c r="R48" t="n">
-        <v>7037875</v>
+        <v>7038072</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5753,32 +5753,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129254196</v>
+        <v>129254224</v>
       </c>
       <c r="B49" t="n">
-        <v>83012</v>
+        <v>80053</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6440</v>
+        <v>6456</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5788,10 +5788,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>486582</v>
+        <v>486599</v>
       </c>
       <c r="R49" t="n">
-        <v>7038072</v>
+        <v>7038068</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5850,32 +5850,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129254224</v>
+        <v>129254231</v>
       </c>
       <c r="B50" t="n">
-        <v>80053</v>
+        <v>88950</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6456</v>
+        <v>510</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5885,10 +5885,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>486599</v>
+        <v>486615</v>
       </c>
       <c r="R50" t="n">
-        <v>7038068</v>
+        <v>7037875</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>

--- a/artfynd/A 39541-2025 artfynd.xlsx
+++ b/artfynd/A 39541-2025 artfynd.xlsx
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129254218</v>
+        <v>129242015</v>
       </c>
       <c r="B3" t="n">
         <v>57727</v>
@@ -810,19 +810,29 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>486524</v>
+        <v>486782</v>
       </c>
       <c r="R3" t="n">
-        <v>7037965</v>
+        <v>7037909</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -849,14 +859,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,26 +887,51 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129254875</v>
+        <v>129241859</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -894,37 +939,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Tomasbodarna, Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486429</v>
+        <v>486860</v>
       </c>
       <c r="R4" t="n">
-        <v>7037954</v>
+        <v>7037938</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -951,14 +996,19 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -969,26 +1019,31 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129254206</v>
+        <v>129242509</v>
       </c>
       <c r="B5" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -996,37 +1051,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>486751</v>
+        <v>486672</v>
       </c>
       <c r="R5" t="n">
-        <v>7037804</v>
+        <v>7037952</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1053,14 +1108,19 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,16 +1131,21 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1196,10 +1261,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129241859</v>
+        <v>129254218</v>
       </c>
       <c r="B7" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1207,37 +1272,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tomasbodarna, Tomasbodarna, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>486860</v>
+        <v>486524</v>
       </c>
       <c r="R7" t="n">
-        <v>7037938</v>
+        <v>7037965</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1264,19 +1329,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>14:27</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:27</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1287,31 +1347,26 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129242509</v>
+        <v>129254875</v>
       </c>
       <c r="B8" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1319,37 +1374,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>486672</v>
+        <v>486429</v>
       </c>
       <c r="R8" t="n">
-        <v>7037952</v>
+        <v>7037954</v>
       </c>
       <c r="S8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1376,19 +1431,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>14:42</t>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1399,28 +1449,23 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129242015</v>
+        <v>129254206</v>
       </c>
       <c r="B9" t="n">
         <v>57727</v>
@@ -1449,29 +1494,19 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>486782</v>
+        <v>486751</v>
       </c>
       <c r="R9" t="n">
-        <v>7037909</v>
+        <v>7037804</v>
       </c>
       <c r="S9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1498,24 +1533,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,41 +1551,16 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -2887,10 +2887,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129254228</v>
+        <v>129254210</v>
       </c>
       <c r="B22" t="n">
-        <v>91570</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2898,19 +2898,23 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2918,10 +2922,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>486556</v>
+        <v>486650</v>
       </c>
       <c r="R22" t="n">
-        <v>7037879</v>
+        <v>7037866</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2954,6 +2958,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2980,10 +2989,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129254210</v>
+        <v>129254228</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>91570</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2991,23 +3000,19 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3015,10 +3020,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>486650</v>
+        <v>486556</v>
       </c>
       <c r="R23" t="n">
-        <v>7037866</v>
+        <v>7037879</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3051,11 +3056,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3297,10 +3297,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129254874</v>
+        <v>129244388</v>
       </c>
       <c r="B26" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3308,34 +3308,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>486550</v>
+        <v>486782</v>
       </c>
       <c r="R26" t="n">
-        <v>7037929</v>
+        <v>7037877</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3365,14 +3365,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3383,23 +3393,28 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129254219</v>
+        <v>129254874</v>
       </c>
       <c r="B27" t="n">
         <v>57727</v>
@@ -3434,10 +3449,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>486543</v>
+        <v>486550</v>
       </c>
       <c r="R27" t="n">
-        <v>7037939</v>
+        <v>7037929</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3474,7 +3489,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3489,22 +3504,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129244388</v>
+        <v>129254219</v>
       </c>
       <c r="B28" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3512,34 +3527,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>486782</v>
+        <v>486543</v>
       </c>
       <c r="R28" t="n">
-        <v>7037877</v>
+        <v>7037939</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3569,24 +3584,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>15:53</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>15:53</t>
-        </is>
-      </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3597,31 +3602,26 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129241899</v>
+        <v>129254201</v>
       </c>
       <c r="B29" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3629,34 +3629,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>486803</v>
+        <v>486797</v>
       </c>
       <c r="R29" t="n">
-        <v>7037939</v>
+        <v>7037788</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3686,24 +3686,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3714,43 +3704,23 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129254201</v>
+        <v>129254876</v>
       </c>
       <c r="B30" t="n">
         <v>57727</v>
@@ -3785,10 +3755,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>486797</v>
+        <v>486409</v>
       </c>
       <c r="R30" t="n">
-        <v>7037788</v>
+        <v>7037957</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3825,7 +3795,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3840,22 +3810,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129254876</v>
+        <v>129241899</v>
       </c>
       <c r="B31" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3863,34 +3833,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>486409</v>
+        <v>486803</v>
       </c>
       <c r="R31" t="n">
-        <v>7037957</v>
+        <v>7037939</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3920,14 +3890,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3938,23 +3918,43 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129254873</v>
+        <v>129254202</v>
       </c>
       <c r="B32" t="n">
         <v>57727</v>
@@ -3989,10 +3989,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>486683</v>
+        <v>486780</v>
       </c>
       <c r="R32" t="n">
-        <v>7037917</v>
+        <v>7037796</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4044,19 +4044,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129254877</v>
+        <v>129254207</v>
       </c>
       <c r="B33" t="n">
         <v>57727</v>
@@ -4091,10 +4091,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>486495</v>
+        <v>486743</v>
       </c>
       <c r="R33" t="n">
-        <v>7037956</v>
+        <v>7037808</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4131,7 +4131,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4146,19 +4146,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129254204</v>
+        <v>129254873</v>
       </c>
       <c r="B34" t="n">
         <v>57727</v>
@@ -4193,10 +4193,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>486767</v>
+        <v>486683</v>
       </c>
       <c r="R34" t="n">
-        <v>7037800</v>
+        <v>7037917</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4233,7 +4233,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4248,19 +4248,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129254202</v>
+        <v>129254877</v>
       </c>
       <c r="B35" t="n">
         <v>57727</v>
@@ -4295,10 +4295,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>486780</v>
+        <v>486495</v>
       </c>
       <c r="R35" t="n">
-        <v>7037796</v>
+        <v>7037956</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4335,7 +4335,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4350,19 +4350,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129254207</v>
+        <v>129254204</v>
       </c>
       <c r="B36" t="n">
         <v>57727</v>
@@ -4397,10 +4397,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>486743</v>
+        <v>486767</v>
       </c>
       <c r="R36" t="n">
-        <v>7037808</v>
+        <v>7037800</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4437,7 +4437,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4877,10 +4877,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129254230</v>
+        <v>129243061</v>
       </c>
       <c r="B41" t="n">
-        <v>82878</v>
+        <v>57727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4888,34 +4888,44 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>486609</v>
+        <v>486568</v>
       </c>
       <c r="R41" t="n">
-        <v>7038052</v>
+        <v>7037962</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4945,11 +4955,26 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -4958,16 +4983,41 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5071,10 +5121,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129254879</v>
+        <v>129243863</v>
       </c>
       <c r="B43" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5082,37 +5132,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>486552</v>
+        <v>486663</v>
       </c>
       <c r="R43" t="n">
-        <v>7037942</v>
+        <v>7037905</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5139,14 +5189,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Långväxta bålar, på flera granar.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5157,26 +5217,51 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129254872</v>
+        <v>129254230</v>
       </c>
       <c r="B44" t="n">
-        <v>57727</v>
+        <v>82878</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5184,21 +5269,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5208,10 +5293,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>486715</v>
+        <v>486609</v>
       </c>
       <c r="R44" t="n">
-        <v>7037924</v>
+        <v>7038052</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5246,11 +5331,6 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5263,22 +5343,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129243863</v>
+        <v>129254879</v>
       </c>
       <c r="B45" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5286,37 +5366,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>486663</v>
+        <v>486552</v>
       </c>
       <c r="R45" t="n">
-        <v>7037905</v>
+        <v>7037942</v>
       </c>
       <c r="S45" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5343,24 +5423,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Långväxta bålar, på flera granar.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5371,48 +5441,23 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129243061</v>
+        <v>129254872</v>
       </c>
       <c r="B46" t="n">
         <v>57727</v>
@@ -5441,26 +5486,16 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>486568</v>
+        <v>486715</v>
       </c>
       <c r="R46" t="n">
-        <v>7037962</v>
+        <v>7037924</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5490,24 +5525,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5518,41 +5543,16 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5656,10 +5656,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129254196</v>
+        <v>129254231</v>
       </c>
       <c r="B48" t="n">
-        <v>83012</v>
+        <v>88950</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5667,21 +5667,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6440</v>
+        <v>510</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5691,10 +5691,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>486582</v>
+        <v>486615</v>
       </c>
       <c r="R48" t="n">
-        <v>7038072</v>
+        <v>7037875</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5753,32 +5753,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129254224</v>
+        <v>129254214</v>
       </c>
       <c r="B49" t="n">
-        <v>80053</v>
+        <v>57727</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5788,10 +5788,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>486599</v>
+        <v>486551</v>
       </c>
       <c r="R49" t="n">
-        <v>7038068</v>
+        <v>7037889</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5824,6 +5824,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5850,10 +5855,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129254231</v>
+        <v>129254196</v>
       </c>
       <c r="B50" t="n">
-        <v>88950</v>
+        <v>83012</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5861,21 +5866,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>510</v>
+        <v>6440</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5885,10 +5890,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>486615</v>
+        <v>486582</v>
       </c>
       <c r="R50" t="n">
-        <v>7037875</v>
+        <v>7038072</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5947,32 +5952,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129254214</v>
+        <v>129254224</v>
       </c>
       <c r="B51" t="n">
-        <v>57727</v>
+        <v>80053</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5982,10 +5987,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>486551</v>
+        <v>486599</v>
       </c>
       <c r="R51" t="n">
-        <v>7037889</v>
+        <v>7038068</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6018,11 +6023,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6355,10 +6355,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129254878</v>
+        <v>129243772</v>
       </c>
       <c r="B55" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6366,37 +6366,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>486553</v>
+        <v>486608</v>
       </c>
       <c r="R55" t="n">
-        <v>7037937</v>
+        <v>7037908</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6423,14 +6423,19 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6441,26 +6446,51 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129243772</v>
+        <v>129254878</v>
       </c>
       <c r="B56" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6468,37 +6498,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>486608</v>
+        <v>486553</v>
       </c>
       <c r="R56" t="n">
-        <v>7037908</v>
+        <v>7037937</v>
       </c>
       <c r="S56" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6525,19 +6555,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>15:38</t>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6548,41 +6573,16 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>

--- a/artfynd/A 39541-2025 artfynd.xlsx
+++ b/artfynd/A 39541-2025 artfynd.xlsx
@@ -1152,27 +1152,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129254223</v>
+        <v>129254218</v>
       </c>
       <c r="B6" t="n">
-        <v>57568</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1180,29 +1180,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>486737</v>
+        <v>486524</v>
       </c>
       <c r="R6" t="n">
-        <v>7037835</v>
+        <v>7037965</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1235,6 +1223,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1261,7 +1254,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129254218</v>
+        <v>129254875</v>
       </c>
       <c r="B7" t="n">
         <v>57727</v>
@@ -1296,10 +1289,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>486524</v>
+        <v>486429</v>
       </c>
       <c r="R7" t="n">
-        <v>7037965</v>
+        <v>7037954</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1336,7 +1329,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,19 +1344,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129254875</v>
+        <v>129254206</v>
       </c>
       <c r="B8" t="n">
         <v>57727</v>
@@ -1398,10 +1391,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>486429</v>
+        <v>486751</v>
       </c>
       <c r="R8" t="n">
-        <v>7037954</v>
+        <v>7037804</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1438,7 +1431,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1453,39 +1446,39 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129254206</v>
+        <v>129254223</v>
       </c>
       <c r="B9" t="n">
-        <v>57727</v>
+        <v>57568</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1493,17 +1486,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>486751</v>
+        <v>486737</v>
       </c>
       <c r="R9" t="n">
-        <v>7037804</v>
+        <v>7037835</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1536,11 +1541,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1567,7 +1567,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129254871</v>
+        <v>129243523</v>
       </c>
       <c r="B10" t="n">
         <v>57727</v>
@@ -1596,19 +1596,29 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>486833</v>
+        <v>486472</v>
       </c>
       <c r="R10" t="n">
-        <v>7037850</v>
+        <v>7037927</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1635,14 +1645,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre, på stambasen av en hyfsat grov gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,23 +1673,48 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129254205</v>
+        <v>129254871</v>
       </c>
       <c r="B11" t="n">
         <v>57727</v>
@@ -1704,10 +1749,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>486752</v>
+        <v>486833</v>
       </c>
       <c r="R11" t="n">
-        <v>7037802</v>
+        <v>7037850</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1744,7 +1789,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1759,19 +1804,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129254220</v>
+        <v>129254205</v>
       </c>
       <c r="B12" t="n">
         <v>57727</v>
@@ -1806,10 +1851,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>486583</v>
+        <v>486752</v>
       </c>
       <c r="R12" t="n">
-        <v>7038073</v>
+        <v>7037802</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1873,7 +1918,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129254215</v>
+        <v>129254220</v>
       </c>
       <c r="B13" t="n">
         <v>57727</v>
@@ -1908,10 +1953,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>486524</v>
+        <v>486583</v>
       </c>
       <c r="R13" t="n">
-        <v>7037917</v>
+        <v>7038073</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1975,7 +2020,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129243523</v>
+        <v>129254215</v>
       </c>
       <c r="B14" t="n">
         <v>57727</v>
@@ -2004,29 +2049,19 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>486472</v>
+        <v>486524</v>
       </c>
       <c r="R14" t="n">
-        <v>7037927</v>
+        <v>7037917</v>
       </c>
       <c r="S14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2053,24 +2088,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>15:21</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>15:21</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en hyfsat grov gran.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2081,41 +2106,16 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2224,48 +2224,68 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129254211</v>
+        <v>129243687</v>
       </c>
       <c r="B16" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>486582</v>
+        <v>486517</v>
       </c>
       <c r="R16" t="n">
-        <v>7037881</v>
+        <v>7037922</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2292,14 +2312,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Minst 120 plantor och 1 fröställning inom ca 1 m2 yta  intill en naturvårdsnitslad björk.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2308,25 +2338,31 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129254221</v>
+        <v>129254211</v>
       </c>
       <c r="B17" t="n">
         <v>57727</v>
@@ -2361,10 +2397,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>486595</v>
+        <v>486582</v>
       </c>
       <c r="R17" t="n">
-        <v>7038075</v>
+        <v>7037881</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2428,68 +2464,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129243687</v>
+        <v>129254221</v>
       </c>
       <c r="B18" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>486517</v>
+        <v>486595</v>
       </c>
       <c r="R18" t="n">
-        <v>7037922</v>
+        <v>7038075</v>
       </c>
       <c r="S18" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2516,24 +2532,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>15:26</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>15:26</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Minst 120 plantor och 1 fröställning inom ca 1 m2 yta  intill en naturvårdsnitslad björk.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2542,24 +2548,18 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2663,10 +2663,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129254216</v>
+        <v>129242968</v>
       </c>
       <c r="B20" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2674,37 +2674,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>486478</v>
+        <v>486617</v>
       </c>
       <c r="R20" t="n">
-        <v>7037962</v>
+        <v>7037991</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2731,14 +2731,19 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2749,26 +2754,41 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129242968</v>
+        <v>129254216</v>
       </c>
       <c r="B21" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2776,37 +2796,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>486617</v>
+        <v>486478</v>
       </c>
       <c r="R21" t="n">
-        <v>7037991</v>
+        <v>7037962</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2833,19 +2853,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>14:51</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>14:51</t>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2856,31 +2871,16 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3297,10 +3297,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129244388</v>
+        <v>129254874</v>
       </c>
       <c r="B26" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3308,34 +3308,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>486782</v>
+        <v>486550</v>
       </c>
       <c r="R26" t="n">
-        <v>7037877</v>
+        <v>7037929</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3365,24 +3365,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>15:53</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>15:53</t>
-        </is>
-      </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3393,28 +3383,23 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129254874</v>
+        <v>129254219</v>
       </c>
       <c r="B27" t="n">
         <v>57727</v>
@@ -3449,10 +3434,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>486550</v>
+        <v>486543</v>
       </c>
       <c r="R27" t="n">
-        <v>7037929</v>
+        <v>7037939</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3489,7 +3474,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3504,22 +3489,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129254219</v>
+        <v>129244388</v>
       </c>
       <c r="B28" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3527,34 +3512,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>486543</v>
+        <v>486782</v>
       </c>
       <c r="R28" t="n">
-        <v>7037939</v>
+        <v>7037877</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3584,14 +3569,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3602,26 +3597,31 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129254201</v>
+        <v>129241899</v>
       </c>
       <c r="B29" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3629,34 +3629,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>486797</v>
+        <v>486803</v>
       </c>
       <c r="R29" t="n">
-        <v>7037788</v>
+        <v>7037939</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3686,14 +3686,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3704,23 +3714,43 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129254876</v>
+        <v>129254201</v>
       </c>
       <c r="B30" t="n">
         <v>57727</v>
@@ -3755,10 +3785,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>486409</v>
+        <v>486797</v>
       </c>
       <c r="R30" t="n">
-        <v>7037957</v>
+        <v>7037788</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3795,7 +3825,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3810,22 +3840,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129241899</v>
+        <v>129254876</v>
       </c>
       <c r="B31" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3833,34 +3863,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>486803</v>
+        <v>486409</v>
       </c>
       <c r="R31" t="n">
-        <v>7037939</v>
+        <v>7037957</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3890,24 +3920,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3918,43 +3938,23 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129254202</v>
+        <v>129254873</v>
       </c>
       <c r="B32" t="n">
         <v>57727</v>
@@ -3989,10 +3989,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>486780</v>
+        <v>486683</v>
       </c>
       <c r="R32" t="n">
-        <v>7037796</v>
+        <v>7037917</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4044,19 +4044,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129254207</v>
+        <v>129254877</v>
       </c>
       <c r="B33" t="n">
         <v>57727</v>
@@ -4091,10 +4091,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>486743</v>
+        <v>486495</v>
       </c>
       <c r="R33" t="n">
-        <v>7037808</v>
+        <v>7037956</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4131,7 +4131,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4146,19 +4146,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129254873</v>
+        <v>129254204</v>
       </c>
       <c r="B34" t="n">
         <v>57727</v>
@@ -4193,10 +4193,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>486683</v>
+        <v>486767</v>
       </c>
       <c r="R34" t="n">
-        <v>7037917</v>
+        <v>7037800</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4233,7 +4233,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4248,19 +4248,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129254877</v>
+        <v>129254202</v>
       </c>
       <c r="B35" t="n">
         <v>57727</v>
@@ -4295,10 +4295,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>486495</v>
+        <v>486780</v>
       </c>
       <c r="R35" t="n">
-        <v>7037956</v>
+        <v>7037796</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4335,7 +4335,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4350,19 +4350,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129254204</v>
+        <v>129254207</v>
       </c>
       <c r="B36" t="n">
         <v>57727</v>
@@ -4397,10 +4397,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>486767</v>
+        <v>486743</v>
       </c>
       <c r="R36" t="n">
-        <v>7037800</v>
+        <v>7037808</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4437,7 +4437,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4668,10 +4668,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129244231</v>
+        <v>129254226</v>
       </c>
       <c r="B39" t="n">
-        <v>79044</v>
+        <v>78057</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4679,37 +4679,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>486671</v>
+        <v>486585</v>
       </c>
       <c r="R39" t="n">
-        <v>7037887</v>
+        <v>7038070</v>
       </c>
       <c r="S39" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4736,24 +4736,9 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4768,22 +4753,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129254226</v>
+        <v>129244231</v>
       </c>
       <c r="B40" t="n">
-        <v>78057</v>
+        <v>79044</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4791,37 +4776,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>486585</v>
+        <v>486671</v>
       </c>
       <c r="R40" t="n">
-        <v>7038070</v>
+        <v>7037887</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4848,9 +4833,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4865,12 +4865,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>

--- a/artfynd/A 39541-2025 artfynd.xlsx
+++ b/artfynd/A 39541-2025 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129242015</v>
+        <v>129241859</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,47 +792,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
+          <t>Tomasbodarna, Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>486782</v>
+        <v>486860</v>
       </c>
       <c r="R3" t="n">
-        <v>7037909</v>
+        <v>7037938</v>
       </c>
       <c r="S3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,7 +851,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -871,12 +861,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,27 +875,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -928,7 +893,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129241859</v>
+        <v>129242509</v>
       </c>
       <c r="B4" t="n">
         <v>79044</v>
@@ -959,17 +924,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tomasbodarna, Tomasbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486860</v>
+        <v>486672</v>
       </c>
       <c r="R4" t="n">
-        <v>7037938</v>
+        <v>7037952</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -998,7 +963,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,7 +973,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129242509</v>
+        <v>129242015</v>
       </c>
       <c r="B5" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1051,34 +1016,44 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>486672</v>
+        <v>486782</v>
       </c>
       <c r="R5" t="n">
-        <v>7037952</v>
+        <v>7037909</v>
       </c>
       <c r="S5" t="n">
         <v>11</v>
@@ -1110,7 +1085,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,7 +1095,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,7 +1114,27 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1152,27 +1152,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129254218</v>
+        <v>129254223</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>57568</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1180,17 +1180,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>486524</v>
+        <v>486737</v>
       </c>
       <c r="R6" t="n">
-        <v>7037965</v>
+        <v>7037835</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1223,11 +1235,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,7 +1261,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129254875</v>
+        <v>129254218</v>
       </c>
       <c r="B7" t="n">
         <v>57727</v>
@@ -1289,10 +1296,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>486429</v>
+        <v>486524</v>
       </c>
       <c r="R7" t="n">
-        <v>7037954</v>
+        <v>7037965</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1329,7 +1336,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1344,19 +1351,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129254206</v>
+        <v>129254875</v>
       </c>
       <c r="B8" t="n">
         <v>57727</v>
@@ -1391,10 +1398,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>486751</v>
+        <v>486429</v>
       </c>
       <c r="R8" t="n">
-        <v>7037804</v>
+        <v>7037954</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1431,7 +1438,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1446,39 +1453,39 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129254223</v>
+        <v>129254206</v>
       </c>
       <c r="B9" t="n">
-        <v>57568</v>
+        <v>57727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1486,29 +1493,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>486737</v>
+        <v>486751</v>
       </c>
       <c r="R9" t="n">
-        <v>7037835</v>
+        <v>7037804</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1541,6 +1536,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1567,7 +1567,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129243523</v>
+        <v>129254871</v>
       </c>
       <c r="B10" t="n">
         <v>57727</v>
@@ -1596,29 +1596,19 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>486472</v>
+        <v>486833</v>
       </c>
       <c r="R10" t="n">
-        <v>7037927</v>
+        <v>7037850</v>
       </c>
       <c r="S10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1645,24 +1635,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>15:21</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:21</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en hyfsat grov gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1673,48 +1653,23 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129254871</v>
+        <v>129254205</v>
       </c>
       <c r="B11" t="n">
         <v>57727</v>
@@ -1749,10 +1704,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>486833</v>
+        <v>486752</v>
       </c>
       <c r="R11" t="n">
-        <v>7037850</v>
+        <v>7037802</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1789,7 +1744,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1804,19 +1759,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129254205</v>
+        <v>129254220</v>
       </c>
       <c r="B12" t="n">
         <v>57727</v>
@@ -1851,10 +1806,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>486752</v>
+        <v>486583</v>
       </c>
       <c r="R12" t="n">
-        <v>7037802</v>
+        <v>7038073</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1918,7 +1873,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129254220</v>
+        <v>129254215</v>
       </c>
       <c r="B13" t="n">
         <v>57727</v>
@@ -1953,10 +1908,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>486583</v>
+        <v>486524</v>
       </c>
       <c r="R13" t="n">
-        <v>7038073</v>
+        <v>7037917</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2020,7 +1975,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129254215</v>
+        <v>129243523</v>
       </c>
       <c r="B14" t="n">
         <v>57727</v>
@@ -2049,19 +2004,29 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>486524</v>
+        <v>486472</v>
       </c>
       <c r="R14" t="n">
-        <v>7037917</v>
+        <v>7037927</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2088,14 +2053,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack, äldre, på stambasen av en hyfsat grov gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2106,16 +2081,41 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2227,7 +2227,7 @@
         <v>129243687</v>
       </c>
       <c r="B16" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2887,10 +2887,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129254210</v>
+        <v>129254228</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>91573</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2898,23 +2898,19 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2922,10 +2918,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>486650</v>
+        <v>486556</v>
       </c>
       <c r="R22" t="n">
-        <v>7037866</v>
+        <v>7037879</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2958,11 +2954,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2989,10 +2980,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129254228</v>
+        <v>129254210</v>
       </c>
       <c r="B23" t="n">
-        <v>91570</v>
+        <v>57727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3000,19 +2991,23 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3020,10 +3015,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>486556</v>
+        <v>486650</v>
       </c>
       <c r="R23" t="n">
-        <v>7037879</v>
+        <v>7037866</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3056,6 +3051,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3297,10 +3297,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129254874</v>
+        <v>129244388</v>
       </c>
       <c r="B26" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3308,34 +3308,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>486550</v>
+        <v>486782</v>
       </c>
       <c r="R26" t="n">
-        <v>7037929</v>
+        <v>7037877</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3365,14 +3365,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3383,23 +3393,28 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129254219</v>
+        <v>129254874</v>
       </c>
       <c r="B27" t="n">
         <v>57727</v>
@@ -3434,10 +3449,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>486543</v>
+        <v>486550</v>
       </c>
       <c r="R27" t="n">
-        <v>7037939</v>
+        <v>7037929</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3474,7 +3489,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3489,22 +3504,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129244388</v>
+        <v>129254219</v>
       </c>
       <c r="B28" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3512,34 +3527,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>486782</v>
+        <v>486543</v>
       </c>
       <c r="R28" t="n">
-        <v>7037877</v>
+        <v>7037939</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3569,24 +3584,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>15:53</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>15:53</t>
-        </is>
-      </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3597,21 +3602,16 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -4877,10 +4877,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129243061</v>
+        <v>129243863</v>
       </c>
       <c r="B41" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4888,47 +4888,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>486568</v>
+        <v>486663</v>
       </c>
       <c r="R41" t="n">
-        <v>7037962</v>
+        <v>7037905</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4957,7 +4947,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4967,12 +4957,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Långväxta bålar, på flera granar.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4986,7 +4976,7 @@
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ41" t="inlineStr">
@@ -5001,12 +4991,12 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5024,45 +5014,55 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129254225</v>
+        <v>129243061</v>
       </c>
       <c r="B42" t="n">
-        <v>80053</v>
+        <v>57727</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>486624</v>
+        <v>486568</v>
       </c>
       <c r="R42" t="n">
-        <v>7038036</v>
+        <v>7037962</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5092,11 +5092,26 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5105,26 +5120,51 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129243863</v>
+        <v>129254230</v>
       </c>
       <c r="B43" t="n">
-        <v>79044</v>
+        <v>82878</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5132,37 +5172,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>486663</v>
+        <v>486609</v>
       </c>
       <c r="R43" t="n">
-        <v>7037905</v>
+        <v>7038052</v>
       </c>
       <c r="S43" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5189,26 +5229,11 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Långväxta bålar, på flera granar.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5217,73 +5242,48 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129254230</v>
+        <v>129254225</v>
       </c>
       <c r="B44" t="n">
-        <v>82878</v>
+        <v>80053</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1312</v>
+        <v>6456</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5293,10 +5293,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>486609</v>
+        <v>486624</v>
       </c>
       <c r="R44" t="n">
-        <v>7038052</v>
+        <v>7038036</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5562,7 +5562,7 @@
         <v>129254227</v>
       </c>
       <c r="B47" t="n">
-        <v>91546</v>
+        <v>91549</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         <v>129254231</v>
       </c>
       <c r="B48" t="n">
-        <v>88950</v>
+        <v>88952</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5753,10 +5753,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129254214</v>
+        <v>129254196</v>
       </c>
       <c r="B49" t="n">
-        <v>57727</v>
+        <v>83012</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5764,21 +5764,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5788,10 +5788,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>486551</v>
+        <v>486582</v>
       </c>
       <c r="R49" t="n">
-        <v>7037889</v>
+        <v>7038072</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5824,11 +5824,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5855,32 +5850,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129254196</v>
+        <v>129254224</v>
       </c>
       <c r="B50" t="n">
-        <v>83012</v>
+        <v>80053</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6440</v>
+        <v>6456</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5890,10 +5885,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>486582</v>
+        <v>486599</v>
       </c>
       <c r="R50" t="n">
-        <v>7038072</v>
+        <v>7038068</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5952,32 +5947,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129254224</v>
+        <v>129254214</v>
       </c>
       <c r="B51" t="n">
-        <v>80053</v>
+        <v>57727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5987,10 +5982,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>486599</v>
+        <v>486551</v>
       </c>
       <c r="R51" t="n">
-        <v>7038068</v>
+        <v>7037889</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6023,6 +6018,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6355,10 +6355,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129243772</v>
+        <v>129254878</v>
       </c>
       <c r="B55" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6366,37 +6366,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>486608</v>
+        <v>486553</v>
       </c>
       <c r="R55" t="n">
-        <v>7037908</v>
+        <v>7037937</v>
       </c>
       <c r="S55" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6423,19 +6423,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>15:38</t>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6446,51 +6441,26 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129254878</v>
+        <v>129243772</v>
       </c>
       <c r="B56" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6498,37 +6468,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>486553</v>
+        <v>486608</v>
       </c>
       <c r="R56" t="n">
-        <v>7037937</v>
+        <v>7037908</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6555,14 +6525,19 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6573,16 +6548,41 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>

--- a/artfynd/A 39541-2025 artfynd.xlsx
+++ b/artfynd/A 39541-2025 artfynd.xlsx
@@ -781,48 +781,60 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129241859</v>
+        <v>129254223</v>
       </c>
       <c r="B3" t="n">
-        <v>79044</v>
+        <v>57568</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>102621</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tomasbodarna, Tomasbodarna, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>486860</v>
+        <v>486737</v>
       </c>
       <c r="R3" t="n">
-        <v>7037938</v>
+        <v>7037835</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -849,21 +861,11 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:27</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:27</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -872,28 +874,23 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129242509</v>
+        <v>129241859</v>
       </c>
       <c r="B4" t="n">
         <v>79044</v>
@@ -924,17 +921,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Tomasbodarna, Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486672</v>
+        <v>486860</v>
       </c>
       <c r="R4" t="n">
-        <v>7037952</v>
+        <v>7037938</v>
       </c>
       <c r="S4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -963,7 +960,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -973,7 +970,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,7 +1002,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129242015</v>
+        <v>129254206</v>
       </c>
       <c r="B5" t="n">
         <v>57727</v>
@@ -1034,29 +1031,19 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>486782</v>
+        <v>486751</v>
       </c>
       <c r="R5" t="n">
-        <v>7037909</v>
+        <v>7037804</v>
       </c>
       <c r="S5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,24 +1070,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,68 +1088,43 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129254223</v>
+        <v>129254218</v>
       </c>
       <c r="B6" t="n">
-        <v>57568</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1180,29 +1132,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>486737</v>
+        <v>486524</v>
       </c>
       <c r="R6" t="n">
-        <v>7037835</v>
+        <v>7037965</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1235,6 +1175,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1261,7 +1206,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129254218</v>
+        <v>129254875</v>
       </c>
       <c r="B7" t="n">
         <v>57727</v>
@@ -1296,10 +1241,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>486524</v>
+        <v>486429</v>
       </c>
       <c r="R7" t="n">
-        <v>7037965</v>
+        <v>7037954</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1336,7 +1281,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,22 +1296,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129254875</v>
+        <v>129242509</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1374,37 +1319,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>486429</v>
+        <v>486672</v>
       </c>
       <c r="R8" t="n">
-        <v>7037954</v>
+        <v>7037952</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1431,14 +1376,19 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1449,23 +1399,28 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129254206</v>
+        <v>129242015</v>
       </c>
       <c r="B9" t="n">
         <v>57727</v>
@@ -1494,19 +1449,29 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>486751</v>
+        <v>486782</v>
       </c>
       <c r="R9" t="n">
-        <v>7037804</v>
+        <v>7037909</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1533,14 +1498,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1551,23 +1526,48 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129254871</v>
+        <v>129243523</v>
       </c>
       <c r="B10" t="n">
         <v>57727</v>
@@ -1596,19 +1596,29 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>486833</v>
+        <v>486472</v>
       </c>
       <c r="R10" t="n">
-        <v>7037850</v>
+        <v>7037927</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1635,14 +1645,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre, på stambasen av en hyfsat grov gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,16 +1673,41 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1771,7 +1816,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129254220</v>
+        <v>129254215</v>
       </c>
       <c r="B12" t="n">
         <v>57727</v>
@@ -1806,10 +1851,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>486583</v>
+        <v>486524</v>
       </c>
       <c r="R12" t="n">
-        <v>7038073</v>
+        <v>7037917</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1873,7 +1918,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129254215</v>
+        <v>129254871</v>
       </c>
       <c r="B13" t="n">
         <v>57727</v>
@@ -1908,10 +1953,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>486524</v>
+        <v>486833</v>
       </c>
       <c r="R13" t="n">
-        <v>7037917</v>
+        <v>7037850</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1948,7 +1993,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1963,19 +2008,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129243523</v>
+        <v>129254220</v>
       </c>
       <c r="B14" t="n">
         <v>57727</v>
@@ -2004,29 +2049,19 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>486472</v>
+        <v>486583</v>
       </c>
       <c r="R14" t="n">
-        <v>7037927</v>
+        <v>7038073</v>
       </c>
       <c r="S14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2053,24 +2088,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>15:21</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>15:21</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en hyfsat grov gran.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2081,41 +2106,16 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2362,7 +2362,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129254211</v>
+        <v>129254221</v>
       </c>
       <c r="B17" t="n">
         <v>57727</v>
@@ -2397,10 +2397,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>486582</v>
+        <v>486595</v>
       </c>
       <c r="R17" t="n">
-        <v>7037881</v>
+        <v>7038075</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2464,7 +2464,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129254221</v>
+        <v>129254211</v>
       </c>
       <c r="B18" t="n">
         <v>57727</v>
@@ -2499,10 +2499,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>486595</v>
+        <v>486582</v>
       </c>
       <c r="R18" t="n">
-        <v>7038075</v>
+        <v>7037881</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2663,10 +2663,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129242968</v>
+        <v>129254216</v>
       </c>
       <c r="B20" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2674,37 +2674,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>486617</v>
+        <v>486478</v>
       </c>
       <c r="R20" t="n">
-        <v>7037991</v>
+        <v>7037962</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2731,19 +2731,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>14:51</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>14:51</t>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2754,41 +2749,26 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129254216</v>
+        <v>129242968</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2796,37 +2776,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>486478</v>
+        <v>486617</v>
       </c>
       <c r="R21" t="n">
-        <v>7037962</v>
+        <v>7037991</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2853,14 +2833,19 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2871,26 +2856,41 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129254228</v>
+        <v>129254210</v>
       </c>
       <c r="B22" t="n">
-        <v>91573</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2898,19 +2898,23 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2918,10 +2922,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>486556</v>
+        <v>486650</v>
       </c>
       <c r="R22" t="n">
-        <v>7037879</v>
+        <v>7037866</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2954,6 +2958,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2980,10 +2989,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129254210</v>
+        <v>129254222</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2991,34 +3000,50 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>486650</v>
+        <v>486607</v>
       </c>
       <c r="R23" t="n">
-        <v>7037866</v>
+        <v>7038047</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3051,11 +3076,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3082,10 +3102,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129254222</v>
+        <v>129254228</v>
       </c>
       <c r="B24" t="n">
-        <v>57887</v>
+        <v>91573</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3093,50 +3113,30 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>486607</v>
+        <v>486556</v>
       </c>
       <c r="R24" t="n">
-        <v>7038047</v>
+        <v>7037879</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3297,10 +3297,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129244388</v>
+        <v>129254874</v>
       </c>
       <c r="B26" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3308,34 +3308,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>486782</v>
+        <v>486550</v>
       </c>
       <c r="R26" t="n">
-        <v>7037877</v>
+        <v>7037929</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3365,24 +3365,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>15:53</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>15:53</t>
-        </is>
-      </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3393,31 +3383,26 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129254874</v>
+        <v>129244388</v>
       </c>
       <c r="B27" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3425,34 +3410,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>486550</v>
+        <v>486782</v>
       </c>
       <c r="R27" t="n">
-        <v>7037929</v>
+        <v>7037877</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3482,14 +3467,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3500,16 +3495,21 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3618,10 +3618,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129241899</v>
+        <v>129254201</v>
       </c>
       <c r="B29" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3629,34 +3629,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>486803</v>
+        <v>486797</v>
       </c>
       <c r="R29" t="n">
-        <v>7037939</v>
+        <v>7037788</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3686,24 +3686,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3714,43 +3704,23 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129254201</v>
+        <v>129254876</v>
       </c>
       <c r="B30" t="n">
         <v>57727</v>
@@ -3785,10 +3755,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>486797</v>
+        <v>486409</v>
       </c>
       <c r="R30" t="n">
-        <v>7037788</v>
+        <v>7037957</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3825,7 +3795,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3840,22 +3810,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129254876</v>
+        <v>129241899</v>
       </c>
       <c r="B31" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3863,34 +3833,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>486409</v>
+        <v>486803</v>
       </c>
       <c r="R31" t="n">
-        <v>7037957</v>
+        <v>7037939</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3920,14 +3890,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3938,23 +3918,43 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129254873</v>
+        <v>129254204</v>
       </c>
       <c r="B32" t="n">
         <v>57727</v>
@@ -3989,10 +3989,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>486683</v>
+        <v>486767</v>
       </c>
       <c r="R32" t="n">
-        <v>7037917</v>
+        <v>7037800</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4044,19 +4044,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129254877</v>
+        <v>129254202</v>
       </c>
       <c r="B33" t="n">
         <v>57727</v>
@@ -4091,10 +4091,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>486495</v>
+        <v>486780</v>
       </c>
       <c r="R33" t="n">
-        <v>7037956</v>
+        <v>7037796</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4131,7 +4131,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4146,19 +4146,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129254204</v>
+        <v>129254207</v>
       </c>
       <c r="B34" t="n">
         <v>57727</v>
@@ -4193,10 +4193,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>486767</v>
+        <v>486743</v>
       </c>
       <c r="R34" t="n">
-        <v>7037800</v>
+        <v>7037808</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4233,7 +4233,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4260,7 +4260,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129254202</v>
+        <v>129254873</v>
       </c>
       <c r="B35" t="n">
         <v>57727</v>
@@ -4295,10 +4295,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>486780</v>
+        <v>486683</v>
       </c>
       <c r="R35" t="n">
-        <v>7037796</v>
+        <v>7037917</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4335,7 +4335,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4350,19 +4350,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129254207</v>
+        <v>129254877</v>
       </c>
       <c r="B36" t="n">
         <v>57727</v>
@@ -4397,10 +4397,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>486743</v>
+        <v>486495</v>
       </c>
       <c r="R36" t="n">
-        <v>7037808</v>
+        <v>7037956</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4437,7 +4437,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4452,12 +4452,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4668,10 +4668,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129254226</v>
+        <v>129244231</v>
       </c>
       <c r="B39" t="n">
-        <v>78057</v>
+        <v>79044</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4679,37 +4679,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>486585</v>
+        <v>486671</v>
       </c>
       <c r="R39" t="n">
-        <v>7038070</v>
+        <v>7037887</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4736,9 +4736,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4753,22 +4768,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129244231</v>
+        <v>129254226</v>
       </c>
       <c r="B40" t="n">
-        <v>79044</v>
+        <v>78057</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4776,37 +4791,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>486671</v>
+        <v>486585</v>
       </c>
       <c r="R40" t="n">
-        <v>7037887</v>
+        <v>7038070</v>
       </c>
       <c r="S40" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4833,24 +4848,9 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4865,22 +4865,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129243863</v>
+        <v>129254230</v>
       </c>
       <c r="B41" t="n">
-        <v>79044</v>
+        <v>82878</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4888,37 +4888,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>486663</v>
+        <v>486609</v>
       </c>
       <c r="R41" t="n">
-        <v>7037905</v>
+        <v>7038052</v>
       </c>
       <c r="S41" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4945,26 +4945,11 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Långväxta bålar, på flera granar.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -4973,96 +4958,61 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129243061</v>
+        <v>129254225</v>
       </c>
       <c r="B42" t="n">
-        <v>57727</v>
+        <v>80053</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>486568</v>
+        <v>486624</v>
       </c>
       <c r="R42" t="n">
-        <v>7037962</v>
+        <v>7038036</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5092,26 +5042,11 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen.</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5120,51 +5055,26 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129254230</v>
+        <v>129254879</v>
       </c>
       <c r="B43" t="n">
-        <v>82878</v>
+        <v>57727</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5172,21 +5082,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5196,10 +5106,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>486609</v>
+        <v>486552</v>
       </c>
       <c r="R43" t="n">
-        <v>7038052</v>
+        <v>7037942</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5234,6 +5144,11 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5246,44 +5161,44 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129254225</v>
+        <v>129254872</v>
       </c>
       <c r="B44" t="n">
-        <v>80053</v>
+        <v>57727</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5293,10 +5208,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>486624</v>
+        <v>486715</v>
       </c>
       <c r="R44" t="n">
-        <v>7038036</v>
+        <v>7037924</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5331,6 +5246,11 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5343,22 +5263,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129254879</v>
+        <v>129243863</v>
       </c>
       <c r="B45" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5366,37 +5286,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>486552</v>
+        <v>486663</v>
       </c>
       <c r="R45" t="n">
-        <v>7037942</v>
+        <v>7037905</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5423,14 +5343,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Långväxta bålar, på flera granar.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5441,23 +5371,48 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129254872</v>
+        <v>129243061</v>
       </c>
       <c r="B46" t="n">
         <v>57727</v>
@@ -5486,16 +5441,26 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>486715</v>
+        <v>486568</v>
       </c>
       <c r="R46" t="n">
-        <v>7037924</v>
+        <v>7037962</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5525,14 +5490,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5543,16 +5518,41 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5656,10 +5656,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129254231</v>
+        <v>129254214</v>
       </c>
       <c r="B48" t="n">
-        <v>88952</v>
+        <v>57727</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5667,21 +5667,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5691,10 +5691,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>486615</v>
+        <v>486551</v>
       </c>
       <c r="R48" t="n">
-        <v>7037875</v>
+        <v>7037889</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5727,6 +5727,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5753,10 +5758,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129254196</v>
+        <v>129254231</v>
       </c>
       <c r="B49" t="n">
-        <v>83012</v>
+        <v>88952</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5764,21 +5769,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6440</v>
+        <v>510</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5788,10 +5793,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>486582</v>
+        <v>486615</v>
       </c>
       <c r="R49" t="n">
-        <v>7038072</v>
+        <v>7037875</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5850,32 +5855,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129254224</v>
+        <v>129254196</v>
       </c>
       <c r="B50" t="n">
-        <v>80053</v>
+        <v>83012</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6456</v>
+        <v>6440</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5885,10 +5890,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>486599</v>
+        <v>486582</v>
       </c>
       <c r="R50" t="n">
-        <v>7038068</v>
+        <v>7038072</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5947,32 +5952,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129254214</v>
+        <v>129254224</v>
       </c>
       <c r="B51" t="n">
-        <v>57727</v>
+        <v>80053</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5982,10 +5987,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>486551</v>
+        <v>486599</v>
       </c>
       <c r="R51" t="n">
-        <v>7037889</v>
+        <v>7038068</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6018,11 +6023,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">

--- a/artfynd/A 39541-2025 artfynd.xlsx
+++ b/artfynd/A 39541-2025 artfynd.xlsx
@@ -890,10 +890,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129241859</v>
+        <v>129254218</v>
       </c>
       <c r="B4" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -901,37 +901,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tomasbodarna, Tomasbodarna, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486860</v>
+        <v>486524</v>
       </c>
       <c r="R4" t="n">
-        <v>7037938</v>
+        <v>7037965</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -958,19 +958,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:27</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:27</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,28 +976,23 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129254206</v>
+        <v>129254875</v>
       </c>
       <c r="B5" t="n">
         <v>57727</v>
@@ -1037,10 +1027,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>486751</v>
+        <v>486429</v>
       </c>
       <c r="R5" t="n">
-        <v>7037804</v>
+        <v>7037954</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1077,7 +1067,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1092,19 +1082,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129254218</v>
+        <v>129254206</v>
       </c>
       <c r="B6" t="n">
         <v>57727</v>
@@ -1139,10 +1129,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>486524</v>
+        <v>486751</v>
       </c>
       <c r="R6" t="n">
-        <v>7037965</v>
+        <v>7037804</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1179,7 +1169,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1206,10 +1196,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129254875</v>
+        <v>129241859</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1217,37 +1207,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Tomasbodarna, Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>486429</v>
+        <v>486860</v>
       </c>
       <c r="R7" t="n">
-        <v>7037954</v>
+        <v>7037938</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1274,14 +1264,19 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1292,16 +1287,21 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1567,7 +1567,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129243523</v>
+        <v>129254871</v>
       </c>
       <c r="B10" t="n">
         <v>57727</v>
@@ -1596,29 +1596,19 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>486472</v>
+        <v>486833</v>
       </c>
       <c r="R10" t="n">
-        <v>7037927</v>
+        <v>7037850</v>
       </c>
       <c r="S10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1645,24 +1635,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>15:21</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:21</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en hyfsat grov gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1673,41 +1653,16 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1816,7 +1771,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129254215</v>
+        <v>129254220</v>
       </c>
       <c r="B12" t="n">
         <v>57727</v>
@@ -1851,10 +1806,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>486524</v>
+        <v>486583</v>
       </c>
       <c r="R12" t="n">
-        <v>7037917</v>
+        <v>7038073</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1918,7 +1873,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129254871</v>
+        <v>129254215</v>
       </c>
       <c r="B13" t="n">
         <v>57727</v>
@@ -1953,10 +1908,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>486833</v>
+        <v>486524</v>
       </c>
       <c r="R13" t="n">
-        <v>7037850</v>
+        <v>7037917</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1993,7 +1948,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2008,19 +1963,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129254220</v>
+        <v>129243523</v>
       </c>
       <c r="B14" t="n">
         <v>57727</v>
@@ -2049,19 +2004,29 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>486583</v>
+        <v>486472</v>
       </c>
       <c r="R14" t="n">
-        <v>7038073</v>
+        <v>7037927</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2088,14 +2053,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack, äldre, på stambasen av en hyfsat grov gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2106,16 +2081,41 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2362,7 +2362,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129254221</v>
+        <v>129254211</v>
       </c>
       <c r="B17" t="n">
         <v>57727</v>
@@ -2397,10 +2397,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>486595</v>
+        <v>486582</v>
       </c>
       <c r="R17" t="n">
-        <v>7038075</v>
+        <v>7037881</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2464,7 +2464,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129254211</v>
+        <v>129254221</v>
       </c>
       <c r="B18" t="n">
         <v>57727</v>
@@ -2499,10 +2499,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>486582</v>
+        <v>486595</v>
       </c>
       <c r="R18" t="n">
-        <v>7037881</v>
+        <v>7038075</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2887,10 +2887,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129254210</v>
+        <v>129254228</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>91573</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2898,23 +2898,19 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2922,10 +2918,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>486650</v>
+        <v>486556</v>
       </c>
       <c r="R22" t="n">
-        <v>7037866</v>
+        <v>7037879</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2958,11 +2954,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2989,10 +2980,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129254222</v>
+        <v>129254210</v>
       </c>
       <c r="B23" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3000,50 +2991,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>486607</v>
+        <v>486650</v>
       </c>
       <c r="R23" t="n">
-        <v>7038047</v>
+        <v>7037866</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3076,6 +3051,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3102,10 +3082,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129254228</v>
+        <v>129254222</v>
       </c>
       <c r="B24" t="n">
-        <v>91573</v>
+        <v>57887</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3113,30 +3093,50 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>486556</v>
+        <v>486607</v>
       </c>
       <c r="R24" t="n">
-        <v>7037879</v>
+        <v>7038047</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3399,10 +3399,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129244388</v>
+        <v>129254219</v>
       </c>
       <c r="B27" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3410,34 +3410,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>486782</v>
+        <v>486543</v>
       </c>
       <c r="R27" t="n">
-        <v>7037877</v>
+        <v>7037939</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3467,24 +3467,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>15:53</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>15:53</t>
-        </is>
-      </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3495,31 +3485,26 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129254219</v>
+        <v>129244388</v>
       </c>
       <c r="B28" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3527,34 +3512,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>486543</v>
+        <v>486782</v>
       </c>
       <c r="R28" t="n">
-        <v>7037939</v>
+        <v>7037877</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3584,14 +3569,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3602,16 +3597,21 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3954,7 +3954,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129254204</v>
+        <v>129254873</v>
       </c>
       <c r="B32" t="n">
         <v>57727</v>
@@ -3989,10 +3989,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>486767</v>
+        <v>486683</v>
       </c>
       <c r="R32" t="n">
-        <v>7037800</v>
+        <v>7037917</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4044,19 +4044,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129254202</v>
+        <v>129254877</v>
       </c>
       <c r="B33" t="n">
         <v>57727</v>
@@ -4091,10 +4091,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>486780</v>
+        <v>486495</v>
       </c>
       <c r="R33" t="n">
-        <v>7037796</v>
+        <v>7037956</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4131,7 +4131,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4146,19 +4146,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129254207</v>
+        <v>129254204</v>
       </c>
       <c r="B34" t="n">
         <v>57727</v>
@@ -4193,10 +4193,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>486743</v>
+        <v>486767</v>
       </c>
       <c r="R34" t="n">
-        <v>7037808</v>
+        <v>7037800</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4233,7 +4233,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4260,7 +4260,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129254873</v>
+        <v>129254202</v>
       </c>
       <c r="B35" t="n">
         <v>57727</v>
@@ -4295,10 +4295,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>486683</v>
+        <v>486780</v>
       </c>
       <c r="R35" t="n">
-        <v>7037917</v>
+        <v>7037796</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4335,7 +4335,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4350,19 +4350,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129254877</v>
+        <v>129254207</v>
       </c>
       <c r="B36" t="n">
         <v>57727</v>
@@ -4397,10 +4397,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>486495</v>
+        <v>486743</v>
       </c>
       <c r="R36" t="n">
-        <v>7037956</v>
+        <v>7037808</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4437,7 +4437,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4452,12 +4452,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4668,10 +4668,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129244231</v>
+        <v>129254226</v>
       </c>
       <c r="B39" t="n">
-        <v>79044</v>
+        <v>78057</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4679,37 +4679,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>486671</v>
+        <v>486585</v>
       </c>
       <c r="R39" t="n">
-        <v>7037887</v>
+        <v>7038070</v>
       </c>
       <c r="S39" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4736,24 +4736,9 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4768,22 +4753,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129254226</v>
+        <v>129244231</v>
       </c>
       <c r="B40" t="n">
-        <v>78057</v>
+        <v>79044</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4791,37 +4776,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>486585</v>
+        <v>486671</v>
       </c>
       <c r="R40" t="n">
-        <v>7038070</v>
+        <v>7037887</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4848,9 +4833,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4865,12 +4865,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5275,10 +5275,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129243863</v>
+        <v>129243061</v>
       </c>
       <c r="B45" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5286,37 +5286,47 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>486663</v>
+        <v>486568</v>
       </c>
       <c r="R45" t="n">
-        <v>7037905</v>
+        <v>7037962</v>
       </c>
       <c r="S45" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5345,7 +5355,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5355,12 +5365,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Långväxta bålar, på flera granar.</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5374,7 +5384,7 @@
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr">
@@ -5389,12 +5399,12 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5412,10 +5422,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129243061</v>
+        <v>129243863</v>
       </c>
       <c r="B46" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5423,47 +5433,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>486568</v>
+        <v>486663</v>
       </c>
       <c r="R46" t="n">
-        <v>7037962</v>
+        <v>7037905</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5492,7 +5492,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5502,12 +5502,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Långväxta bålar, på flera granar.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5521,7 +5521,7 @@
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ46" t="inlineStr">
@@ -5536,12 +5536,12 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5656,10 +5656,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129254214</v>
+        <v>129254231</v>
       </c>
       <c r="B48" t="n">
-        <v>57727</v>
+        <v>88952</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5667,21 +5667,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5691,10 +5691,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>486551</v>
+        <v>486615</v>
       </c>
       <c r="R48" t="n">
-        <v>7037889</v>
+        <v>7037875</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5727,11 +5727,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5758,10 +5753,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129254231</v>
+        <v>129254214</v>
       </c>
       <c r="B49" t="n">
-        <v>88952</v>
+        <v>57727</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5769,21 +5764,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5793,10 +5788,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>486615</v>
+        <v>486551</v>
       </c>
       <c r="R49" t="n">
-        <v>7037875</v>
+        <v>7037889</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5829,6 +5824,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6355,10 +6355,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129254878</v>
+        <v>129243772</v>
       </c>
       <c r="B55" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6366,37 +6366,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>486553</v>
+        <v>486608</v>
       </c>
       <c r="R55" t="n">
-        <v>7037937</v>
+        <v>7037908</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6423,14 +6423,19 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6441,26 +6446,51 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129243772</v>
+        <v>129254878</v>
       </c>
       <c r="B56" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6468,37 +6498,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>486608</v>
+        <v>486553</v>
       </c>
       <c r="R56" t="n">
-        <v>7037908</v>
+        <v>7037937</v>
       </c>
       <c r="S56" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6525,19 +6555,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>15:38</t>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6548,41 +6573,16 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>

--- a/artfynd/A 39541-2025 artfynd.xlsx
+++ b/artfynd/A 39541-2025 artfynd.xlsx
@@ -781,27 +781,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129254223</v>
+        <v>129254218</v>
       </c>
       <c r="B3" t="n">
-        <v>57568</v>
+        <v>57727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -809,29 +809,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>486737</v>
+        <v>486524</v>
       </c>
       <c r="R3" t="n">
-        <v>7037835</v>
+        <v>7037965</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,6 +852,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,7 +883,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129254218</v>
+        <v>129254875</v>
       </c>
       <c r="B4" t="n">
         <v>57727</v>
@@ -925,10 +918,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486524</v>
+        <v>486429</v>
       </c>
       <c r="R4" t="n">
-        <v>7037965</v>
+        <v>7037954</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,7 +958,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -980,19 +973,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129254875</v>
+        <v>129254206</v>
       </c>
       <c r="B5" t="n">
         <v>57727</v>
@@ -1027,10 +1020,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>486429</v>
+        <v>486751</v>
       </c>
       <c r="R5" t="n">
-        <v>7037954</v>
+        <v>7037804</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,7 +1060,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1082,39 +1075,39 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129254206</v>
+        <v>129254223</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>57568</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1122,17 +1115,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>486751</v>
+        <v>486737</v>
       </c>
       <c r="R6" t="n">
-        <v>7037804</v>
+        <v>7037835</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,11 +1170,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -2224,68 +2224,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129243687</v>
+        <v>129254211</v>
       </c>
       <c r="B16" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>486517</v>
+        <v>486582</v>
       </c>
       <c r="R16" t="n">
-        <v>7037922</v>
+        <v>7037881</v>
       </c>
       <c r="S16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2312,24 +2292,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>15:26</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>15:26</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Minst 120 plantor och 1 fröställning inom ca 1 m2 yta  intill en naturvårdsnitslad björk.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2338,31 +2308,25 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129254211</v>
+        <v>129254221</v>
       </c>
       <c r="B17" t="n">
         <v>57727</v>
@@ -2397,10 +2361,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>486582</v>
+        <v>486595</v>
       </c>
       <c r="R17" t="n">
-        <v>7037881</v>
+        <v>7038075</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2464,48 +2428,68 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129254221</v>
+        <v>129243687</v>
       </c>
       <c r="B18" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>486595</v>
+        <v>486517</v>
       </c>
       <c r="R18" t="n">
-        <v>7038075</v>
+        <v>7037922</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2532,14 +2516,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Minst 120 plantor och 1 fröställning inom ca 1 m2 yta  intill en naturvårdsnitslad björk.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2548,18 +2542,24 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -3297,10 +3297,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129254874</v>
+        <v>129244388</v>
       </c>
       <c r="B26" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3308,34 +3308,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>486550</v>
+        <v>486782</v>
       </c>
       <c r="R26" t="n">
-        <v>7037929</v>
+        <v>7037877</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3365,14 +3365,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3383,23 +3393,28 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129254219</v>
+        <v>129254874</v>
       </c>
       <c r="B27" t="n">
         <v>57727</v>
@@ -3434,10 +3449,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>486543</v>
+        <v>486550</v>
       </c>
       <c r="R27" t="n">
-        <v>7037939</v>
+        <v>7037929</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3474,7 +3489,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3489,22 +3504,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129244388</v>
+        <v>129254219</v>
       </c>
       <c r="B28" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3512,34 +3527,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>486782</v>
+        <v>486543</v>
       </c>
       <c r="R28" t="n">
-        <v>7037877</v>
+        <v>7037939</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3569,24 +3584,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>15:53</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>15:53</t>
-        </is>
-      </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3597,31 +3602,26 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129254201</v>
+        <v>129241899</v>
       </c>
       <c r="B29" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3629,34 +3629,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>486797</v>
+        <v>486803</v>
       </c>
       <c r="R29" t="n">
-        <v>7037788</v>
+        <v>7037939</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3686,14 +3686,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3704,23 +3714,43 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129254876</v>
+        <v>129254201</v>
       </c>
       <c r="B30" t="n">
         <v>57727</v>
@@ -3755,10 +3785,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>486409</v>
+        <v>486797</v>
       </c>
       <c r="R30" t="n">
-        <v>7037957</v>
+        <v>7037788</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3795,7 +3825,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3810,22 +3840,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129241899</v>
+        <v>129254876</v>
       </c>
       <c r="B31" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3833,34 +3863,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>486803</v>
+        <v>486409</v>
       </c>
       <c r="R31" t="n">
-        <v>7037939</v>
+        <v>7037957</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3890,24 +3920,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3918,36 +3938,16 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4668,10 +4668,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129254226</v>
+        <v>129244231</v>
       </c>
       <c r="B39" t="n">
-        <v>78057</v>
+        <v>79044</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4679,37 +4679,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>486585</v>
+        <v>486671</v>
       </c>
       <c r="R39" t="n">
-        <v>7038070</v>
+        <v>7037887</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4736,9 +4736,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4753,22 +4768,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129244231</v>
+        <v>129254226</v>
       </c>
       <c r="B40" t="n">
-        <v>79044</v>
+        <v>78057</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4776,37 +4791,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>486671</v>
+        <v>486585</v>
       </c>
       <c r="R40" t="n">
-        <v>7037887</v>
+        <v>7038070</v>
       </c>
       <c r="S40" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4833,24 +4848,9 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4865,22 +4865,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129254230</v>
+        <v>129243863</v>
       </c>
       <c r="B41" t="n">
-        <v>82878</v>
+        <v>79044</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4888,37 +4888,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>486609</v>
+        <v>486663</v>
       </c>
       <c r="R41" t="n">
-        <v>7038052</v>
+        <v>7037905</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4945,11 +4945,26 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Långväxta bålar, på flera granar.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -4958,61 +4973,96 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129254225</v>
+        <v>129243061</v>
       </c>
       <c r="B42" t="n">
-        <v>80053</v>
+        <v>57727</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>486624</v>
+        <v>486568</v>
       </c>
       <c r="R42" t="n">
-        <v>7038036</v>
+        <v>7037962</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5042,11 +5092,26 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5055,26 +5120,51 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129254879</v>
+        <v>129254230</v>
       </c>
       <c r="B43" t="n">
-        <v>57727</v>
+        <v>82878</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5082,21 +5172,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5106,10 +5196,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>486552</v>
+        <v>486609</v>
       </c>
       <c r="R43" t="n">
-        <v>7037942</v>
+        <v>7038052</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5144,11 +5234,6 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5161,44 +5246,44 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129254872</v>
+        <v>129254225</v>
       </c>
       <c r="B44" t="n">
-        <v>57727</v>
+        <v>80053</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5208,10 +5293,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>486715</v>
+        <v>486624</v>
       </c>
       <c r="R44" t="n">
-        <v>7037924</v>
+        <v>7038036</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5246,11 +5331,6 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5263,19 +5343,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129243061</v>
+        <v>129254879</v>
       </c>
       <c r="B45" t="n">
         <v>57727</v>
@@ -5304,26 +5384,16 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>486568</v>
+        <v>486552</v>
       </c>
       <c r="R45" t="n">
-        <v>7037962</v>
+        <v>7037942</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5353,24 +5423,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5381,51 +5441,26 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129243863</v>
+        <v>129254872</v>
       </c>
       <c r="B46" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5433,37 +5468,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>486663</v>
+        <v>486715</v>
       </c>
       <c r="R46" t="n">
-        <v>7037905</v>
+        <v>7037924</v>
       </c>
       <c r="S46" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5490,24 +5525,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Långväxta bålar, på flera granar.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5518,41 +5543,16 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5753,10 +5753,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129254214</v>
+        <v>129254196</v>
       </c>
       <c r="B49" t="n">
-        <v>57727</v>
+        <v>83012</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5764,21 +5764,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5788,10 +5788,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>486551</v>
+        <v>486582</v>
       </c>
       <c r="R49" t="n">
-        <v>7037889</v>
+        <v>7038072</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5824,11 +5824,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5855,32 +5850,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129254196</v>
+        <v>129254224</v>
       </c>
       <c r="B50" t="n">
-        <v>83012</v>
+        <v>80053</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6440</v>
+        <v>6456</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5890,10 +5885,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>486582</v>
+        <v>486599</v>
       </c>
       <c r="R50" t="n">
-        <v>7038072</v>
+        <v>7038068</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5952,32 +5947,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129254224</v>
+        <v>129254214</v>
       </c>
       <c r="B51" t="n">
-        <v>80053</v>
+        <v>57727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5987,10 +5982,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>486599</v>
+        <v>486551</v>
       </c>
       <c r="R51" t="n">
-        <v>7038068</v>
+        <v>7037889</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6023,6 +6018,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6355,10 +6355,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129243772</v>
+        <v>129254878</v>
       </c>
       <c r="B55" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6366,37 +6366,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>486608</v>
+        <v>486553</v>
       </c>
       <c r="R55" t="n">
-        <v>7037908</v>
+        <v>7037937</v>
       </c>
       <c r="S55" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6423,19 +6423,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>15:38</t>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6446,51 +6441,26 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129254878</v>
+        <v>129243772</v>
       </c>
       <c r="B56" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6498,37 +6468,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>486553</v>
+        <v>486608</v>
       </c>
       <c r="R56" t="n">
-        <v>7037937</v>
+        <v>7037908</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6555,14 +6525,19 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6573,16 +6548,41 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>

--- a/artfynd/A 39541-2025 artfynd.xlsx
+++ b/artfynd/A 39541-2025 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129254218</v>
+        <v>129242509</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,37 +792,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>486524</v>
+        <v>486672</v>
       </c>
       <c r="R3" t="n">
-        <v>7037965</v>
+        <v>7037952</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -849,14 +849,19 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,26 +872,31 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129254875</v>
+        <v>129241859</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -894,37 +904,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Tomasbodarna, Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486429</v>
+        <v>486860</v>
       </c>
       <c r="R4" t="n">
-        <v>7037954</v>
+        <v>7037938</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -951,14 +961,19 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -969,23 +984,28 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129254206</v>
+        <v>129242015</v>
       </c>
       <c r="B5" t="n">
         <v>57727</v>
@@ -1014,19 +1034,29 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>486751</v>
+        <v>486782</v>
       </c>
       <c r="R5" t="n">
-        <v>7037804</v>
+        <v>7037909</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1053,14 +1083,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,43 +1111,68 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129254223</v>
+        <v>129254218</v>
       </c>
       <c r="B6" t="n">
-        <v>57568</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1115,29 +1180,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>486737</v>
+        <v>486524</v>
       </c>
       <c r="R6" t="n">
-        <v>7037835</v>
+        <v>7037965</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,6 +1223,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1196,10 +1254,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129241859</v>
+        <v>129254875</v>
       </c>
       <c r="B7" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1207,37 +1265,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tomasbodarna, Tomasbodarna, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>486860</v>
+        <v>486429</v>
       </c>
       <c r="R7" t="n">
-        <v>7037938</v>
+        <v>7037954</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1264,19 +1322,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>14:27</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:27</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1287,31 +1340,26 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129242509</v>
+        <v>129254206</v>
       </c>
       <c r="B8" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1319,37 +1367,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>486672</v>
+        <v>486751</v>
       </c>
       <c r="R8" t="n">
-        <v>7037952</v>
+        <v>7037804</v>
       </c>
       <c r="S8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1376,19 +1424,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>14:42</t>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1399,48 +1442,43 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129242015</v>
+        <v>129254223</v>
       </c>
       <c r="B9" t="n">
-        <v>57727</v>
+        <v>57568</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1448,30 +1486,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>486782</v>
+        <v>486737</v>
       </c>
       <c r="R9" t="n">
-        <v>7037909</v>
+        <v>7037835</v>
       </c>
       <c r="S9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1498,26 +1538,11 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1526,41 +1551,16 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -2224,48 +2224,68 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129254211</v>
+        <v>129243687</v>
       </c>
       <c r="B16" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>486582</v>
+        <v>486517</v>
       </c>
       <c r="R16" t="n">
-        <v>7037881</v>
+        <v>7037922</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2292,14 +2312,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Minst 120 plantor och 1 fröställning inom ca 1 m2 yta  intill en naturvårdsnitslad björk.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2308,25 +2338,31 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129254221</v>
+        <v>129254211</v>
       </c>
       <c r="B17" t="n">
         <v>57727</v>
@@ -2361,10 +2397,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>486595</v>
+        <v>486582</v>
       </c>
       <c r="R17" t="n">
-        <v>7038075</v>
+        <v>7037881</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2428,68 +2464,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129243687</v>
+        <v>129254221</v>
       </c>
       <c r="B18" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>486517</v>
+        <v>486595</v>
       </c>
       <c r="R18" t="n">
-        <v>7037922</v>
+        <v>7038075</v>
       </c>
       <c r="S18" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2516,24 +2532,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>15:26</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>15:26</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Minst 120 plantor och 1 fröställning inom ca 1 m2 yta  intill en naturvårdsnitslad björk.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2542,24 +2548,18 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -3297,10 +3297,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129244388</v>
+        <v>129254874</v>
       </c>
       <c r="B26" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3308,34 +3308,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>486782</v>
+        <v>486550</v>
       </c>
       <c r="R26" t="n">
-        <v>7037877</v>
+        <v>7037929</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3365,24 +3365,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>15:53</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>15:53</t>
-        </is>
-      </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3393,28 +3383,23 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129254874</v>
+        <v>129254219</v>
       </c>
       <c r="B27" t="n">
         <v>57727</v>
@@ -3449,10 +3434,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>486550</v>
+        <v>486543</v>
       </c>
       <c r="R27" t="n">
-        <v>7037929</v>
+        <v>7037939</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3489,7 +3474,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3504,22 +3489,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129254219</v>
+        <v>129244388</v>
       </c>
       <c r="B28" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3527,34 +3512,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>486543</v>
+        <v>486782</v>
       </c>
       <c r="R28" t="n">
-        <v>7037939</v>
+        <v>7037877</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3584,14 +3569,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3602,16 +3597,21 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3750,7 +3750,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129254201</v>
+        <v>129254876</v>
       </c>
       <c r="B30" t="n">
         <v>57727</v>
@@ -3785,10 +3785,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>486797</v>
+        <v>486409</v>
       </c>
       <c r="R30" t="n">
-        <v>7037788</v>
+        <v>7037957</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3840,19 +3840,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129254876</v>
+        <v>129254201</v>
       </c>
       <c r="B31" t="n">
         <v>57727</v>
@@ -3887,10 +3887,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>486409</v>
+        <v>486797</v>
       </c>
       <c r="R31" t="n">
-        <v>7037957</v>
+        <v>7037788</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3927,7 +3927,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3942,12 +3942,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4668,10 +4668,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129244231</v>
+        <v>129254226</v>
       </c>
       <c r="B39" t="n">
-        <v>79044</v>
+        <v>78057</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4679,37 +4679,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>486671</v>
+        <v>486585</v>
       </c>
       <c r="R39" t="n">
-        <v>7037887</v>
+        <v>7038070</v>
       </c>
       <c r="S39" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4736,24 +4736,9 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4768,22 +4753,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129254226</v>
+        <v>129244231</v>
       </c>
       <c r="B40" t="n">
-        <v>78057</v>
+        <v>79044</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4791,37 +4776,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>486585</v>
+        <v>486671</v>
       </c>
       <c r="R40" t="n">
-        <v>7038070</v>
+        <v>7037887</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4848,9 +4833,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4865,22 +4865,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129243863</v>
+        <v>129254230</v>
       </c>
       <c r="B41" t="n">
-        <v>79044</v>
+        <v>82878</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4888,37 +4888,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>486663</v>
+        <v>486609</v>
       </c>
       <c r="R41" t="n">
-        <v>7037905</v>
+        <v>7038052</v>
       </c>
       <c r="S41" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4945,26 +4945,11 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Långväxta bålar, på flera granar.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -4973,41 +4958,16 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5161,32 +5121,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129254230</v>
+        <v>129254225</v>
       </c>
       <c r="B43" t="n">
-        <v>82878</v>
+        <v>80053</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1312</v>
+        <v>6456</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5196,10 +5156,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>486609</v>
+        <v>486624</v>
       </c>
       <c r="R43" t="n">
-        <v>7038052</v>
+        <v>7038036</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5258,32 +5218,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129254225</v>
+        <v>129254879</v>
       </c>
       <c r="B44" t="n">
-        <v>80053</v>
+        <v>57727</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5293,10 +5253,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>486624</v>
+        <v>486552</v>
       </c>
       <c r="R44" t="n">
-        <v>7038036</v>
+        <v>7037942</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5331,6 +5291,11 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5343,19 +5308,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129254879</v>
+        <v>129254872</v>
       </c>
       <c r="B45" t="n">
         <v>57727</v>
@@ -5390,10 +5355,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>486552</v>
+        <v>486715</v>
       </c>
       <c r="R45" t="n">
-        <v>7037942</v>
+        <v>7037924</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5457,10 +5422,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129254872</v>
+        <v>129243863</v>
       </c>
       <c r="B46" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5468,37 +5433,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>486715</v>
+        <v>486663</v>
       </c>
       <c r="R46" t="n">
-        <v>7037924</v>
+        <v>7037905</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5525,14 +5490,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Långväxta bålar, på flera granar.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5543,16 +5518,41 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -6355,10 +6355,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129254878</v>
+        <v>129243772</v>
       </c>
       <c r="B55" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6366,37 +6366,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>486553</v>
+        <v>486608</v>
       </c>
       <c r="R55" t="n">
-        <v>7037937</v>
+        <v>7037908</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6423,14 +6423,19 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6441,26 +6446,51 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129243772</v>
+        <v>129254878</v>
       </c>
       <c r="B56" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6468,37 +6498,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>486608</v>
+        <v>486553</v>
       </c>
       <c r="R56" t="n">
-        <v>7037908</v>
+        <v>7037937</v>
       </c>
       <c r="S56" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6525,19 +6555,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>15:38</t>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6548,41 +6573,16 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>

--- a/artfynd/A 39541-2025 artfynd.xlsx
+++ b/artfynd/A 39541-2025 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129242509</v>
+        <v>129254218</v>
       </c>
       <c r="B3" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,37 +792,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>486672</v>
+        <v>486524</v>
       </c>
       <c r="R3" t="n">
-        <v>7037952</v>
+        <v>7037965</v>
       </c>
       <c r="S3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -849,19 +849,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:42</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,31 +867,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129241859</v>
+        <v>129254875</v>
       </c>
       <c r="B4" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,37 +894,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tomasbodarna, Tomasbodarna, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486860</v>
+        <v>486429</v>
       </c>
       <c r="R4" t="n">
-        <v>7037938</v>
+        <v>7037954</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -961,19 +951,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:27</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:27</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,28 +969,23 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129242015</v>
+        <v>129254206</v>
       </c>
       <c r="B5" t="n">
         <v>57727</v>
@@ -1034,29 +1014,19 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>486782</v>
+        <v>486751</v>
       </c>
       <c r="R5" t="n">
-        <v>7037909</v>
+        <v>7037804</v>
       </c>
       <c r="S5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,24 +1053,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,51 +1071,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129254218</v>
+        <v>129241859</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,37 +1098,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Tomasbodarna, Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>486524</v>
+        <v>486860</v>
       </c>
       <c r="R6" t="n">
-        <v>7037965</v>
+        <v>7037938</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1220,14 +1155,19 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,26 +1178,31 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129254875</v>
+        <v>129242509</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,37 +1210,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>486429</v>
+        <v>486672</v>
       </c>
       <c r="R7" t="n">
-        <v>7037954</v>
+        <v>7037952</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1322,14 +1267,19 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1340,23 +1290,28 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129254206</v>
+        <v>129242015</v>
       </c>
       <c r="B8" t="n">
         <v>57727</v>
@@ -1385,19 +1340,29 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>486751</v>
+        <v>486782</v>
       </c>
       <c r="R8" t="n">
-        <v>7037804</v>
+        <v>7037909</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1424,14 +1389,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1442,16 +1417,41 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -2224,68 +2224,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129243687</v>
+        <v>129254211</v>
       </c>
       <c r="B16" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>486517</v>
+        <v>486582</v>
       </c>
       <c r="R16" t="n">
-        <v>7037922</v>
+        <v>7037881</v>
       </c>
       <c r="S16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2312,24 +2292,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>15:26</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>15:26</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Minst 120 plantor och 1 fröställning inom ca 1 m2 yta  intill en naturvårdsnitslad björk.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2338,31 +2308,25 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129254211</v>
+        <v>129254221</v>
       </c>
       <c r="B17" t="n">
         <v>57727</v>
@@ -2397,10 +2361,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>486582</v>
+        <v>486595</v>
       </c>
       <c r="R17" t="n">
-        <v>7037881</v>
+        <v>7038075</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2464,48 +2428,68 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129254221</v>
+        <v>129243687</v>
       </c>
       <c r="B18" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>486595</v>
+        <v>486517</v>
       </c>
       <c r="R18" t="n">
-        <v>7038075</v>
+        <v>7037922</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2532,14 +2516,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Minst 120 plantor och 1 fröställning inom ca 1 m2 yta  intill en naturvårdsnitslad björk.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2548,18 +2542,24 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2980,10 +2980,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129254210</v>
+        <v>129254222</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2991,34 +2991,50 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>486650</v>
+        <v>486607</v>
       </c>
       <c r="R23" t="n">
-        <v>7037866</v>
+        <v>7038047</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3051,11 +3067,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3082,10 +3093,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129254222</v>
+        <v>129254210</v>
       </c>
       <c r="B24" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3093,50 +3104,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>486607</v>
+        <v>486650</v>
       </c>
       <c r="R24" t="n">
-        <v>7038047</v>
+        <v>7037866</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3169,6 +3164,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3618,10 +3618,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129241899</v>
+        <v>129254201</v>
       </c>
       <c r="B29" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3629,34 +3629,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>486803</v>
+        <v>486797</v>
       </c>
       <c r="R29" t="n">
-        <v>7037939</v>
+        <v>7037788</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3686,24 +3686,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3714,36 +3704,16 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3852,10 +3822,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129254201</v>
+        <v>129241899</v>
       </c>
       <c r="B31" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3863,34 +3833,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>486797</v>
+        <v>486803</v>
       </c>
       <c r="R31" t="n">
-        <v>7037788</v>
+        <v>7037939</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3920,14 +3890,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3938,16 +3918,36 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4668,10 +4668,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129254226</v>
+        <v>129244231</v>
       </c>
       <c r="B39" t="n">
-        <v>78057</v>
+        <v>79044</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4679,37 +4679,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>486585</v>
+        <v>486671</v>
       </c>
       <c r="R39" t="n">
-        <v>7038070</v>
+        <v>7037887</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4736,9 +4736,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4753,22 +4768,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129244231</v>
+        <v>129254226</v>
       </c>
       <c r="B40" t="n">
-        <v>79044</v>
+        <v>78057</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4776,37 +4791,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>486671</v>
+        <v>486585</v>
       </c>
       <c r="R40" t="n">
-        <v>7037887</v>
+        <v>7038070</v>
       </c>
       <c r="S40" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4833,24 +4848,9 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4865,22 +4865,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129254230</v>
+        <v>129254879</v>
       </c>
       <c r="B41" t="n">
-        <v>82878</v>
+        <v>57727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4888,21 +4888,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4912,10 +4912,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>486609</v>
+        <v>486552</v>
       </c>
       <c r="R41" t="n">
-        <v>7038052</v>
+        <v>7037942</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4950,6 +4950,11 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -4962,19 +4967,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129243061</v>
+        <v>129254872</v>
       </c>
       <c r="B42" t="n">
         <v>57727</v>
@@ -5003,26 +5008,16 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>486568</v>
+        <v>486715</v>
       </c>
       <c r="R42" t="n">
-        <v>7037962</v>
+        <v>7037924</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5052,24 +5047,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5080,89 +5065,64 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129254225</v>
+        <v>129243863</v>
       </c>
       <c r="B43" t="n">
-        <v>80053</v>
+        <v>79044</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>486624</v>
+        <v>486663</v>
       </c>
       <c r="R43" t="n">
-        <v>7038036</v>
+        <v>7037905</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5189,11 +5149,26 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Långväxta bålar, på flera granar.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5202,23 +5177,48 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129254879</v>
+        <v>129243061</v>
       </c>
       <c r="B44" t="n">
         <v>57727</v>
@@ -5247,16 +5247,26 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>486552</v>
+        <v>486568</v>
       </c>
       <c r="R44" t="n">
-        <v>7037942</v>
+        <v>7037962</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5286,14 +5296,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5304,48 +5324,73 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129254872</v>
+        <v>129254225</v>
       </c>
       <c r="B45" t="n">
-        <v>57727</v>
+        <v>80053</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5355,10 +5400,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>486715</v>
+        <v>486624</v>
       </c>
       <c r="R45" t="n">
-        <v>7037924</v>
+        <v>7038036</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5393,11 +5438,6 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5410,22 +5450,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129243863</v>
+        <v>129254230</v>
       </c>
       <c r="B46" t="n">
-        <v>79044</v>
+        <v>82878</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5433,37 +5473,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>486663</v>
+        <v>486609</v>
       </c>
       <c r="R46" t="n">
-        <v>7037905</v>
+        <v>7038052</v>
       </c>
       <c r="S46" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5490,26 +5530,11 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Långväxta bålar, på flera granar.</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5518,41 +5543,16 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5656,10 +5656,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129254231</v>
+        <v>129254196</v>
       </c>
       <c r="B48" t="n">
-        <v>88952</v>
+        <v>83012</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5667,21 +5667,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>510</v>
+        <v>6440</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5691,10 +5691,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>486615</v>
+        <v>486582</v>
       </c>
       <c r="R48" t="n">
-        <v>7037875</v>
+        <v>7038072</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5753,32 +5753,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129254196</v>
+        <v>129254224</v>
       </c>
       <c r="B49" t="n">
-        <v>83012</v>
+        <v>80053</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6440</v>
+        <v>6456</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5788,10 +5788,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>486582</v>
+        <v>486599</v>
       </c>
       <c r="R49" t="n">
-        <v>7038072</v>
+        <v>7038068</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5850,32 +5850,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129254224</v>
+        <v>129254231</v>
       </c>
       <c r="B50" t="n">
-        <v>80053</v>
+        <v>88952</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6456</v>
+        <v>510</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5885,10 +5885,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>486599</v>
+        <v>486615</v>
       </c>
       <c r="R50" t="n">
-        <v>7038068</v>
+        <v>7037875</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6156,10 +6156,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129254229</v>
+        <v>129254213</v>
       </c>
       <c r="B53" t="n">
-        <v>82878</v>
+        <v>57727</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6167,21 +6167,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6191,10 +6191,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>486611</v>
+        <v>486551</v>
       </c>
       <c r="R53" t="n">
-        <v>7038042</v>
+        <v>7037886</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6227,6 +6227,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6253,10 +6258,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129254213</v>
+        <v>129254229</v>
       </c>
       <c r="B54" t="n">
-        <v>57727</v>
+        <v>82878</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6264,21 +6269,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6288,10 +6293,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>486551</v>
+        <v>486611</v>
       </c>
       <c r="R54" t="n">
-        <v>7037886</v>
+        <v>7038042</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6324,11 +6329,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6355,10 +6355,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129243772</v>
+        <v>129254878</v>
       </c>
       <c r="B55" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6366,37 +6366,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>486608</v>
+        <v>486553</v>
       </c>
       <c r="R55" t="n">
-        <v>7037908</v>
+        <v>7037937</v>
       </c>
       <c r="S55" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6423,19 +6423,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>15:38</t>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6446,51 +6441,26 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129254878</v>
+        <v>129243772</v>
       </c>
       <c r="B56" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6498,37 +6468,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>486553</v>
+        <v>486608</v>
       </c>
       <c r="R56" t="n">
-        <v>7037937</v>
+        <v>7037908</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6555,14 +6525,19 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6573,16 +6548,41 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>

--- a/artfynd/A 39541-2025 artfynd.xlsx
+++ b/artfynd/A 39541-2025 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129254218</v>
+        <v>129241859</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>79070</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,37 +792,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Tomasbodarna, Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>486524</v>
+        <v>486860</v>
       </c>
       <c r="R3" t="n">
-        <v>7037965</v>
+        <v>7037938</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -849,14 +849,19 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,26 +872,31 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129254875</v>
+        <v>129242509</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>79070</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -894,37 +904,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486429</v>
+        <v>486672</v>
       </c>
       <c r="R4" t="n">
-        <v>7037954</v>
+        <v>7037952</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -951,14 +961,19 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -969,26 +984,31 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129254206</v>
+        <v>129254218</v>
       </c>
       <c r="B5" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1020,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>486751</v>
+        <v>486524</v>
       </c>
       <c r="R5" t="n">
-        <v>7037804</v>
+        <v>7037965</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1060,7 +1080,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1087,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129241859</v>
+        <v>129254875</v>
       </c>
       <c r="B6" t="n">
-        <v>79044</v>
+        <v>57730</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,37 +1118,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tomasbodarna, Tomasbodarna, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>486860</v>
+        <v>486429</v>
       </c>
       <c r="R6" t="n">
-        <v>7037938</v>
+        <v>7037954</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1155,19 +1175,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>14:27</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:27</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1178,31 +1193,26 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129242509</v>
+        <v>129254206</v>
       </c>
       <c r="B7" t="n">
-        <v>79044</v>
+        <v>57730</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1210,37 +1220,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>486672</v>
+        <v>486751</v>
       </c>
       <c r="R7" t="n">
-        <v>7037952</v>
+        <v>7037804</v>
       </c>
       <c r="S7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1267,19 +1277,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:42</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1290,48 +1295,43 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129242015</v>
+        <v>129254223</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>57571</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1339,30 +1339,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>486782</v>
+        <v>486737</v>
       </c>
       <c r="R8" t="n">
-        <v>7037909</v>
+        <v>7037835</v>
       </c>
       <c r="S8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1389,26 +1391,11 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1417,68 +1404,43 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129254223</v>
+        <v>129242015</v>
       </c>
       <c r="B9" t="n">
-        <v>57568</v>
+        <v>57730</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1486,32 +1448,30 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>486737</v>
+        <v>486782</v>
       </c>
       <c r="R9" t="n">
-        <v>7037835</v>
+        <v>7037909</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1538,11 +1498,26 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1551,16 +1526,41 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1570,7 +1570,7 @@
         <v>129254871</v>
       </c>
       <c r="B10" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>129254205</v>
       </c>
       <c r="B11" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>129254220</v>
       </c>
       <c r="B12" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
         <v>129254215</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>129243523</v>
       </c>
       <c r="B14" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>129254208</v>
       </c>
       <c r="B15" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>129254211</v>
       </c>
       <c r="B16" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         <v>129254221</v>
       </c>
       <c r="B17" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>129243687</v>
       </c>
       <c r="B18" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>129254199</v>
       </c>
       <c r="B19" t="n">
-        <v>83012</v>
+        <v>83039</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         <v>129254216</v>
       </c>
       <c r="B20" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>129242968</v>
       </c>
       <c r="B21" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2887,10 +2887,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129254228</v>
+        <v>129254210</v>
       </c>
       <c r="B22" t="n">
-        <v>91573</v>
+        <v>57730</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2898,19 +2898,23 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2918,10 +2922,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>486556</v>
+        <v>486650</v>
       </c>
       <c r="R22" t="n">
-        <v>7037879</v>
+        <v>7037866</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2954,6 +2958,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2983,7 +2992,7 @@
         <v>129254222</v>
       </c>
       <c r="B23" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3093,10 +3102,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129254210</v>
+        <v>129254228</v>
       </c>
       <c r="B24" t="n">
-        <v>57727</v>
+        <v>91601</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3104,23 +3113,19 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3128,10 +3133,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>486650</v>
+        <v>486556</v>
       </c>
       <c r="R24" t="n">
-        <v>7037866</v>
+        <v>7037879</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3164,11 +3169,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3198,7 +3198,7 @@
         <v>129254212</v>
       </c>
       <c r="B25" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>129254874</v>
       </c>
       <c r="B26" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>129254219</v>
       </c>
       <c r="B27" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3504,7 +3504,7 @@
         <v>129244388</v>
       </c>
       <c r="B28" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3618,10 +3618,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129254201</v>
+        <v>129241899</v>
       </c>
       <c r="B29" t="n">
-        <v>57727</v>
+        <v>79070</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3629,34 +3629,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>486797</v>
+        <v>486803</v>
       </c>
       <c r="R29" t="n">
-        <v>7037788</v>
+        <v>7037939</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3686,14 +3686,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3704,26 +3714,46 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129254876</v>
+        <v>129254201</v>
       </c>
       <c r="B30" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3755,10 +3785,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>486409</v>
+        <v>486797</v>
       </c>
       <c r="R30" t="n">
-        <v>7037957</v>
+        <v>7037788</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3795,7 +3825,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3810,22 +3840,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129241899</v>
+        <v>129254876</v>
       </c>
       <c r="B31" t="n">
-        <v>79044</v>
+        <v>57730</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3833,34 +3863,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>486803</v>
+        <v>486409</v>
       </c>
       <c r="R31" t="n">
-        <v>7037939</v>
+        <v>7037957</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3890,24 +3920,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3918,36 +3938,16 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -3957,7 +3957,7 @@
         <v>129254873</v>
       </c>
       <c r="B32" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
         <v>129254877</v>
       </c>
       <c r="B33" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         <v>129254204</v>
       </c>
       <c r="B34" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4263,7 +4263,7 @@
         <v>129254202</v>
       </c>
       <c r="B35" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         <v>129254207</v>
       </c>
       <c r="B36" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4467,7 +4467,7 @@
         <v>129254203</v>
       </c>
       <c r="B37" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         <v>129254217</v>
       </c>
       <c r="B38" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4668,10 +4668,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129244231</v>
+        <v>129254226</v>
       </c>
       <c r="B39" t="n">
-        <v>79044</v>
+        <v>78083</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4679,37 +4679,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>486671</v>
+        <v>486585</v>
       </c>
       <c r="R39" t="n">
-        <v>7037887</v>
+        <v>7038070</v>
       </c>
       <c r="S39" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4736,24 +4736,9 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4768,22 +4753,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129254226</v>
+        <v>129244231</v>
       </c>
       <c r="B40" t="n">
-        <v>78057</v>
+        <v>79070</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4791,37 +4776,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>486585</v>
+        <v>486671</v>
       </c>
       <c r="R40" t="n">
-        <v>7038070</v>
+        <v>7037887</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4848,9 +4833,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4865,44 +4865,44 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129254879</v>
+        <v>129254225</v>
       </c>
       <c r="B41" t="n">
-        <v>57727</v>
+        <v>80079</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4912,10 +4912,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>486552</v>
+        <v>486624</v>
       </c>
       <c r="R41" t="n">
-        <v>7037942</v>
+        <v>7038036</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4950,11 +4950,6 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -4967,22 +4962,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129254872</v>
+        <v>129254230</v>
       </c>
       <c r="B42" t="n">
-        <v>57727</v>
+        <v>82905</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4990,21 +4985,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5014,10 +5009,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>486715</v>
+        <v>486609</v>
       </c>
       <c r="R42" t="n">
-        <v>7037924</v>
+        <v>7038052</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5052,11 +5047,6 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5069,22 +5059,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129243863</v>
+        <v>129254879</v>
       </c>
       <c r="B43" t="n">
-        <v>79044</v>
+        <v>57730</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5092,37 +5082,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>486663</v>
+        <v>486552</v>
       </c>
       <c r="R43" t="n">
-        <v>7037905</v>
+        <v>7037942</v>
       </c>
       <c r="S43" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5149,24 +5139,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Långväxta bålar, på flera granar.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5177,51 +5157,26 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129243061</v>
+        <v>129254872</v>
       </c>
       <c r="B44" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5247,26 +5202,16 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>486568</v>
+        <v>486715</v>
       </c>
       <c r="R44" t="n">
-        <v>7037962</v>
+        <v>7037924</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5296,24 +5241,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5324,89 +5259,64 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129254225</v>
+        <v>129243863</v>
       </c>
       <c r="B45" t="n">
-        <v>80053</v>
+        <v>79070</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>486624</v>
+        <v>486663</v>
       </c>
       <c r="R45" t="n">
-        <v>7038036</v>
+        <v>7037905</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5433,11 +5343,26 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Långväxta bålar, på flera granar.</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5446,26 +5371,51 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129254230</v>
+        <v>129243061</v>
       </c>
       <c r="B46" t="n">
-        <v>82878</v>
+        <v>57730</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5473,34 +5423,44 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>486609</v>
+        <v>486568</v>
       </c>
       <c r="R46" t="n">
-        <v>7038052</v>
+        <v>7037962</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5530,11 +5490,26 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen.</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5543,16 +5518,41 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5562,7 +5562,7 @@
         <v>129254227</v>
       </c>
       <c r="B47" t="n">
-        <v>91549</v>
+        <v>91577</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5656,10 +5656,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129254196</v>
+        <v>129254214</v>
       </c>
       <c r="B48" t="n">
-        <v>83012</v>
+        <v>57730</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5667,21 +5667,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5691,10 +5691,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>486582</v>
+        <v>486551</v>
       </c>
       <c r="R48" t="n">
-        <v>7038072</v>
+        <v>7037889</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5727,6 +5727,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5753,32 +5758,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129254224</v>
+        <v>129254196</v>
       </c>
       <c r="B49" t="n">
-        <v>80053</v>
+        <v>83039</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6456</v>
+        <v>6440</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5788,10 +5793,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>486599</v>
+        <v>486582</v>
       </c>
       <c r="R49" t="n">
-        <v>7038068</v>
+        <v>7038072</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5850,32 +5855,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129254231</v>
+        <v>129254224</v>
       </c>
       <c r="B50" t="n">
-        <v>88952</v>
+        <v>80079</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>510</v>
+        <v>6456</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5885,10 +5890,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>486615</v>
+        <v>486599</v>
       </c>
       <c r="R50" t="n">
-        <v>7037875</v>
+        <v>7038068</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5947,10 +5952,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129254214</v>
+        <v>129254231</v>
       </c>
       <c r="B51" t="n">
-        <v>57727</v>
+        <v>88980</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5958,21 +5963,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5982,10 +5987,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>486551</v>
+        <v>486615</v>
       </c>
       <c r="R51" t="n">
-        <v>7037889</v>
+        <v>7037875</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6018,11 +6023,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6052,7 +6052,7 @@
         <v>129243695</v>
       </c>
       <c r="B52" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6159,7 +6159,7 @@
         <v>129254213</v>
       </c>
       <c r="B53" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6261,7 +6261,7 @@
         <v>129254229</v>
       </c>
       <c r="B54" t="n">
-        <v>82878</v>
+        <v>82905</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6358,7 +6358,7 @@
         <v>129254878</v>
       </c>
       <c r="B55" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6460,7 +6460,7 @@
         <v>129243772</v>
       </c>
       <c r="B56" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 39541-2025 artfynd.xlsx
+++ b/artfynd/A 39541-2025 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129241859</v>
+        <v>129242015</v>
       </c>
       <c r="B3" t="n">
-        <v>79070</v>
+        <v>57730</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,37 +792,47 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tomasbodarna, Tomasbodarna, Jmt</t>
+          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>486860</v>
+        <v>486782</v>
       </c>
       <c r="R3" t="n">
-        <v>7037938</v>
+        <v>7037909</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -851,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -861,7 +871,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -875,7 +890,27 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -893,10 +928,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129242509</v>
+        <v>129254218</v>
       </c>
       <c r="B4" t="n">
-        <v>79070</v>
+        <v>57730</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,37 +939,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486672</v>
+        <v>486524</v>
       </c>
       <c r="R4" t="n">
-        <v>7037952</v>
+        <v>7037965</v>
       </c>
       <c r="S4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -961,19 +996,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:42</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,28 +1014,23 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129254218</v>
+        <v>129254875</v>
       </c>
       <c r="B5" t="n">
         <v>57730</v>
@@ -1040,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>486524</v>
+        <v>486429</v>
       </c>
       <c r="R5" t="n">
-        <v>7037965</v>
+        <v>7037954</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1080,7 +1105,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1095,19 +1120,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129254875</v>
+        <v>129254206</v>
       </c>
       <c r="B6" t="n">
         <v>57730</v>
@@ -1142,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>486429</v>
+        <v>486751</v>
       </c>
       <c r="R6" t="n">
-        <v>7037954</v>
+        <v>7037804</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1182,7 +1207,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1197,39 +1222,39 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129254206</v>
+        <v>129254223</v>
       </c>
       <c r="B7" t="n">
-        <v>57730</v>
+        <v>57571</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1237,17 +1262,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>486751</v>
+        <v>486737</v>
       </c>
       <c r="R7" t="n">
-        <v>7037804</v>
+        <v>7037835</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,11 +1317,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1311,60 +1343,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129254223</v>
+        <v>129241859</v>
       </c>
       <c r="B8" t="n">
-        <v>57571</v>
+        <v>79070</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102621</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Tomasbodarna, Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>486737</v>
+        <v>486860</v>
       </c>
       <c r="R8" t="n">
-        <v>7037835</v>
+        <v>7037938</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1391,11 +1411,21 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1404,26 +1434,31 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129242015</v>
+        <v>129242509</v>
       </c>
       <c r="B9" t="n">
-        <v>57730</v>
+        <v>79070</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1431,44 +1466,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>486782</v>
+        <v>486672</v>
       </c>
       <c r="R9" t="n">
-        <v>7037909</v>
+        <v>7037952</v>
       </c>
       <c r="S9" t="n">
         <v>11</v>
@@ -1500,7 +1525,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1510,12 +1535,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1529,27 +1549,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -2663,10 +2663,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129254216</v>
+        <v>129242968</v>
       </c>
       <c r="B20" t="n">
-        <v>57730</v>
+        <v>79070</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2674,37 +2674,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>486478</v>
+        <v>486617</v>
       </c>
       <c r="R20" t="n">
-        <v>7037962</v>
+        <v>7037991</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2731,14 +2731,19 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2749,26 +2754,41 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129242968</v>
+        <v>129254216</v>
       </c>
       <c r="B21" t="n">
-        <v>79070</v>
+        <v>57730</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2776,37 +2796,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>486617</v>
+        <v>486478</v>
       </c>
       <c r="R21" t="n">
-        <v>7037991</v>
+        <v>7037962</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2833,19 +2853,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>14:51</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>14:51</t>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2856,31 +2871,16 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -5656,10 +5656,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129254214</v>
+        <v>129254231</v>
       </c>
       <c r="B48" t="n">
-        <v>57730</v>
+        <v>88980</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5667,21 +5667,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5691,10 +5691,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>486551</v>
+        <v>486615</v>
       </c>
       <c r="R48" t="n">
-        <v>7037889</v>
+        <v>7037875</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5727,11 +5727,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5758,10 +5753,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129254196</v>
+        <v>129254214</v>
       </c>
       <c r="B49" t="n">
-        <v>83039</v>
+        <v>57730</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5769,21 +5764,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5793,10 +5788,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>486582</v>
+        <v>486551</v>
       </c>
       <c r="R49" t="n">
-        <v>7038072</v>
+        <v>7037889</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5829,6 +5824,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5855,32 +5855,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129254224</v>
+        <v>129254196</v>
       </c>
       <c r="B50" t="n">
-        <v>80079</v>
+        <v>83039</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6456</v>
+        <v>6440</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5890,10 +5890,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>486599</v>
+        <v>486582</v>
       </c>
       <c r="R50" t="n">
-        <v>7038068</v>
+        <v>7038072</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5952,32 +5952,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129254231</v>
+        <v>129254224</v>
       </c>
       <c r="B51" t="n">
-        <v>88980</v>
+        <v>80079</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>510</v>
+        <v>6456</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5987,10 +5987,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>486615</v>
+        <v>486599</v>
       </c>
       <c r="R51" t="n">
-        <v>7037875</v>
+        <v>7038068</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>

--- a/artfynd/A 39541-2025 artfynd.xlsx
+++ b/artfynd/A 39541-2025 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129242015</v>
+        <v>129241859</v>
       </c>
       <c r="B3" t="n">
-        <v>57730</v>
+        <v>79075</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,47 +792,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
+          <t>Tomasbodarna, Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>486782</v>
+        <v>486860</v>
       </c>
       <c r="R3" t="n">
-        <v>7037909</v>
+        <v>7037938</v>
       </c>
       <c r="S3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,7 +851,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -871,12 +861,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,27 +875,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -928,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129254218</v>
+        <v>129242509</v>
       </c>
       <c r="B4" t="n">
-        <v>57730</v>
+        <v>79075</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -939,37 +904,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486524</v>
+        <v>486672</v>
       </c>
       <c r="R4" t="n">
-        <v>7037965</v>
+        <v>7037952</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -996,14 +961,19 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,64 +984,89 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129254875</v>
+        <v>129243687</v>
       </c>
       <c r="B5" t="n">
-        <v>57730</v>
+        <v>98768</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>486429</v>
+        <v>486517</v>
       </c>
       <c r="R5" t="n">
-        <v>7037954</v>
+        <v>7037922</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1098,14 +1093,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Minst 120 plantor och 1 fröställning inom ca 1 m2 yta  intill en naturvårdsnitslad björk.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1114,28 +1119,34 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129254206</v>
+        <v>129254199</v>
       </c>
       <c r="B6" t="n">
-        <v>57730</v>
+        <v>83044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,21 +1154,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1167,10 +1178,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>486751</v>
+        <v>486581</v>
       </c>
       <c r="R6" t="n">
-        <v>7037804</v>
+        <v>7038074</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,11 +1216,6 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1222,72 +1228,60 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129254223</v>
+        <v>129242968</v>
       </c>
       <c r="B7" t="n">
-        <v>57571</v>
+        <v>79075</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102621</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>486737</v>
+        <v>486617</v>
       </c>
       <c r="R7" t="n">
-        <v>7037835</v>
+        <v>7037991</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1314,11 +1308,21 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1327,26 +1331,41 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129241859</v>
+        <v>129254222</v>
       </c>
       <c r="B8" t="n">
-        <v>79070</v>
+        <v>57895</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1354,37 +1373,53 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tomasbodarna, Tomasbodarna, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>486860</v>
+        <v>486607</v>
       </c>
       <c r="R8" t="n">
-        <v>7037938</v>
+        <v>7038047</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1411,21 +1446,11 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>14:27</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>14:27</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1434,31 +1459,26 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129242509</v>
+        <v>129254228</v>
       </c>
       <c r="B9" t="n">
-        <v>79070</v>
+        <v>91607</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1466,37 +1486,33 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>486672</v>
+        <v>486556</v>
       </c>
       <c r="R9" t="n">
-        <v>7037952</v>
+        <v>7037879</v>
       </c>
       <c r="S9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1523,21 +1539,11 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1546,31 +1552,26 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129254871</v>
+        <v>129244388</v>
       </c>
       <c r="B10" t="n">
-        <v>57730</v>
+        <v>79075</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1578,34 +1579,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>486833</v>
+        <v>486782</v>
       </c>
       <c r="R10" t="n">
-        <v>7037850</v>
+        <v>7037877</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1635,14 +1636,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,26 +1664,31 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129254205</v>
+        <v>129241899</v>
       </c>
       <c r="B11" t="n">
-        <v>57730</v>
+        <v>79075</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1680,34 +1696,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>486752</v>
+        <v>486803</v>
       </c>
       <c r="R11" t="n">
-        <v>7037802</v>
+        <v>7037939</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1737,14 +1753,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1755,26 +1781,46 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129254220</v>
+        <v>129254226</v>
       </c>
       <c r="B12" t="n">
-        <v>57730</v>
+        <v>78088</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1782,21 +1828,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1806,10 +1852,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>486583</v>
+        <v>486585</v>
       </c>
       <c r="R12" t="n">
-        <v>7038073</v>
+        <v>7038070</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1844,11 +1890,6 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1861,22 +1902,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129254215</v>
+        <v>129244231</v>
       </c>
       <c r="B13" t="n">
-        <v>57730</v>
+        <v>79075</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1884,37 +1925,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>486524</v>
+        <v>486671</v>
       </c>
       <c r="R13" t="n">
-        <v>7037917</v>
+        <v>7037887</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1941,14 +1982,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1963,70 +2014,60 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129243523</v>
+        <v>129254225</v>
       </c>
       <c r="B14" t="n">
-        <v>57730</v>
+        <v>80084</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>486472</v>
+        <v>486624</v>
       </c>
       <c r="R14" t="n">
-        <v>7037927</v>
+        <v>7038036</v>
       </c>
       <c r="S14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2053,26 +2094,11 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>15:21</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>15:21</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en hyfsat grov gran.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2081,51 +2107,26 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129254208</v>
+        <v>129243863</v>
       </c>
       <c r="B15" t="n">
-        <v>57730</v>
+        <v>79075</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2133,37 +2134,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>486747</v>
+        <v>486663</v>
       </c>
       <c r="R15" t="n">
-        <v>7037816</v>
+        <v>7037905</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2190,14 +2191,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Långväxta bålar, på flera granar.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2208,26 +2219,51 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129254211</v>
+        <v>129254230</v>
       </c>
       <c r="B16" t="n">
-        <v>57730</v>
+        <v>82910</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2235,21 +2271,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2259,10 +2295,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>486582</v>
+        <v>486609</v>
       </c>
       <c r="R16" t="n">
-        <v>7037881</v>
+        <v>7038052</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2297,11 +2333,6 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2314,22 +2345,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129254221</v>
+        <v>129254227</v>
       </c>
       <c r="B17" t="n">
-        <v>57730</v>
+        <v>91583</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2337,21 +2368,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2361,10 +2392,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>486595</v>
+        <v>486462</v>
       </c>
       <c r="R17" t="n">
-        <v>7038075</v>
+        <v>7037962</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2399,11 +2430,6 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2416,80 +2442,60 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129243687</v>
+        <v>129254231</v>
       </c>
       <c r="B18" t="n">
-        <v>98756</v>
+        <v>88986</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>510</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>486517</v>
+        <v>486615</v>
       </c>
       <c r="R18" t="n">
-        <v>7037922</v>
+        <v>7037875</v>
       </c>
       <c r="S18" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2516,60 +2522,39 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>15:26</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>15:26</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Minst 120 plantor och 1 fröställning inom ca 1 m2 yta  intill en naturvårdsnitslad björk.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129254199</v>
+        <v>129254196</v>
       </c>
       <c r="B19" t="n">
-        <v>83039</v>
+        <v>83044</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2601,10 +2586,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>486581</v>
+        <v>486582</v>
       </c>
       <c r="R19" t="n">
-        <v>7038074</v>
+        <v>7038072</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2651,60 +2636,60 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129242968</v>
+        <v>129254224</v>
       </c>
       <c r="B20" t="n">
-        <v>79070</v>
+        <v>80084</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>486617</v>
+        <v>486599</v>
       </c>
       <c r="R20" t="n">
-        <v>7037991</v>
+        <v>7038068</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2731,21 +2716,11 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>14:51</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>14:51</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2754,41 +2729,26 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129254216</v>
+        <v>129243695</v>
       </c>
       <c r="B21" t="n">
-        <v>57730</v>
+        <v>79075</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2796,37 +2756,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>486478</v>
+        <v>486541</v>
       </c>
       <c r="R21" t="n">
-        <v>7037962</v>
+        <v>7037938</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2853,14 +2813,19 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2875,22 +2840,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129254210</v>
+        <v>129254229</v>
       </c>
       <c r="B22" t="n">
-        <v>57730</v>
+        <v>82910</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2898,21 +2863,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2922,10 +2887,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>486650</v>
+        <v>486611</v>
       </c>
       <c r="R22" t="n">
-        <v>7037866</v>
+        <v>7038042</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2960,11 +2925,6 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -2977,22 +2937,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129254222</v>
+        <v>129243772</v>
       </c>
       <c r="B23" t="n">
-        <v>57890</v>
+        <v>79075</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3000,53 +2960,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>486607</v>
+        <v>486608</v>
       </c>
       <c r="R23" t="n">
-        <v>7038047</v>
+        <v>7037908</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3073,11 +3017,21 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3086,26 +3040,51 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129254228</v>
+        <v>129254875</v>
       </c>
       <c r="B24" t="n">
-        <v>91601</v>
+        <v>57735</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3113,19 +3092,23 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3133,10 +3116,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>486556</v>
+        <v>486429</v>
       </c>
       <c r="R24" t="n">
-        <v>7037879</v>
+        <v>7037954</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3171,6 +3154,11 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3183,39 +3171,39 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129254212</v>
+        <v>129254223</v>
       </c>
       <c r="B25" t="n">
-        <v>57730</v>
+        <v>57576</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3223,17 +3211,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>486572</v>
+        <v>486737</v>
       </c>
       <c r="R25" t="n">
-        <v>7037884</v>
+        <v>7037835</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3268,11 +3268,6 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3285,22 +3280,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129254874</v>
+        <v>129242015</v>
       </c>
       <c r="B26" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3326,19 +3321,29 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>486550</v>
+        <v>486782</v>
       </c>
       <c r="R26" t="n">
-        <v>7037929</v>
+        <v>7037909</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3365,14 +3370,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3383,26 +3398,51 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129254219</v>
+        <v>129254218</v>
       </c>
       <c r="B27" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3434,10 +3474,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>486543</v>
+        <v>486524</v>
       </c>
       <c r="R27" t="n">
-        <v>7037939</v>
+        <v>7037965</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3489,22 +3529,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129244388</v>
+        <v>129254206</v>
       </c>
       <c r="B28" t="n">
-        <v>79070</v>
+        <v>57735</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3512,34 +3552,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>486782</v>
+        <v>486751</v>
       </c>
       <c r="R28" t="n">
-        <v>7037877</v>
+        <v>7037804</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3569,24 +3609,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>15:53</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>15:53</t>
-        </is>
-      </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3597,31 +3627,26 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129241899</v>
+        <v>129254871</v>
       </c>
       <c r="B29" t="n">
-        <v>79070</v>
+        <v>57735</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3629,34 +3654,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>486803</v>
+        <v>486833</v>
       </c>
       <c r="R29" t="n">
-        <v>7037939</v>
+        <v>7037850</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3686,24 +3711,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3714,46 +3729,26 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129254201</v>
+        <v>129254205</v>
       </c>
       <c r="B30" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3785,10 +3780,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>486797</v>
+        <v>486752</v>
       </c>
       <c r="R30" t="n">
-        <v>7037788</v>
+        <v>7037802</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3840,22 +3835,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129254876</v>
+        <v>129243523</v>
       </c>
       <c r="B31" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3881,19 +3876,29 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>486409</v>
+        <v>486472</v>
       </c>
       <c r="R31" t="n">
-        <v>7037957</v>
+        <v>7037927</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3920,14 +3925,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på stambasen av en hyfsat grov gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3938,26 +3953,51 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129254873</v>
+        <v>129254220</v>
       </c>
       <c r="B32" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3989,10 +4029,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>486683</v>
+        <v>486583</v>
       </c>
       <c r="R32" t="n">
-        <v>7037917</v>
+        <v>7038073</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4029,7 +4069,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4044,22 +4084,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129254877</v>
+        <v>129254215</v>
       </c>
       <c r="B33" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4091,10 +4131,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>486495</v>
+        <v>486524</v>
       </c>
       <c r="R33" t="n">
-        <v>7037956</v>
+        <v>7037917</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4131,7 +4171,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4146,22 +4186,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129254204</v>
+        <v>129254208</v>
       </c>
       <c r="B34" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4193,10 +4233,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>486767</v>
+        <v>486747</v>
       </c>
       <c r="R34" t="n">
-        <v>7037800</v>
+        <v>7037816</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4233,7 +4273,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4248,22 +4288,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129254202</v>
+        <v>129254211</v>
       </c>
       <c r="B35" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4295,10 +4335,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>486780</v>
+        <v>486582</v>
       </c>
       <c r="R35" t="n">
-        <v>7037796</v>
+        <v>7037881</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4350,22 +4390,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129254207</v>
+        <v>129254221</v>
       </c>
       <c r="B36" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4397,10 +4437,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>486743</v>
+        <v>486595</v>
       </c>
       <c r="R36" t="n">
-        <v>7037808</v>
+        <v>7038075</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4452,22 +4492,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129254203</v>
+        <v>129254216</v>
       </c>
       <c r="B37" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4499,10 +4539,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>486775</v>
+        <v>486478</v>
       </c>
       <c r="R37" t="n">
-        <v>7037792</v>
+        <v>7037962</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4554,22 +4594,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129254217</v>
+        <v>129254210</v>
       </c>
       <c r="B38" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4601,10 +4641,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>486372</v>
+        <v>486650</v>
       </c>
       <c r="R38" t="n">
-        <v>7038001</v>
+        <v>7037866</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4656,22 +4696,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129254226</v>
+        <v>129254212</v>
       </c>
       <c r="B39" t="n">
-        <v>78083</v>
+        <v>57735</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4679,21 +4719,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4703,10 +4743,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>486585</v>
+        <v>486572</v>
       </c>
       <c r="R39" t="n">
-        <v>7038070</v>
+        <v>7037884</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4741,6 +4781,11 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -4753,22 +4798,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129244231</v>
+        <v>129254874</v>
       </c>
       <c r="B40" t="n">
-        <v>79070</v>
+        <v>57735</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4776,37 +4821,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>486671</v>
+        <v>486550</v>
       </c>
       <c r="R40" t="n">
-        <v>7037887</v>
+        <v>7037929</v>
       </c>
       <c r="S40" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4833,24 +4878,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4865,44 +4900,44 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129254225</v>
+        <v>129254219</v>
       </c>
       <c r="B41" t="n">
-        <v>80079</v>
+        <v>57735</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4912,10 +4947,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>486624</v>
+        <v>486543</v>
       </c>
       <c r="R41" t="n">
-        <v>7038036</v>
+        <v>7037939</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4950,6 +4985,11 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -4962,22 +5002,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129254230</v>
+        <v>129254201</v>
       </c>
       <c r="B42" t="n">
-        <v>82905</v>
+        <v>57735</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4985,21 +5025,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5009,10 +5049,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>486609</v>
+        <v>486797</v>
       </c>
       <c r="R42" t="n">
-        <v>7038052</v>
+        <v>7037788</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5047,6 +5087,11 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5059,22 +5104,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129254879</v>
+        <v>129254876</v>
       </c>
       <c r="B43" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5106,10 +5151,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>486552</v>
+        <v>486409</v>
       </c>
       <c r="R43" t="n">
-        <v>7037942</v>
+        <v>7037957</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5173,10 +5218,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129254872</v>
+        <v>129254873</v>
       </c>
       <c r="B44" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5208,10 +5253,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>486715</v>
+        <v>486683</v>
       </c>
       <c r="R44" t="n">
-        <v>7037924</v>
+        <v>7037917</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5275,10 +5320,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129243863</v>
+        <v>129254877</v>
       </c>
       <c r="B45" t="n">
-        <v>79070</v>
+        <v>57735</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5286,37 +5331,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>486663</v>
+        <v>486495</v>
       </c>
       <c r="R45" t="n">
-        <v>7037905</v>
+        <v>7037956</v>
       </c>
       <c r="S45" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5343,24 +5388,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Långväxta bålar, på flera granar.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5371,51 +5406,26 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129243061</v>
+        <v>129254204</v>
       </c>
       <c r="B46" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5441,26 +5451,16 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>486568</v>
+        <v>486767</v>
       </c>
       <c r="R46" t="n">
-        <v>7037962</v>
+        <v>7037800</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5490,24 +5490,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5518,51 +5508,26 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129254227</v>
+        <v>129254202</v>
       </c>
       <c r="B47" t="n">
-        <v>91577</v>
+        <v>57735</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5570,21 +5535,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5594,10 +5559,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>486462</v>
+        <v>486780</v>
       </c>
       <c r="R47" t="n">
-        <v>7037962</v>
+        <v>7037796</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5632,6 +5597,11 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5644,22 +5614,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129254231</v>
+        <v>129254207</v>
       </c>
       <c r="B48" t="n">
-        <v>88980</v>
+        <v>57735</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5667,21 +5637,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5691,10 +5661,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>486615</v>
+        <v>486743</v>
       </c>
       <c r="R48" t="n">
-        <v>7037875</v>
+        <v>7037808</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5729,6 +5699,11 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5741,22 +5716,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129254214</v>
+        <v>129254203</v>
       </c>
       <c r="B49" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5788,10 +5763,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>486551</v>
+        <v>486775</v>
       </c>
       <c r="R49" t="n">
-        <v>7037889</v>
+        <v>7037792</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5843,22 +5818,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129254196</v>
+        <v>129254217</v>
       </c>
       <c r="B50" t="n">
-        <v>83039</v>
+        <v>57735</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5866,21 +5841,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5890,10 +5865,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>486582</v>
+        <v>486372</v>
       </c>
       <c r="R50" t="n">
-        <v>7038072</v>
+        <v>7038001</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5928,6 +5903,11 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -5940,44 +5920,44 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129254224</v>
+        <v>129254879</v>
       </c>
       <c r="B51" t="n">
-        <v>80079</v>
+        <v>57735</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5987,10 +5967,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>486599</v>
+        <v>486552</v>
       </c>
       <c r="R51" t="n">
-        <v>7038068</v>
+        <v>7037942</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6025,6 +6005,11 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6037,22 +6022,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129243695</v>
+        <v>129254872</v>
       </c>
       <c r="B52" t="n">
-        <v>79070</v>
+        <v>57735</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6060,37 +6045,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>486541</v>
+        <v>486715</v>
       </c>
       <c r="R52" t="n">
-        <v>7037938</v>
+        <v>7037924</v>
       </c>
       <c r="S52" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6117,19 +6102,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>15:32</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>15:32</t>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6144,22 +6124,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129254213</v>
+        <v>129243061</v>
       </c>
       <c r="B53" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6185,16 +6165,26 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>486551</v>
+        <v>486568</v>
       </c>
       <c r="R53" t="n">
-        <v>7037886</v>
+        <v>7037962</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6224,14 +6214,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6242,26 +6242,51 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129254229</v>
+        <v>129254214</v>
       </c>
       <c r="B54" t="n">
-        <v>82905</v>
+        <v>57735</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6269,21 +6294,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6293,10 +6318,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>486611</v>
+        <v>486551</v>
       </c>
       <c r="R54" t="n">
-        <v>7038042</v>
+        <v>7037889</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6331,6 +6356,11 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6343,22 +6373,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129254878</v>
+        <v>129254213</v>
       </c>
       <c r="B55" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6390,10 +6420,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>486553</v>
+        <v>486551</v>
       </c>
       <c r="R55" t="n">
-        <v>7037937</v>
+        <v>7037886</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6430,7 +6460,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6445,22 +6475,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129243772</v>
+        <v>129254878</v>
       </c>
       <c r="B56" t="n">
-        <v>79070</v>
+        <v>57735</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6468,37 +6498,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>486608</v>
+        <v>486553</v>
       </c>
       <c r="R56" t="n">
-        <v>7037908</v>
+        <v>7037937</v>
       </c>
       <c r="S56" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6525,19 +6555,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>15:38</t>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6548,41 +6573,16 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>

--- a/artfynd/A 39541-2025 artfynd.xlsx
+++ b/artfynd/A 39541-2025 artfynd.xlsx
@@ -3081,27 +3081,27 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129254875</v>
+        <v>129254223</v>
       </c>
       <c r="B24" t="n">
-        <v>57735</v>
+        <v>57577</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3109,17 +3109,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>486429</v>
+        <v>486737</v>
       </c>
       <c r="R24" t="n">
-        <v>7037954</v>
+        <v>7037835</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3154,11 +3166,6 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3171,39 +3178,39 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129254223</v>
+        <v>129242015</v>
       </c>
       <c r="B25" t="n">
-        <v>57576</v>
+        <v>57736</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3211,32 +3218,30 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>486737</v>
+        <v>486782</v>
       </c>
       <c r="R25" t="n">
-        <v>7037835</v>
+        <v>7037909</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3263,11 +3268,26 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3276,26 +3296,51 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129242015</v>
+        <v>129254206</v>
       </c>
       <c r="B26" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3321,29 +3366,19 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>486782</v>
+        <v>486751</v>
       </c>
       <c r="R26" t="n">
-        <v>7037909</v>
+        <v>7037804</v>
       </c>
       <c r="S26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3370,24 +3405,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3398,41 +3423,16 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3442,7 +3442,7 @@
         <v>129254218</v>
       </c>
       <c r="B27" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3541,10 +3541,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129254206</v>
+        <v>129254875</v>
       </c>
       <c r="B28" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3576,10 +3576,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>486751</v>
+        <v>486429</v>
       </c>
       <c r="R28" t="n">
-        <v>7037804</v>
+        <v>7037954</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3631,22 +3631,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129254871</v>
+        <v>129243523</v>
       </c>
       <c r="B29" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3672,19 +3672,29 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>486833</v>
+        <v>486472</v>
       </c>
       <c r="R29" t="n">
-        <v>7037850</v>
+        <v>7037927</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3711,14 +3721,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre, på stambasen av en hyfsat grov gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3729,16 +3749,41 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3748,7 +3793,7 @@
         <v>129254205</v>
       </c>
       <c r="B30" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3847,10 +3892,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129243523</v>
+        <v>129254871</v>
       </c>
       <c r="B31" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3876,29 +3921,19 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>486472</v>
+        <v>486833</v>
       </c>
       <c r="R31" t="n">
-        <v>7037927</v>
+        <v>7037850</v>
       </c>
       <c r="S31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3925,24 +3960,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>15:21</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>15:21</t>
-        </is>
-      </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en hyfsat grov gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3953,41 +3978,16 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -3997,7 +3997,7 @@
         <v>129254220</v>
       </c>
       <c r="B32" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4099,7 +4099,7 @@
         <v>129254215</v>
       </c>
       <c r="B33" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>129254208</v>
       </c>
       <c r="B34" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4303,7 +4303,7 @@
         <v>129254211</v>
       </c>
       <c r="B35" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         <v>129254221</v>
       </c>
       <c r="B36" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4507,7 +4507,7 @@
         <v>129254216</v>
       </c>
       <c r="B37" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4609,7 +4609,7 @@
         <v>129254210</v>
       </c>
       <c r="B38" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
         <v>129254212</v>
       </c>
       <c r="B39" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
         <v>129254874</v>
       </c>
       <c r="B40" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         <v>129254219</v>
       </c>
       <c r="B41" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         <v>129254201</v>
       </c>
       <c r="B42" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>129254876</v>
       </c>
       <c r="B43" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5218,10 +5218,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129254873</v>
+        <v>129254207</v>
       </c>
       <c r="B44" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5253,10 +5253,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>486683</v>
+        <v>486743</v>
       </c>
       <c r="R44" t="n">
-        <v>7037917</v>
+        <v>7037808</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5293,7 +5293,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5308,22 +5308,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129254877</v>
+        <v>129254873</v>
       </c>
       <c r="B45" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5355,10 +5355,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>486495</v>
+        <v>486683</v>
       </c>
       <c r="R45" t="n">
-        <v>7037956</v>
+        <v>7037917</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5422,10 +5422,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129254204</v>
+        <v>129254877</v>
       </c>
       <c r="B46" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5457,10 +5457,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>486767</v>
+        <v>486495</v>
       </c>
       <c r="R46" t="n">
-        <v>7037800</v>
+        <v>7037956</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5497,7 +5497,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5512,22 +5512,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129254202</v>
+        <v>129254204</v>
       </c>
       <c r="B47" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5559,10 +5559,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>486780</v>
+        <v>486767</v>
       </c>
       <c r="R47" t="n">
-        <v>7037796</v>
+        <v>7037800</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5626,10 +5626,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129254207</v>
+        <v>129254202</v>
       </c>
       <c r="B48" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5661,10 +5661,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>486743</v>
+        <v>486780</v>
       </c>
       <c r="R48" t="n">
-        <v>7037808</v>
+        <v>7037796</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5731,7 +5731,7 @@
         <v>129254203</v>
       </c>
       <c r="B49" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         <v>129254217</v>
       </c>
       <c r="B50" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5932,10 +5932,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129254879</v>
+        <v>129243061</v>
       </c>
       <c r="B51" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5961,16 +5961,26 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>486552</v>
+        <v>486568</v>
       </c>
       <c r="R51" t="n">
-        <v>7037942</v>
+        <v>7037962</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6000,14 +6010,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6018,26 +6038,51 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129254872</v>
+        <v>129254879</v>
       </c>
       <c r="B52" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6069,10 +6114,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>486715</v>
+        <v>486552</v>
       </c>
       <c r="R52" t="n">
-        <v>7037924</v>
+        <v>7037942</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6136,10 +6181,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129243061</v>
+        <v>129254872</v>
       </c>
       <c r="B53" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6165,26 +6210,16 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>486568</v>
+        <v>486715</v>
       </c>
       <c r="R53" t="n">
-        <v>7037962</v>
+        <v>7037924</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6214,24 +6249,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6242,41 +6267,16 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -6286,7 +6286,7 @@
         <v>129254214</v>
       </c>
       <c r="B54" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6388,7 +6388,7 @@
         <v>129254213</v>
       </c>
       <c r="B55" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6490,7 +6490,7 @@
         <v>129254878</v>
       </c>
       <c r="B56" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 39541-2025 artfynd.xlsx
+++ b/artfynd/A 39541-2025 artfynd.xlsx
@@ -5014,7 +5014,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129254201</v>
+        <v>129254876</v>
       </c>
       <c r="B42" t="n">
         <v>57736</v>
@@ -5049,10 +5049,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>486797</v>
+        <v>486409</v>
       </c>
       <c r="R42" t="n">
-        <v>7037788</v>
+        <v>7037957</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5089,7 +5089,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5104,19 +5104,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129254876</v>
+        <v>129254201</v>
       </c>
       <c r="B43" t="n">
         <v>57736</v>
@@ -5151,10 +5151,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>486409</v>
+        <v>486797</v>
       </c>
       <c r="R43" t="n">
-        <v>7037957</v>
+        <v>7037788</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5206,12 +5206,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>

--- a/artfynd/A 39541-2025 artfynd.xlsx
+++ b/artfynd/A 39541-2025 artfynd.xlsx
@@ -3190,7 +3190,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129242015</v>
+        <v>129254218</v>
       </c>
       <c r="B25" t="n">
         <v>57736</v>
@@ -3219,29 +3219,19 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>486782</v>
+        <v>486524</v>
       </c>
       <c r="R25" t="n">
-        <v>7037909</v>
+        <v>7037965</v>
       </c>
       <c r="S25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3268,24 +3258,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3296,48 +3276,23 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129254206</v>
+        <v>129254875</v>
       </c>
       <c r="B26" t="n">
         <v>57736</v>
@@ -3372,10 +3327,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>486751</v>
+        <v>486429</v>
       </c>
       <c r="R26" t="n">
-        <v>7037804</v>
+        <v>7037954</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3412,7 +3367,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3427,19 +3382,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129254218</v>
+        <v>129254206</v>
       </c>
       <c r="B27" t="n">
         <v>57736</v>
@@ -3474,10 +3429,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>486524</v>
+        <v>486751</v>
       </c>
       <c r="R27" t="n">
-        <v>7037965</v>
+        <v>7037804</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3514,7 +3469,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3541,7 +3496,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129254875</v>
+        <v>129242015</v>
       </c>
       <c r="B28" t="n">
         <v>57736</v>
@@ -3570,19 +3525,29 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>486429</v>
+        <v>486782</v>
       </c>
       <c r="R28" t="n">
-        <v>7037954</v>
+        <v>7037909</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3609,14 +3574,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3627,16 +3602,41 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3790,7 +3790,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129254205</v>
+        <v>129254871</v>
       </c>
       <c r="B30" t="n">
         <v>57736</v>
@@ -3825,10 +3825,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>486752</v>
+        <v>486833</v>
       </c>
       <c r="R30" t="n">
-        <v>7037802</v>
+        <v>7037850</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3865,7 +3865,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3880,19 +3880,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129254871</v>
+        <v>129254205</v>
       </c>
       <c r="B31" t="n">
         <v>57736</v>
@@ -3927,10 +3927,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>486833</v>
+        <v>486752</v>
       </c>
       <c r="R31" t="n">
-        <v>7037850</v>
+        <v>7037802</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3967,7 +3967,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3982,12 +3982,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -5014,7 +5014,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129254876</v>
+        <v>129254201</v>
       </c>
       <c r="B42" t="n">
         <v>57736</v>
@@ -5049,10 +5049,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>486409</v>
+        <v>486797</v>
       </c>
       <c r="R42" t="n">
-        <v>7037957</v>
+        <v>7037788</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5089,7 +5089,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5104,19 +5104,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129254201</v>
+        <v>129254876</v>
       </c>
       <c r="B43" t="n">
         <v>57736</v>
@@ -5151,10 +5151,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>486797</v>
+        <v>486409</v>
       </c>
       <c r="R43" t="n">
-        <v>7037788</v>
+        <v>7037957</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5206,19 +5206,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129254207</v>
+        <v>129254873</v>
       </c>
       <c r="B44" t="n">
         <v>57736</v>
@@ -5253,10 +5253,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>486743</v>
+        <v>486683</v>
       </c>
       <c r="R44" t="n">
-        <v>7037808</v>
+        <v>7037917</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5293,7 +5293,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5308,19 +5308,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129254873</v>
+        <v>129254877</v>
       </c>
       <c r="B45" t="n">
         <v>57736</v>
@@ -5355,10 +5355,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>486683</v>
+        <v>486495</v>
       </c>
       <c r="R45" t="n">
-        <v>7037917</v>
+        <v>7037956</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5422,7 +5422,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129254877</v>
+        <v>129254204</v>
       </c>
       <c r="B46" t="n">
         <v>57736</v>
@@ -5457,10 +5457,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>486495</v>
+        <v>486767</v>
       </c>
       <c r="R46" t="n">
-        <v>7037956</v>
+        <v>7037800</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5497,7 +5497,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5512,19 +5512,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129254204</v>
+        <v>129254202</v>
       </c>
       <c r="B47" t="n">
         <v>57736</v>
@@ -5559,10 +5559,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>486767</v>
+        <v>486780</v>
       </c>
       <c r="R47" t="n">
-        <v>7037800</v>
+        <v>7037796</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5626,7 +5626,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129254202</v>
+        <v>129254207</v>
       </c>
       <c r="B48" t="n">
         <v>57736</v>
@@ -5661,10 +5661,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>486780</v>
+        <v>486743</v>
       </c>
       <c r="R48" t="n">
-        <v>7037796</v>
+        <v>7037808</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>

--- a/artfynd/A 39541-2025 artfynd.xlsx
+++ b/artfynd/A 39541-2025 artfynd.xlsx
@@ -3081,27 +3081,27 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129254223</v>
+        <v>129254875</v>
       </c>
       <c r="B24" t="n">
-        <v>57577</v>
+        <v>57736</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3109,29 +3109,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>486737</v>
+        <v>486429</v>
       </c>
       <c r="R24" t="n">
-        <v>7037835</v>
+        <v>7037954</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3166,6 +3154,11 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3178,19 +3171,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129254218</v>
+        <v>129254206</v>
       </c>
       <c r="B25" t="n">
         <v>57736</v>
@@ -3225,10 +3218,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>486524</v>
+        <v>486751</v>
       </c>
       <c r="R25" t="n">
-        <v>7037965</v>
+        <v>7037804</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3265,7 +3258,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3292,7 +3285,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129254875</v>
+        <v>129242015</v>
       </c>
       <c r="B26" t="n">
         <v>57736</v>
@@ -3321,19 +3314,29 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>486429</v>
+        <v>486782</v>
       </c>
       <c r="R26" t="n">
-        <v>7037954</v>
+        <v>7037909</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3360,14 +3363,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3378,23 +3391,48 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129254206</v>
+        <v>129254218</v>
       </c>
       <c r="B27" t="n">
         <v>57736</v>
@@ -3429,10 +3467,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>486751</v>
+        <v>486524</v>
       </c>
       <c r="R27" t="n">
-        <v>7037804</v>
+        <v>7037965</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3469,7 +3507,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3496,27 +3534,27 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129242015</v>
+        <v>129254223</v>
       </c>
       <c r="B28" t="n">
-        <v>57736</v>
+        <v>57577</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3524,30 +3562,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>486782</v>
+        <v>486737</v>
       </c>
       <c r="R28" t="n">
-        <v>7037909</v>
+        <v>7037835</v>
       </c>
       <c r="S28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3574,26 +3614,11 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3602,41 +3627,16 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -5932,7 +5932,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129243061</v>
+        <v>129254879</v>
       </c>
       <c r="B51" t="n">
         <v>57736</v>
@@ -5961,26 +5961,16 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>486568</v>
+        <v>486552</v>
       </c>
       <c r="R51" t="n">
-        <v>7037962</v>
+        <v>7037942</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6010,24 +6000,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6038,48 +6018,23 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129254879</v>
+        <v>129254872</v>
       </c>
       <c r="B52" t="n">
         <v>57736</v>
@@ -6114,10 +6069,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>486552</v>
+        <v>486715</v>
       </c>
       <c r="R52" t="n">
-        <v>7037942</v>
+        <v>7037924</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6181,7 +6136,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129254872</v>
+        <v>129243061</v>
       </c>
       <c r="B53" t="n">
         <v>57736</v>
@@ -6210,16 +6165,26 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>486715</v>
+        <v>486568</v>
       </c>
       <c r="R53" t="n">
-        <v>7037924</v>
+        <v>7037962</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6249,14 +6214,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6267,16 +6242,41 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>

--- a/artfynd/A 39541-2025 artfynd.xlsx
+++ b/artfynd/A 39541-2025 artfynd.xlsx
@@ -3081,7 +3081,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129254875</v>
+        <v>129242015</v>
       </c>
       <c r="B24" t="n">
         <v>57736</v>
@@ -3110,19 +3110,29 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>486429</v>
+        <v>486782</v>
       </c>
       <c r="R24" t="n">
-        <v>7037954</v>
+        <v>7037909</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3149,14 +3159,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3167,23 +3187,48 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129254206</v>
+        <v>129254218</v>
       </c>
       <c r="B25" t="n">
         <v>57736</v>
@@ -3218,10 +3263,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>486751</v>
+        <v>486524</v>
       </c>
       <c r="R25" t="n">
-        <v>7037804</v>
+        <v>7037965</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3258,7 +3303,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3285,7 +3330,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129242015</v>
+        <v>129254875</v>
       </c>
       <c r="B26" t="n">
         <v>57736</v>
@@ -3314,29 +3359,19 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>486782</v>
+        <v>486429</v>
       </c>
       <c r="R26" t="n">
-        <v>7037909</v>
+        <v>7037954</v>
       </c>
       <c r="S26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3363,24 +3398,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3391,48 +3416,23 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129254218</v>
+        <v>129254206</v>
       </c>
       <c r="B27" t="n">
         <v>57736</v>
@@ -3467,10 +3467,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>486524</v>
+        <v>486751</v>
       </c>
       <c r="R27" t="n">
-        <v>7037965</v>
+        <v>7037804</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3507,7 +3507,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3643,7 +3643,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129243523</v>
+        <v>129254871</v>
       </c>
       <c r="B29" t="n">
         <v>57736</v>
@@ -3672,29 +3672,19 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>486472</v>
+        <v>486833</v>
       </c>
       <c r="R29" t="n">
-        <v>7037927</v>
+        <v>7037850</v>
       </c>
       <c r="S29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3721,24 +3711,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>15:21</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>15:21</t>
-        </is>
-      </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en hyfsat grov gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3749,48 +3729,23 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129254871</v>
+        <v>129254205</v>
       </c>
       <c r="B30" t="n">
         <v>57736</v>
@@ -3825,10 +3780,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>486833</v>
+        <v>486752</v>
       </c>
       <c r="R30" t="n">
-        <v>7037850</v>
+        <v>7037802</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3865,7 +3820,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3880,19 +3835,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129254205</v>
+        <v>129254220</v>
       </c>
       <c r="B31" t="n">
         <v>57736</v>
@@ -3927,10 +3882,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>486752</v>
+        <v>486583</v>
       </c>
       <c r="R31" t="n">
-        <v>7037802</v>
+        <v>7038073</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3994,7 +3949,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129254220</v>
+        <v>129254215</v>
       </c>
       <c r="B32" t="n">
         <v>57736</v>
@@ -4029,10 +3984,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>486583</v>
+        <v>486524</v>
       </c>
       <c r="R32" t="n">
-        <v>7038073</v>
+        <v>7037917</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4096,7 +4051,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129254215</v>
+        <v>129243523</v>
       </c>
       <c r="B33" t="n">
         <v>57736</v>
@@ -4125,19 +4080,29 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>486524</v>
+        <v>486472</v>
       </c>
       <c r="R33" t="n">
-        <v>7037917</v>
+        <v>7037927</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4164,14 +4129,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack, äldre, på stambasen av en hyfsat grov gran.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4182,16 +4157,41 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -5218,7 +5218,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129254873</v>
+        <v>129254203</v>
       </c>
       <c r="B44" t="n">
         <v>57736</v>
@@ -5253,10 +5253,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>486683</v>
+        <v>486775</v>
       </c>
       <c r="R44" t="n">
-        <v>7037917</v>
+        <v>7037792</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5293,7 +5293,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5308,19 +5308,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129254877</v>
+        <v>129254873</v>
       </c>
       <c r="B45" t="n">
         <v>57736</v>
@@ -5355,10 +5355,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>486495</v>
+        <v>486683</v>
       </c>
       <c r="R45" t="n">
-        <v>7037956</v>
+        <v>7037917</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5422,7 +5422,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129254204</v>
+        <v>129254877</v>
       </c>
       <c r="B46" t="n">
         <v>57736</v>
@@ -5457,10 +5457,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>486767</v>
+        <v>486495</v>
       </c>
       <c r="R46" t="n">
-        <v>7037800</v>
+        <v>7037956</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5497,7 +5497,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5512,19 +5512,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129254202</v>
+        <v>129254204</v>
       </c>
       <c r="B47" t="n">
         <v>57736</v>
@@ -5559,10 +5559,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>486780</v>
+        <v>486767</v>
       </c>
       <c r="R47" t="n">
-        <v>7037796</v>
+        <v>7037800</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5626,7 +5626,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129254207</v>
+        <v>129254202</v>
       </c>
       <c r="B48" t="n">
         <v>57736</v>
@@ -5661,10 +5661,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>486743</v>
+        <v>486780</v>
       </c>
       <c r="R48" t="n">
-        <v>7037808</v>
+        <v>7037796</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5728,7 +5728,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129254203</v>
+        <v>129254207</v>
       </c>
       <c r="B49" t="n">
         <v>57736</v>
@@ -5763,10 +5763,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>486775</v>
+        <v>486743</v>
       </c>
       <c r="R49" t="n">
-        <v>7037792</v>
+        <v>7037808</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5932,7 +5932,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129254879</v>
+        <v>129243061</v>
       </c>
       <c r="B51" t="n">
         <v>57736</v>
@@ -5961,16 +5961,26 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>486552</v>
+        <v>486568</v>
       </c>
       <c r="R51" t="n">
-        <v>7037942</v>
+        <v>7037962</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6000,14 +6010,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6018,23 +6038,48 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129254872</v>
+        <v>129254879</v>
       </c>
       <c r="B52" t="n">
         <v>57736</v>
@@ -6069,10 +6114,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>486715</v>
+        <v>486552</v>
       </c>
       <c r="R52" t="n">
-        <v>7037924</v>
+        <v>7037942</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6136,7 +6181,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129243061</v>
+        <v>129254872</v>
       </c>
       <c r="B53" t="n">
         <v>57736</v>
@@ -6165,26 +6210,16 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>486568</v>
+        <v>486715</v>
       </c>
       <c r="R53" t="n">
-        <v>7037962</v>
+        <v>7037924</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6214,24 +6249,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6242,41 +6267,16 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>

--- a/artfynd/A 39541-2025 artfynd.xlsx
+++ b/artfynd/A 39541-2025 artfynd.xlsx
@@ -3081,7 +3081,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129242015</v>
+        <v>129254218</v>
       </c>
       <c r="B24" t="n">
         <v>57736</v>
@@ -3110,29 +3110,19 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>486782</v>
+        <v>486524</v>
       </c>
       <c r="R24" t="n">
-        <v>7037909</v>
+        <v>7037965</v>
       </c>
       <c r="S24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3159,24 +3149,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3187,48 +3167,23 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129254218</v>
+        <v>129254875</v>
       </c>
       <c r="B25" t="n">
         <v>57736</v>
@@ -3263,10 +3218,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>486524</v>
+        <v>486429</v>
       </c>
       <c r="R25" t="n">
-        <v>7037965</v>
+        <v>7037954</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3303,7 +3258,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3318,19 +3273,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129254875</v>
+        <v>129254206</v>
       </c>
       <c r="B26" t="n">
         <v>57736</v>
@@ -3365,10 +3320,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>486429</v>
+        <v>486751</v>
       </c>
       <c r="R26" t="n">
-        <v>7037954</v>
+        <v>7037804</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3405,7 +3360,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3420,19 +3375,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129254206</v>
+        <v>129242015</v>
       </c>
       <c r="B27" t="n">
         <v>57736</v>
@@ -3461,19 +3416,29 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>486751</v>
+        <v>486782</v>
       </c>
       <c r="R27" t="n">
-        <v>7037804</v>
+        <v>7037909</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3500,14 +3465,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3518,16 +3493,41 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -5218,7 +5218,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129254203</v>
+        <v>129254873</v>
       </c>
       <c r="B44" t="n">
         <v>57736</v>
@@ -5253,10 +5253,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>486775</v>
+        <v>486683</v>
       </c>
       <c r="R44" t="n">
-        <v>7037792</v>
+        <v>7037917</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5293,7 +5293,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5308,19 +5308,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129254873</v>
+        <v>129254877</v>
       </c>
       <c r="B45" t="n">
         <v>57736</v>
@@ -5355,10 +5355,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>486683</v>
+        <v>486495</v>
       </c>
       <c r="R45" t="n">
-        <v>7037917</v>
+        <v>7037956</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5422,7 +5422,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129254877</v>
+        <v>129254204</v>
       </c>
       <c r="B46" t="n">
         <v>57736</v>
@@ -5457,10 +5457,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>486495</v>
+        <v>486767</v>
       </c>
       <c r="R46" t="n">
-        <v>7037956</v>
+        <v>7037800</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5497,7 +5497,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5512,19 +5512,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129254204</v>
+        <v>129254202</v>
       </c>
       <c r="B47" t="n">
         <v>57736</v>
@@ -5559,10 +5559,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>486767</v>
+        <v>486780</v>
       </c>
       <c r="R47" t="n">
-        <v>7037800</v>
+        <v>7037796</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5626,7 +5626,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129254202</v>
+        <v>129254207</v>
       </c>
       <c r="B48" t="n">
         <v>57736</v>
@@ -5661,10 +5661,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>486780</v>
+        <v>486743</v>
       </c>
       <c r="R48" t="n">
-        <v>7037796</v>
+        <v>7037808</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5728,7 +5728,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129254207</v>
+        <v>129254203</v>
       </c>
       <c r="B49" t="n">
         <v>57736</v>
@@ -5763,10 +5763,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>486743</v>
+        <v>486775</v>
       </c>
       <c r="R49" t="n">
-        <v>7037808</v>
+        <v>7037792</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5932,7 +5932,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129243061</v>
+        <v>129254879</v>
       </c>
       <c r="B51" t="n">
         <v>57736</v>
@@ -5961,26 +5961,16 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>486568</v>
+        <v>486552</v>
       </c>
       <c r="R51" t="n">
-        <v>7037962</v>
+        <v>7037942</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6010,24 +6000,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6038,48 +6018,23 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129254879</v>
+        <v>129254872</v>
       </c>
       <c r="B52" t="n">
         <v>57736</v>
@@ -6114,10 +6069,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>486552</v>
+        <v>486715</v>
       </c>
       <c r="R52" t="n">
-        <v>7037942</v>
+        <v>7037924</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6181,7 +6136,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129254872</v>
+        <v>129243061</v>
       </c>
       <c r="B53" t="n">
         <v>57736</v>
@@ -6210,16 +6165,26 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>486715</v>
+        <v>486568</v>
       </c>
       <c r="R53" t="n">
-        <v>7037924</v>
+        <v>7037962</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6249,14 +6214,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6267,16 +6242,41 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>

--- a/artfynd/A 39541-2025 artfynd.xlsx
+++ b/artfynd/A 39541-2025 artfynd.xlsx
@@ -3081,27 +3081,27 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129254218</v>
+        <v>129254223</v>
       </c>
       <c r="B24" t="n">
-        <v>57736</v>
+        <v>57577</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3109,17 +3109,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>486524</v>
+        <v>486737</v>
       </c>
       <c r="R24" t="n">
-        <v>7037965</v>
+        <v>7037835</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3152,11 +3164,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3183,7 +3190,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129254875</v>
+        <v>129242015</v>
       </c>
       <c r="B25" t="n">
         <v>57736</v>
@@ -3212,19 +3219,29 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>486429</v>
+        <v>486782</v>
       </c>
       <c r="R25" t="n">
-        <v>7037954</v>
+        <v>7037909</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3251,14 +3268,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3269,23 +3296,48 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129254206</v>
+        <v>129254218</v>
       </c>
       <c r="B26" t="n">
         <v>57736</v>
@@ -3320,10 +3372,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>486751</v>
+        <v>486524</v>
       </c>
       <c r="R26" t="n">
-        <v>7037804</v>
+        <v>7037965</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3360,7 +3412,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3387,7 +3439,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129242015</v>
+        <v>129254875</v>
       </c>
       <c r="B27" t="n">
         <v>57736</v>
@@ -3416,29 +3468,19 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>486782</v>
+        <v>486429</v>
       </c>
       <c r="R27" t="n">
-        <v>7037909</v>
+        <v>7037954</v>
       </c>
       <c r="S27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3465,24 +3507,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3493,68 +3525,43 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129254223</v>
+        <v>129254206</v>
       </c>
       <c r="B28" t="n">
-        <v>57577</v>
+        <v>57736</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3562,29 +3569,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>486737</v>
+        <v>486751</v>
       </c>
       <c r="R28" t="n">
-        <v>7037835</v>
+        <v>7037804</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3617,6 +3612,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3643,7 +3643,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129254871</v>
+        <v>129243523</v>
       </c>
       <c r="B29" t="n">
         <v>57736</v>
@@ -3672,19 +3672,29 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>486833</v>
+        <v>486472</v>
       </c>
       <c r="R29" t="n">
-        <v>7037850</v>
+        <v>7037927</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3711,14 +3721,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre, på stambasen av en hyfsat grov gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3729,23 +3749,48 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129254205</v>
+        <v>129254871</v>
       </c>
       <c r="B30" t="n">
         <v>57736</v>
@@ -3780,10 +3825,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>486752</v>
+        <v>486833</v>
       </c>
       <c r="R30" t="n">
-        <v>7037802</v>
+        <v>7037850</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3820,7 +3865,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3835,19 +3880,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129254220</v>
+        <v>129254205</v>
       </c>
       <c r="B31" t="n">
         <v>57736</v>
@@ -3882,10 +3927,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>486583</v>
+        <v>486752</v>
       </c>
       <c r="R31" t="n">
-        <v>7038073</v>
+        <v>7037802</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3949,7 +3994,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129254215</v>
+        <v>129254220</v>
       </c>
       <c r="B32" t="n">
         <v>57736</v>
@@ -3984,10 +4029,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>486524</v>
+        <v>486583</v>
       </c>
       <c r="R32" t="n">
-        <v>7037917</v>
+        <v>7038073</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4051,7 +4096,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129243523</v>
+        <v>129254215</v>
       </c>
       <c r="B33" t="n">
         <v>57736</v>
@@ -4080,29 +4125,19 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>486472</v>
+        <v>486524</v>
       </c>
       <c r="R33" t="n">
-        <v>7037927</v>
+        <v>7037917</v>
       </c>
       <c r="S33" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4129,24 +4164,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>15:21</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>15:21</t>
-        </is>
-      </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en hyfsat grov gran.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4157,41 +4182,16 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -5932,7 +5932,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129254879</v>
+        <v>129243061</v>
       </c>
       <c r="B51" t="n">
         <v>57736</v>
@@ -5961,16 +5961,26 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>486552</v>
+        <v>486568</v>
       </c>
       <c r="R51" t="n">
-        <v>7037942</v>
+        <v>7037962</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6000,14 +6010,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6018,23 +6038,48 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129254872</v>
+        <v>129254879</v>
       </c>
       <c r="B52" t="n">
         <v>57736</v>
@@ -6069,10 +6114,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>486715</v>
+        <v>486552</v>
       </c>
       <c r="R52" t="n">
-        <v>7037924</v>
+        <v>7037942</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6136,7 +6181,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129243061</v>
+        <v>129254872</v>
       </c>
       <c r="B53" t="n">
         <v>57736</v>
@@ -6165,26 +6210,16 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>486568</v>
+        <v>486715</v>
       </c>
       <c r="R53" t="n">
-        <v>7037962</v>
+        <v>7037924</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6214,24 +6249,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6242,41 +6267,16 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>

--- a/artfynd/A 39541-2025 artfynd.xlsx
+++ b/artfynd/A 39541-2025 artfynd.xlsx
@@ -3081,27 +3081,27 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129254223</v>
+        <v>129242015</v>
       </c>
       <c r="B24" t="n">
-        <v>57577</v>
+        <v>57736</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3109,32 +3109,30 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>486737</v>
+        <v>486782</v>
       </c>
       <c r="R24" t="n">
-        <v>7037835</v>
+        <v>7037909</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3161,11 +3159,26 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3174,23 +3187,48 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129242015</v>
+        <v>129254218</v>
       </c>
       <c r="B25" t="n">
         <v>57736</v>
@@ -3219,29 +3257,19 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>486782</v>
+        <v>486524</v>
       </c>
       <c r="R25" t="n">
-        <v>7037909</v>
+        <v>7037965</v>
       </c>
       <c r="S25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3268,24 +3296,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3296,48 +3314,23 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129254218</v>
+        <v>129254206</v>
       </c>
       <c r="B26" t="n">
         <v>57736</v>
@@ -3372,10 +3365,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>486524</v>
+        <v>486751</v>
       </c>
       <c r="R26" t="n">
-        <v>7037965</v>
+        <v>7037804</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3412,7 +3405,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3439,27 +3432,27 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129254875</v>
+        <v>129254223</v>
       </c>
       <c r="B27" t="n">
-        <v>57736</v>
+        <v>57577</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3467,17 +3460,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>486429</v>
+        <v>486737</v>
       </c>
       <c r="R27" t="n">
-        <v>7037954</v>
+        <v>7037835</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3512,11 +3517,6 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3529,19 +3529,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129254206</v>
+        <v>129254875</v>
       </c>
       <c r="B28" t="n">
         <v>57736</v>
@@ -3576,10 +3576,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>486751</v>
+        <v>486429</v>
       </c>
       <c r="R28" t="n">
-        <v>7037804</v>
+        <v>7037954</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3631,12 +3631,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>

--- a/artfynd/A 39541-2025 artfynd.xlsx
+++ b/artfynd/A 39541-2025 artfynd.xlsx
@@ -3081,7 +3081,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129242015</v>
+        <v>129254218</v>
       </c>
       <c r="B24" t="n">
         <v>57736</v>
@@ -3110,29 +3110,19 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>486782</v>
+        <v>486524</v>
       </c>
       <c r="R24" t="n">
-        <v>7037909</v>
+        <v>7037965</v>
       </c>
       <c r="S24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3159,24 +3149,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3187,48 +3167,23 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129254218</v>
+        <v>129254875</v>
       </c>
       <c r="B25" t="n">
         <v>57736</v>
@@ -3263,10 +3218,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>486524</v>
+        <v>486429</v>
       </c>
       <c r="R25" t="n">
-        <v>7037965</v>
+        <v>7037954</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3303,7 +3258,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3318,12 +3273,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3541,7 +3496,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129254875</v>
+        <v>129242015</v>
       </c>
       <c r="B28" t="n">
         <v>57736</v>
@@ -3570,19 +3525,29 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>486429</v>
+        <v>486782</v>
       </c>
       <c r="R28" t="n">
-        <v>7037954</v>
+        <v>7037909</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3609,14 +3574,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3627,16 +3602,41 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -5218,7 +5218,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129254873</v>
+        <v>129254877</v>
       </c>
       <c r="B44" t="n">
         <v>57736</v>
@@ -5253,10 +5253,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>486683</v>
+        <v>486495</v>
       </c>
       <c r="R44" t="n">
-        <v>7037917</v>
+        <v>7037956</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5320,7 +5320,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129254877</v>
+        <v>129254873</v>
       </c>
       <c r="B45" t="n">
         <v>57736</v>
@@ -5355,10 +5355,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>486495</v>
+        <v>486683</v>
       </c>
       <c r="R45" t="n">
-        <v>7037956</v>
+        <v>7037917</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>

--- a/artfynd/A 39541-2025 artfynd.xlsx
+++ b/artfynd/A 39541-2025 artfynd.xlsx
@@ -3081,7 +3081,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129254218</v>
+        <v>129242015</v>
       </c>
       <c r="B24" t="n">
         <v>57736</v>
@@ -3110,19 +3110,29 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>486524</v>
+        <v>486782</v>
       </c>
       <c r="R24" t="n">
-        <v>7037965</v>
+        <v>7037909</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3149,14 +3159,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3167,23 +3187,48 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129254875</v>
+        <v>129254218</v>
       </c>
       <c r="B25" t="n">
         <v>57736</v>
@@ -3218,10 +3263,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>486429</v>
+        <v>486524</v>
       </c>
       <c r="R25" t="n">
-        <v>7037954</v>
+        <v>7037965</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3258,7 +3303,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3273,19 +3318,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129254206</v>
+        <v>129254875</v>
       </c>
       <c r="B26" t="n">
         <v>57736</v>
@@ -3320,10 +3365,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>486751</v>
+        <v>486429</v>
       </c>
       <c r="R26" t="n">
-        <v>7037804</v>
+        <v>7037954</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3360,7 +3405,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3375,39 +3420,39 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129254223</v>
+        <v>129254206</v>
       </c>
       <c r="B27" t="n">
-        <v>57577</v>
+        <v>57736</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3415,29 +3460,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>486737</v>
+        <v>486751</v>
       </c>
       <c r="R27" t="n">
-        <v>7037835</v>
+        <v>7037804</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3470,6 +3503,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3496,27 +3534,27 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129242015</v>
+        <v>129254223</v>
       </c>
       <c r="B28" t="n">
-        <v>57736</v>
+        <v>57577</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3524,30 +3562,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>486782</v>
+        <v>486737</v>
       </c>
       <c r="R28" t="n">
-        <v>7037909</v>
+        <v>7037835</v>
       </c>
       <c r="S28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3574,26 +3614,11 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3602,48 +3627,23 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129243523</v>
+        <v>129254871</v>
       </c>
       <c r="B29" t="n">
         <v>57736</v>
@@ -3672,29 +3672,19 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>486472</v>
+        <v>486833</v>
       </c>
       <c r="R29" t="n">
-        <v>7037927</v>
+        <v>7037850</v>
       </c>
       <c r="S29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3721,24 +3711,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>15:21</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>15:21</t>
-        </is>
-      </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en hyfsat grov gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3749,48 +3729,23 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129254871</v>
+        <v>129254205</v>
       </c>
       <c r="B30" t="n">
         <v>57736</v>
@@ -3825,10 +3780,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>486833</v>
+        <v>486752</v>
       </c>
       <c r="R30" t="n">
-        <v>7037850</v>
+        <v>7037802</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3865,7 +3820,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3880,19 +3835,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129254205</v>
+        <v>129254220</v>
       </c>
       <c r="B31" t="n">
         <v>57736</v>
@@ -3927,10 +3882,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>486752</v>
+        <v>486583</v>
       </c>
       <c r="R31" t="n">
-        <v>7037802</v>
+        <v>7038073</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3994,7 +3949,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129254220</v>
+        <v>129254215</v>
       </c>
       <c r="B32" t="n">
         <v>57736</v>
@@ -4029,10 +3984,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>486583</v>
+        <v>486524</v>
       </c>
       <c r="R32" t="n">
-        <v>7038073</v>
+        <v>7037917</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4096,7 +4051,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129254215</v>
+        <v>129243523</v>
       </c>
       <c r="B33" t="n">
         <v>57736</v>
@@ -4125,19 +4080,29 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>486524</v>
+        <v>486472</v>
       </c>
       <c r="R33" t="n">
-        <v>7037917</v>
+        <v>7037927</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4164,14 +4129,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack, äldre, på stambasen av en hyfsat grov gran.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4182,16 +4157,41 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -5218,7 +5218,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129254877</v>
+        <v>129254207</v>
       </c>
       <c r="B44" t="n">
         <v>57736</v>
@@ -5253,10 +5253,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>486495</v>
+        <v>486743</v>
       </c>
       <c r="R44" t="n">
-        <v>7037956</v>
+        <v>7037808</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5293,7 +5293,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5308,12 +5308,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5422,7 +5422,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129254204</v>
+        <v>129254877</v>
       </c>
       <c r="B46" t="n">
         <v>57736</v>
@@ -5457,10 +5457,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>486767</v>
+        <v>486495</v>
       </c>
       <c r="R46" t="n">
-        <v>7037800</v>
+        <v>7037956</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5497,7 +5497,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5512,19 +5512,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129254202</v>
+        <v>129254204</v>
       </c>
       <c r="B47" t="n">
         <v>57736</v>
@@ -5559,10 +5559,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>486780</v>
+        <v>486767</v>
       </c>
       <c r="R47" t="n">
-        <v>7037796</v>
+        <v>7037800</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5626,7 +5626,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129254207</v>
+        <v>129254202</v>
       </c>
       <c r="B48" t="n">
         <v>57736</v>
@@ -5661,10 +5661,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>486743</v>
+        <v>486780</v>
       </c>
       <c r="R48" t="n">
-        <v>7037808</v>
+        <v>7037796</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>

--- a/artfynd/A 39541-2025 artfynd.xlsx
+++ b/artfynd/A 39541-2025 artfynd.xlsx
@@ -3081,10 +3081,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129242015</v>
+        <v>129254218</v>
       </c>
       <c r="B24" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3110,29 +3110,19 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>486782</v>
+        <v>486524</v>
       </c>
       <c r="R24" t="n">
-        <v>7037909</v>
+        <v>7037965</v>
       </c>
       <c r="S24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3159,24 +3149,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3187,51 +3167,26 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129254218</v>
+        <v>129254875</v>
       </c>
       <c r="B25" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3263,10 +3218,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>486524</v>
+        <v>486429</v>
       </c>
       <c r="R25" t="n">
-        <v>7037965</v>
+        <v>7037954</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3303,7 +3258,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3318,22 +3273,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129254875</v>
+        <v>129254206</v>
       </c>
       <c r="B26" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3365,10 +3320,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>486429</v>
+        <v>486751</v>
       </c>
       <c r="R26" t="n">
-        <v>7037954</v>
+        <v>7037804</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3405,7 +3360,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3420,39 +3375,39 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129254206</v>
+        <v>129254223</v>
       </c>
       <c r="B27" t="n">
-        <v>57736</v>
+        <v>57578</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3460,17 +3415,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>486751</v>
+        <v>486737</v>
       </c>
       <c r="R27" t="n">
-        <v>7037804</v>
+        <v>7037835</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3503,11 +3470,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3534,27 +3496,27 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129254223</v>
+        <v>129242015</v>
       </c>
       <c r="B28" t="n">
-        <v>57577</v>
+        <v>57737</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3562,32 +3524,30 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>486737</v>
+        <v>486782</v>
       </c>
       <c r="R28" t="n">
-        <v>7037835</v>
+        <v>7037909</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3614,11 +3574,26 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3627,26 +3602,51 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129254871</v>
+        <v>129243523</v>
       </c>
       <c r="B29" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3672,19 +3672,29 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>486833</v>
+        <v>486472</v>
       </c>
       <c r="R29" t="n">
-        <v>7037850</v>
+        <v>7037927</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3711,14 +3721,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre, på stambasen av en hyfsat grov gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3729,26 +3749,51 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129254205</v>
+        <v>129254871</v>
       </c>
       <c r="B30" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3780,10 +3825,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>486752</v>
+        <v>486833</v>
       </c>
       <c r="R30" t="n">
-        <v>7037802</v>
+        <v>7037850</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3820,7 +3865,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3835,22 +3880,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129254220</v>
+        <v>129254205</v>
       </c>
       <c r="B31" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3882,10 +3927,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>486583</v>
+        <v>486752</v>
       </c>
       <c r="R31" t="n">
-        <v>7038073</v>
+        <v>7037802</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3949,10 +3994,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129254215</v>
+        <v>129254220</v>
       </c>
       <c r="B32" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3984,10 +4029,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>486524</v>
+        <v>486583</v>
       </c>
       <c r="R32" t="n">
-        <v>7037917</v>
+        <v>7038073</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4051,10 +4096,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129243523</v>
+        <v>129254215</v>
       </c>
       <c r="B33" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4080,29 +4125,19 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>486472</v>
+        <v>486524</v>
       </c>
       <c r="R33" t="n">
-        <v>7037927</v>
+        <v>7037917</v>
       </c>
       <c r="S33" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4129,24 +4164,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>15:21</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>15:21</t>
-        </is>
-      </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en hyfsat grov gran.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4157,41 +4182,16 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4201,7 +4201,7 @@
         <v>129254208</v>
       </c>
       <c r="B34" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4303,7 +4303,7 @@
         <v>129254211</v>
       </c>
       <c r="B35" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         <v>129254221</v>
       </c>
       <c r="B36" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4507,7 +4507,7 @@
         <v>129254216</v>
       </c>
       <c r="B37" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4609,7 +4609,7 @@
         <v>129254210</v>
       </c>
       <c r="B38" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
         <v>129254212</v>
       </c>
       <c r="B39" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
         <v>129254874</v>
       </c>
       <c r="B40" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         <v>129254219</v>
       </c>
       <c r="B41" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         <v>129254201</v>
       </c>
       <c r="B42" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>129254876</v>
       </c>
       <c r="B43" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5218,10 +5218,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129254207</v>
+        <v>129254873</v>
       </c>
       <c r="B44" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5253,10 +5253,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>486743</v>
+        <v>486683</v>
       </c>
       <c r="R44" t="n">
-        <v>7037808</v>
+        <v>7037917</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5293,7 +5293,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5308,22 +5308,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129254873</v>
+        <v>129254877</v>
       </c>
       <c r="B45" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5355,10 +5355,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>486683</v>
+        <v>486495</v>
       </c>
       <c r="R45" t="n">
-        <v>7037917</v>
+        <v>7037956</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5422,10 +5422,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129254877</v>
+        <v>129254204</v>
       </c>
       <c r="B46" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5457,10 +5457,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>486495</v>
+        <v>486767</v>
       </c>
       <c r="R46" t="n">
-        <v>7037956</v>
+        <v>7037800</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5497,7 +5497,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5512,22 +5512,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129254204</v>
+        <v>129254202</v>
       </c>
       <c r="B47" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5559,10 +5559,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>486767</v>
+        <v>486780</v>
       </c>
       <c r="R47" t="n">
-        <v>7037800</v>
+        <v>7037796</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5626,10 +5626,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129254202</v>
+        <v>129254207</v>
       </c>
       <c r="B48" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5661,10 +5661,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>486780</v>
+        <v>486743</v>
       </c>
       <c r="R48" t="n">
-        <v>7037796</v>
+        <v>7037808</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5731,7 +5731,7 @@
         <v>129254203</v>
       </c>
       <c r="B49" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         <v>129254217</v>
       </c>
       <c r="B50" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5935,7 +5935,7 @@
         <v>129243061</v>
       </c>
       <c r="B51" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         <v>129254879</v>
       </c>
       <c r="B52" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6184,7 +6184,7 @@
         <v>129254872</v>
       </c>
       <c r="B53" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6286,7 +6286,7 @@
         <v>129254214</v>
       </c>
       <c r="B54" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6388,7 +6388,7 @@
         <v>129254213</v>
       </c>
       <c r="B55" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6490,7 +6490,7 @@
         <v>129254878</v>
       </c>
       <c r="B56" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 39541-2025 artfynd.xlsx
+++ b/artfynd/A 39541-2025 artfynd.xlsx
@@ -5932,7 +5932,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129243061</v>
+        <v>129254879</v>
       </c>
       <c r="B51" t="n">
         <v>57737</v>
@@ -5961,26 +5961,16 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>486568</v>
+        <v>486552</v>
       </c>
       <c r="R51" t="n">
-        <v>7037962</v>
+        <v>7037942</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6010,24 +6000,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6038,48 +6018,23 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129254879</v>
+        <v>129254872</v>
       </c>
       <c r="B52" t="n">
         <v>57737</v>
@@ -6114,10 +6069,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>486552</v>
+        <v>486715</v>
       </c>
       <c r="R52" t="n">
-        <v>7037942</v>
+        <v>7037924</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6181,7 +6136,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129254872</v>
+        <v>129243061</v>
       </c>
       <c r="B53" t="n">
         <v>57737</v>
@@ -6210,16 +6165,26 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>486715</v>
+        <v>486568</v>
       </c>
       <c r="R53" t="n">
-        <v>7037924</v>
+        <v>7037962</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6249,14 +6214,24 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6267,16 +6242,41 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>

--- a/artfynd/A 39541-2025 artfynd.xlsx
+++ b/artfynd/A 39541-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY56"/>
+  <dimension ref="A1:AY55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110817113</v>
+        <v>129254231</v>
       </c>
       <c r="B2" t="n">
-        <v>90350</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>jämtland, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>486572</v>
+        <v>486615</v>
       </c>
       <c r="R2" t="n">
-        <v>7037977</v>
+        <v>7037875</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-07-14</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-07-14</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,26 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2023</t>
-        </is>
-      </c>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129241859</v>
+        <v>129254227</v>
       </c>
       <c r="B3" t="n">
-        <v>79075</v>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,37 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tomasbodarna, Tomasbodarna, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>486860</v>
+        <v>486462</v>
       </c>
       <c r="R3" t="n">
-        <v>7037938</v>
+        <v>7037962</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -849,21 +840,11 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:27</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:27</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -872,31 +853,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129242509</v>
+        <v>129254229</v>
       </c>
       <c r="B4" t="n">
-        <v>79075</v>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,37 +880,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486672</v>
+        <v>486611</v>
       </c>
       <c r="R4" t="n">
-        <v>7037952</v>
+        <v>7038042</v>
       </c>
       <c r="S4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -961,21 +937,11 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -984,89 +950,64 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129243687</v>
+        <v>129254230</v>
       </c>
       <c r="B5" t="n">
-        <v>98768</v>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>486517</v>
+        <v>486609</v>
       </c>
       <c r="R5" t="n">
-        <v>7037922</v>
+        <v>7038052</v>
       </c>
       <c r="S5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1093,98 +1034,77 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:26</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:26</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Minst 120 plantor och 1 fröställning inom ca 1 m2 yta  intill en naturvårdsnitslad björk.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129254199</v>
+        <v>129241859</v>
       </c>
       <c r="B6" t="n">
-        <v>83044</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Tomasbodarna, Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>486581</v>
+        <v>486860</v>
       </c>
       <c r="R6" t="n">
-        <v>7038074</v>
+        <v>7037938</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1211,11 +1131,21 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1224,30 +1154,35 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129242968</v>
+        <v>129241899</v>
       </c>
       <c r="B7" t="n">
-        <v>79075</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1275,13 +1210,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>486617</v>
+        <v>486803</v>
       </c>
       <c r="R7" t="n">
-        <v>7037991</v>
+        <v>7037939</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1310,7 +1245,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1255,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1331,6 +1271,11 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1362,64 +1307,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129254222</v>
+        <v>129242509</v>
       </c>
       <c r="B8" t="n">
-        <v>57895</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>486607</v>
+        <v>486672</v>
       </c>
       <c r="R8" t="n">
-        <v>7038047</v>
+        <v>7037952</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1446,11 +1375,21 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1459,60 +1398,69 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129254228</v>
+        <v>129242968</v>
       </c>
       <c r="B9" t="n">
-        <v>91607</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>486556</v>
+        <v>486617</v>
       </c>
       <c r="R9" t="n">
-        <v>7037879</v>
+        <v>7037991</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1539,11 +1487,21 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1552,30 +1510,45 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129244388</v>
+        <v>129243695</v>
       </c>
       <c r="B10" t="n">
-        <v>79075</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1603,13 +1576,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>486782</v>
+        <v>486541</v>
       </c>
       <c r="R10" t="n">
-        <v>7037877</v>
+        <v>7037938</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1638,7 +1611,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1648,12 +1621,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:53</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1664,11 +1632,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1685,14 +1648,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129241899</v>
+        <v>129243772</v>
       </c>
       <c r="B11" t="n">
-        <v>79075</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1720,13 +1683,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>486803</v>
+        <v>486608</v>
       </c>
       <c r="R11" t="n">
-        <v>7037939</v>
+        <v>7037908</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1755,7 +1718,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1765,12 +1728,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:29</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1784,7 +1742,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -1797,9 +1755,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1817,48 +1780,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129254226</v>
+        <v>129243863</v>
       </c>
       <c r="B12" t="n">
-        <v>78088</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>486585</v>
+        <v>486663</v>
       </c>
       <c r="R12" t="n">
-        <v>7038070</v>
+        <v>7037905</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1885,11 +1848,26 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Långväxta bålar, på flera granar.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1898,16 +1876,41 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1917,11 +1920,11 @@
         <v>129244231</v>
       </c>
       <c r="B13" t="n">
-        <v>79075</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -2026,45 +2029,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129254225</v>
+        <v>129244388</v>
       </c>
       <c r="B14" t="n">
-        <v>80084</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>486624</v>
+        <v>486782</v>
       </c>
       <c r="R14" t="n">
-        <v>7038036</v>
+        <v>7037877</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2094,11 +2097,26 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2107,26 +2125,31 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129243863</v>
+        <v>129254196</v>
       </c>
       <c r="B15" t="n">
-        <v>79075</v>
+        <v>83307</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2134,37 +2157,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>486663</v>
+        <v>486582</v>
       </c>
       <c r="R15" t="n">
-        <v>7037905</v>
+        <v>7038072</v>
       </c>
       <c r="S15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2191,26 +2214,11 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Långväxta bålar, på flera granar.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2219,51 +2227,26 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129254230</v>
+        <v>129254199</v>
       </c>
       <c r="B16" t="n">
-        <v>82910</v>
+        <v>83307</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2271,21 +2254,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2295,10 +2278,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>486609</v>
+        <v>486581</v>
       </c>
       <c r="R16" t="n">
-        <v>7038052</v>
+        <v>7038074</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2357,32 +2340,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129254227</v>
+        <v>129254224</v>
       </c>
       <c r="B17" t="n">
-        <v>91583</v>
+        <v>80336</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>6456</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2392,10 +2375,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>486462</v>
+        <v>486599</v>
       </c>
       <c r="R17" t="n">
-        <v>7037962</v>
+        <v>7038068</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2454,32 +2437,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129254231</v>
+        <v>129254225</v>
       </c>
       <c r="B18" t="n">
-        <v>88986</v>
+        <v>80336</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>510</v>
+        <v>6456</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2489,10 +2472,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>486615</v>
+        <v>486624</v>
       </c>
       <c r="R18" t="n">
-        <v>7037875</v>
+        <v>7038036</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2551,10 +2534,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129254196</v>
+        <v>129242015</v>
       </c>
       <c r="B19" t="n">
-        <v>83044</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2562,37 +2545,47 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>486582</v>
+        <v>486782</v>
       </c>
       <c r="R19" t="n">
-        <v>7038072</v>
+        <v>7037909</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2619,11 +2612,26 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2632,61 +2640,96 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129254224</v>
+        <v>129243061</v>
       </c>
       <c r="B20" t="n">
-        <v>80084</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>486599</v>
+        <v>486568</v>
       </c>
       <c r="R20" t="n">
-        <v>7038068</v>
+        <v>7037962</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2716,11 +2759,26 @@
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2729,26 +2787,51 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129243695</v>
+        <v>129243523</v>
       </c>
       <c r="B21" t="n">
-        <v>79075</v>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2756,34 +2839,44 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>486541</v>
+        <v>486472</v>
       </c>
       <c r="R21" t="n">
-        <v>7037938</v>
+        <v>7037927</v>
       </c>
       <c r="S21" t="n">
         <v>11</v>
@@ -2815,7 +2908,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2825,7 +2918,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en hyfsat grov gran.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2836,6 +2934,31 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2852,10 +2975,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129254229</v>
+        <v>129254201</v>
       </c>
       <c r="B22" t="n">
-        <v>82910</v>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2863,21 +2986,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2887,10 +3010,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>486611</v>
+        <v>486797</v>
       </c>
       <c r="R22" t="n">
-        <v>7038042</v>
+        <v>7037788</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2923,6 +3046,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2949,10 +3077,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129243772</v>
+        <v>129254202</v>
       </c>
       <c r="B23" t="n">
-        <v>79075</v>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2960,37 +3088,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Mångan, Mångan, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>486608</v>
+        <v>486780</v>
       </c>
       <c r="R23" t="n">
-        <v>7037908</v>
+        <v>7037796</v>
       </c>
       <c r="S23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3017,19 +3145,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>15:38</t>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3040,51 +3163,26 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129254218</v>
+        <v>129254203</v>
       </c>
       <c r="B24" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3116,10 +3214,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>486524</v>
+        <v>486775</v>
       </c>
       <c r="R24" t="n">
-        <v>7037965</v>
+        <v>7037792</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3183,10 +3281,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129254875</v>
+        <v>129254204</v>
       </c>
       <c r="B25" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3218,10 +3316,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>486429</v>
+        <v>486767</v>
       </c>
       <c r="R25" t="n">
-        <v>7037954</v>
+        <v>7037800</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3258,7 +3356,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3273,22 +3371,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129254206</v>
+        <v>129254205</v>
       </c>
       <c r="B26" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3320,10 +3418,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>486751</v>
+        <v>486752</v>
       </c>
       <c r="R26" t="n">
-        <v>7037804</v>
+        <v>7037802</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3360,7 +3458,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3387,10 +3485,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129242015</v>
+        <v>129254206</v>
       </c>
       <c r="B27" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3416,29 +3514,19 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>486782</v>
+        <v>486751</v>
       </c>
       <c r="R27" t="n">
-        <v>7037909</v>
+        <v>7037804</v>
       </c>
       <c r="S27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3465,24 +3553,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3493,68 +3571,43 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129254223</v>
+        <v>129254207</v>
       </c>
       <c r="B28" t="n">
-        <v>57581</v>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3562,29 +3615,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>486737</v>
+        <v>486743</v>
       </c>
       <c r="R28" t="n">
-        <v>7037835</v>
+        <v>7037808</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3617,6 +3658,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3643,10 +3689,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129243523</v>
+        <v>129254208</v>
       </c>
       <c r="B29" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3672,29 +3718,19 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>486472</v>
+        <v>486747</v>
       </c>
       <c r="R29" t="n">
-        <v>7037927</v>
+        <v>7037816</v>
       </c>
       <c r="S29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3721,24 +3757,14 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>15:21</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>15:21</t>
-        </is>
-      </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en hyfsat grov gran.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3749,51 +3775,26 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129254871</v>
+        <v>129254210</v>
       </c>
       <c r="B30" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3825,10 +3826,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>486833</v>
+        <v>486650</v>
       </c>
       <c r="R30" t="n">
-        <v>7037850</v>
+        <v>7037866</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3865,7 +3866,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3880,22 +3881,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129254205</v>
+        <v>129254211</v>
       </c>
       <c r="B31" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3927,10 +3928,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>486752</v>
+        <v>486582</v>
       </c>
       <c r="R31" t="n">
-        <v>7037802</v>
+        <v>7037881</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3994,10 +3995,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129254220</v>
+        <v>129254212</v>
       </c>
       <c r="B32" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4029,10 +4030,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>486583</v>
+        <v>486572</v>
       </c>
       <c r="R32" t="n">
-        <v>7038073</v>
+        <v>7037884</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4096,10 +4097,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129254215</v>
+        <v>129254213</v>
       </c>
       <c r="B33" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4131,10 +4132,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>486524</v>
+        <v>486551</v>
       </c>
       <c r="R33" t="n">
-        <v>7037917</v>
+        <v>7037886</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4198,10 +4199,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129254208</v>
+        <v>129254214</v>
       </c>
       <c r="B34" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4233,10 +4234,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>486747</v>
+        <v>486551</v>
       </c>
       <c r="R34" t="n">
-        <v>7037816</v>
+        <v>7037889</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4300,10 +4301,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129254211</v>
+        <v>129254215</v>
       </c>
       <c r="B35" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4335,10 +4336,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>486582</v>
+        <v>486524</v>
       </c>
       <c r="R35" t="n">
-        <v>7037881</v>
+        <v>7037917</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4402,10 +4403,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129254221</v>
+        <v>129254216</v>
       </c>
       <c r="B36" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4437,10 +4438,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>486595</v>
+        <v>486478</v>
       </c>
       <c r="R36" t="n">
-        <v>7038075</v>
+        <v>7037962</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4504,10 +4505,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129254216</v>
+        <v>129254217</v>
       </c>
       <c r="B37" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4539,10 +4540,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>486478</v>
+        <v>486372</v>
       </c>
       <c r="R37" t="n">
-        <v>7037962</v>
+        <v>7038001</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4606,10 +4607,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129254210</v>
+        <v>129254218</v>
       </c>
       <c r="B38" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4641,10 +4642,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>486650</v>
+        <v>486524</v>
       </c>
       <c r="R38" t="n">
-        <v>7037866</v>
+        <v>7037965</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4708,10 +4709,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129254212</v>
+        <v>129254219</v>
       </c>
       <c r="B39" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4743,10 +4744,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>486572</v>
+        <v>486543</v>
       </c>
       <c r="R39" t="n">
-        <v>7037884</v>
+        <v>7037939</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4810,10 +4811,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129254219</v>
+        <v>129254220</v>
       </c>
       <c r="B40" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4845,10 +4846,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>486543</v>
+        <v>486583</v>
       </c>
       <c r="R40" t="n">
-        <v>7037939</v>
+        <v>7038073</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4912,10 +4913,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129254874</v>
+        <v>129254221</v>
       </c>
       <c r="B41" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4947,10 +4948,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>486550</v>
+        <v>486595</v>
       </c>
       <c r="R41" t="n">
-        <v>7037929</v>
+        <v>7038075</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4987,7 +4988,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5002,22 +5003,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129254201</v>
+        <v>129254871</v>
       </c>
       <c r="B42" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5049,10 +5050,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>486797</v>
+        <v>486833</v>
       </c>
       <c r="R42" t="n">
-        <v>7037788</v>
+        <v>7037850</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5089,7 +5090,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5104,22 +5105,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129254876</v>
+        <v>129254872</v>
       </c>
       <c r="B43" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5151,10 +5152,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>486409</v>
+        <v>486715</v>
       </c>
       <c r="R43" t="n">
-        <v>7037957</v>
+        <v>7037924</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5221,7 +5222,7 @@
         <v>129254873</v>
       </c>
       <c r="B44" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5320,10 +5321,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129254877</v>
+        <v>129254874</v>
       </c>
       <c r="B45" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5355,10 +5356,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>486495</v>
+        <v>486550</v>
       </c>
       <c r="R45" t="n">
-        <v>7037956</v>
+        <v>7037929</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5395,7 +5396,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5422,10 +5423,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129254204</v>
+        <v>129254875</v>
       </c>
       <c r="B46" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5457,10 +5458,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>486767</v>
+        <v>486429</v>
       </c>
       <c r="R46" t="n">
-        <v>7037800</v>
+        <v>7037954</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5497,7 +5498,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5512,22 +5513,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129254202</v>
+        <v>129254876</v>
       </c>
       <c r="B47" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5559,10 +5560,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>486780</v>
+        <v>486409</v>
       </c>
       <c r="R47" t="n">
-        <v>7037796</v>
+        <v>7037957</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5599,7 +5600,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5614,22 +5615,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129254207</v>
+        <v>129254877</v>
       </c>
       <c r="B48" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5661,10 +5662,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>486743</v>
+        <v>486495</v>
       </c>
       <c r="R48" t="n">
-        <v>7037808</v>
+        <v>7037956</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5701,7 +5702,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5716,22 +5717,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129254203</v>
+        <v>129254878</v>
       </c>
       <c r="B49" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5763,10 +5764,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>486775</v>
+        <v>486553</v>
       </c>
       <c r="R49" t="n">
-        <v>7037792</v>
+        <v>7037937</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5803,7 +5804,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5818,22 +5819,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129254217</v>
+        <v>129254879</v>
       </c>
       <c r="B50" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5865,10 +5866,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>486372</v>
+        <v>486552</v>
       </c>
       <c r="R50" t="n">
-        <v>7038001</v>
+        <v>7037942</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5905,7 +5906,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5920,22 +5921,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129254879</v>
+        <v>129254223</v>
       </c>
       <c r="B51" t="n">
-        <v>57740</v>
+        <v>57794</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5943,16 +5944,16 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -5960,17 +5961,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>486552</v>
+        <v>486737</v>
       </c>
       <c r="R51" t="n">
-        <v>7037942</v>
+        <v>7037835</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6005,11 +6018,6 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6022,22 +6030,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129254872</v>
+        <v>129254222</v>
       </c>
       <c r="B52" t="n">
-        <v>57740</v>
+        <v>58114</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6045,34 +6053,50 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>486715</v>
+        <v>486607</v>
       </c>
       <c r="R52" t="n">
-        <v>7037924</v>
+        <v>7038047</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6107,11 +6131,6 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -6124,52 +6143,62 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129243061</v>
+        <v>129243687</v>
       </c>
       <c r="B53" t="n">
-        <v>57740</v>
+        <v>99118</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -6177,17 +6206,17 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Mångan, Lit, Mångan, Lit, Jmt</t>
+          <t>Mångan, Mångan, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>486568</v>
+        <v>486517</v>
       </c>
       <c r="R53" t="n">
-        <v>7037962</v>
+        <v>7037922</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6216,7 +6245,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6226,12 +6255,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Minst 120 plantor och 1 fröställning inom ca 1 m2 yta  intill en naturvårdsnitslad björk.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6240,32 +6269,13 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6283,45 +6293,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129254214</v>
+        <v>110817114</v>
       </c>
       <c r="B54" t="n">
-        <v>57740</v>
+        <v>99140</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Mångbodarna, Jmt</t>
+          <t>jämtland, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>486551</v>
+        <v>486931</v>
       </c>
       <c r="R54" t="n">
-        <v>7037889</v>
+        <v>7037856</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6348,17 +6358,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2023-07-14</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>2023-07-14</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6373,22 +6378,26 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr"/>
+          <t>Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129254213</v>
+        <v>129254226</v>
       </c>
       <c r="B55" t="n">
-        <v>57740</v>
+        <v>78339</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6396,21 +6405,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6420,10 +6429,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>486551</v>
+        <v>486585</v>
       </c>
       <c r="R55" t="n">
-        <v>7037886</v>
+        <v>7038070</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6458,11 +6467,6 @@
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6484,108 +6488,6 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>129254878</v>
-      </c>
-      <c r="B56" t="n">
-        <v>57740</v>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>Mångbodarna, Jmt</t>
-        </is>
-      </c>
-      <c r="Q56" t="n">
-        <v>486553</v>
-      </c>
-      <c r="R56" t="n">
-        <v>7037937</v>
-      </c>
-      <c r="S56" t="n">
-        <v>10</v>
-      </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W56" t="inlineStr">
-        <is>
-          <t>Lit</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AA56" t="inlineStr">
-        <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
-        </is>
-      </c>
-      <c r="AD56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT56" t="inlineStr"/>
-      <c r="AW56" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39541-2025 artfynd.xlsx
+++ b/artfynd/A 39541-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY55"/>
+  <dimension ref="A1:AZ55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129254231</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129254227</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129254229</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129254230</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1172,6 +1197,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129241859</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1304,6 +1334,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129241899</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1416,6 +1451,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129242509</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1538,6 +1578,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129242968</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1645,6 +1690,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129243695</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1777,6 +1827,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129243772</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1914,6 +1969,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129243863</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2026,6 +2086,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129244231</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2143,6 +2208,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129244388</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2240,6 +2310,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129254196</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2337,6 +2412,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129254199</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2434,6 +2514,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129254224</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2531,6 +2616,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129254225</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2678,6 +2768,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129242015</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2825,6 +2920,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129243061</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2972,6 +3072,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129243523</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3074,6 +3179,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129254201</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3176,6 +3286,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129254202</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3278,6 +3393,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129254203</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3380,6 +3500,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129254204</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3482,6 +3607,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129254205</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3584,6 +3714,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129254206</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3686,6 +3821,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129254207</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3788,6 +3928,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129254208</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3890,6 +4035,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129254210</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3992,6 +4142,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129254211</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4094,6 +4249,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129254212</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4196,6 +4356,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129254213</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4298,6 +4463,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129254214</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4400,6 +4570,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129254215</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4502,6 +4677,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129254216</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4604,6 +4784,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129254217</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4706,6 +4891,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129254218</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4808,6 +4998,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129254219</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4910,6 +5105,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129254220</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5012,6 +5212,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129254221</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5114,6 +5319,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129254871</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5216,6 +5426,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129254872</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5318,6 +5533,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129254873</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5420,6 +5640,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129254874</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5522,6 +5747,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129254875</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5624,6 +5854,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129254876</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5726,6 +5961,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129254877</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5828,6 +6068,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129254878</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5930,6 +6175,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129254879</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6039,6 +6289,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129254223</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6152,6 +6407,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129254222</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6290,6 +6550,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129243687</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6391,6 +6656,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110817114</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6488,8 +6758,69 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129254226</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>